--- a/models/Tarnoc_v2_2026-09-07.xlsx
+++ b/models/Tarnoc_v2_2026-09-07.xlsx
@@ -1155,7 +1155,7 @@
     <row r="35">
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Base, EUR3m: 7,400 units and EUR126m revenue in 2030, EBITDA negative until 2030 (EUR18m), 87 people, cash low of -EUR0.25m in December 2029.</t>
+          <t>Base, EUR3m: 310 units in 2027, 1,100 in 2028, 3,300 in 2029, 7,200 in 2030 (EUR123m revenue). EBITDA negative until 2030 (EUR18m), 84 people, cash low of -EUR1.4m in December 2029.</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
     <row r="50">
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Base on EUR3m runs out of cash at the end of 2029. It needs a bigger raise, the two-year BOM pricing, or the extra marketing push above.</t>
+          <t>Base on EUR3m runs out of cash during 2028 and is EUR1.4m short at the end of 2029. It needs a raise of about EUR5m, or the two-year BOM pricing.</t>
         </is>
       </c>
     </row>
@@ -3744,16 +3744,16 @@
         <v>0</v>
       </c>
       <c r="E48" s="32" t="n">
-        <v>28000</v>
+        <v>13000</v>
       </c>
       <c r="F48" s="32" t="n">
-        <v>70000</v>
+        <v>35000</v>
       </c>
       <c r="G48" s="32" t="n">
-        <v>120000</v>
+        <v>85000</v>
       </c>
       <c r="H48" s="32" t="n">
-        <v>170000</v>
+        <v>160000</v>
       </c>
     </row>
     <row r="49">

--- a/models/Tarnoc_v2_2026-09-07.xlsx
+++ b/models/Tarnoc_v2_2026-09-07.xlsx
@@ -778,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:G64"/>
+  <dimension ref="B1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -906,7 +906,7 @@
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>3. Build capacity: the assembly partner's contracted volume, plus 1,000 a month per in-house line once it produces (aggressive case only).</t>
+          <t>3. Build capacity: the assembly partner's contracted volume, plus 1,000 a month per in-house line once it produces (aggressive case only). Own lines are filled first and save the partner's assembly cost.</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
     <row r="38">
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Aggressive, EUR10m: 1,700 / 5,000 / 9,300 / 15,100 units, EUR259m revenue in 2030, EBITDA positive from 2027 (EUR62m in 2030), 256 people. Cash never falls below the EUR6.2m it holds after the raise.</t>
+          <t>Aggressive, EUR10m: 2,800 / 6,900 / 11,700 / 18,800 units, EUR321m revenue in 2030, EBITDA positive from 2027 (EUR5m, then 25m, 49m, 85m), 289 people. EUR9m of capex in Nov 2026 and Jan 2027 for two automated lines; cash low EUR1.0m in January 2027, 90% of the raise used.</t>
         </is>
       </c>
     </row>
@@ -1316,62 +1316,76 @@
     <row r="55">
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Aggressive needs about 60 hires in 2027, a production line and 25 installers signed in the same year. That risk is not in the numbers.</t>
+          <t>Aggressive spends EUR9m on two lines before selling a unit, hires about 75 people in 2027 and signs 36 installers that year. Cash cover at the low point is six weeks. That risk is not in the numbers.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Prices are the client's and unchanged. A forced price cut makes the tier-1 margin worse.</t>
+          <t>The in-house saving (EUR258 a unit) is derived from our own line cost plus a 20% partner margin, because nobody has told us what the assembly partner actually charges. If the BOM tiers do not include assembly, the saving is nil.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="6" t="inlineStr">
         <is>
+          <t>Prices are the client's and unchanged. A forced price cut makes the tier-1 margin worse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="6" t="inlineStr">
+        <is>
           <t>Turbineketel service prices (EUR60 and EUR90 a year) are below the Dutch market. Upside if raised.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="1" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="1" t="inlineStr">
         <is>
           <t>STILL NEEDED FROM THE CLIENT</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n"/>
-      <c r="E59" s="2" t="n"/>
-      <c r="F59" s="2" t="n"/>
-      <c r="G59" s="2" t="n"/>
-    </row>
-    <row r="60">
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>Supplier quotes behind the three BOM tiers, and whether the supplier will price on a two-year volume commitment.</t>
-        </is>
-      </c>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Confirmation of the installer deal: 10% of the unit price on top of the installation fee.</t>
+          <t>Supplier quotes behind the three BOM tiers, and whether the supplier will price on a two-year volume commitment.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="6" t="inlineStr">
         <is>
+          <t>Confirmation of the installer deal: 10% of the unit price on top of the installation fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>What the assembly partner charges per unit and whether it is inside the BOM tiers, so the in-house saving can be a real number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="6" t="inlineStr">
+        <is>
           <t>A view on the direct-to-installer shift (80% direct in 2027, 50% in 2028, 30% by 2030) and on the size of the base raise.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="6" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="B64" s="3" t="inlineStr">
+    <row r="65">
+      <c r="B65" s="6" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>Detail: How to read me for the colour code and switches, Dashboard for the year view, Assumptions for every input.</t>
         </is>
@@ -2087,7 +2101,7 @@
         </is>
       </c>
       <c r="D37" s="10">
-        <f>MIN(INDEX('Financial Statements'!$E$40:$BL$40,MATCH(Assumptions!$F$139,'Financial Statements'!$E$3:$BL$3,0)):INDEX('Financial Statements'!$E$40:$BL$40,60))</f>
+        <f>MIN(INDEX('Financial Statements'!$E$40:$BL$40,MATCH(Assumptions!$F$143,'Financial Statements'!$E$3:$BL$3,0)):INDEX('Financial Statements'!$E$40:$BL$40,60))</f>
         <v/>
       </c>
       <c r="J37" s="28" t="inlineStr">
@@ -2103,7 +2117,7 @@
         </is>
       </c>
       <c r="D38" s="78">
-        <f>INDEX('Financial Statements'!$E$3:$BL$3,MATCH(D37,INDEX('Financial Statements'!$E$40:$BL$40,MATCH(Assumptions!$F$139,'Financial Statements'!$E$3:$BL$3,0)):INDEX('Financial Statements'!$E$40:$BL$40,60),0)+MATCH(Assumptions!$F$139,'Financial Statements'!$E$3:$BL$3,0)-1)</f>
+        <f>INDEX('Financial Statements'!$E$3:$BL$3,MATCH(D37,INDEX('Financial Statements'!$E$40:$BL$40,MATCH(Assumptions!$F$143,'Financial Statements'!$E$3:$BL$3,0)):INDEX('Financial Statements'!$E$40:$BL$40,60),0)+MATCH(Assumptions!$F$143,'Financial Statements'!$E$3:$BL$3,0)-1)</f>
         <v/>
       </c>
     </row>
@@ -2114,7 +2128,7 @@
         </is>
       </c>
       <c r="D39" s="10">
-        <f>MIN(INDEX('Financial Statements'!$E$40:$BL$40,1):INDEX('Financial Statements'!$E$40:$BL$40,MATCH(Assumptions!$F$139,'Financial Statements'!$E$3:$BL$3,0)-1))</f>
+        <f>MIN(INDEX('Financial Statements'!$E$40:$BL$40,1):INDEX('Financial Statements'!$E$40:$BL$40,MATCH(Assumptions!$F$143,'Financial Statements'!$E$3:$BL$3,0)-1))</f>
         <v/>
       </c>
       <c r="J39" s="28" t="inlineStr">
@@ -2264,7 +2278,7 @@
         </is>
       </c>
       <c r="D50" s="10">
-        <f>INDEX('Financial Statements'!$E$40:$BL$40,MATCH(Assumptions!$F$139,'Financial Statements'!$E$3:$BL$3,0))</f>
+        <f>INDEX('Financial Statements'!$E$40:$BL$40,MATCH(Assumptions!$F$143,'Financial Statements'!$E$3:$BL$3,0))</f>
         <v/>
       </c>
     </row>
@@ -2286,7 +2300,7 @@
         </is>
       </c>
       <c r="D52" s="79">
-        <f>IFERROR(D51/SUM(INDEX('Financial Statements'!$E$35:$BL$35,MATCH(Assumptions!$F$139,'Financial Statements'!$E$3:$BL$3,0)):INDEX('Financial Statements'!$E$35:$BL$35,60)),0)</f>
+        <f>IFERROR(D51/SUM(INDEX('Financial Statements'!$E$35:$BL$35,MATCH(Assumptions!$F$143,'Financial Statements'!$E$3:$BL$3,0)):INDEX('Financial Statements'!$E$35:$BL$35,60)),0)</f>
         <v/>
       </c>
       <c r="J52" s="28" t="inlineStr">
@@ -2920,7 +2934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:J142"/>
+  <dimension ref="B1:J146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3859,16 +3873,16 @@
         <v>0</v>
       </c>
       <c r="E48" s="31" t="n">
-        <v>90000</v>
+        <v>150000</v>
       </c>
       <c r="F48" s="31" t="n">
-        <v>190000</v>
+        <v>260000</v>
       </c>
       <c r="G48" s="31" t="n">
-        <v>265000</v>
+        <v>330000</v>
       </c>
       <c r="H48" s="31" t="n">
-        <v>300000</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="49">
@@ -4181,13 +4195,13 @@
         <v>0</v>
       </c>
       <c r="E61" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="F61" s="45" t="n">
-        <v>0.75</v>
-      </c>
       <c r="G61" s="45" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H61" s="45" t="n">
         <v>0.25</v>
@@ -4285,16 +4299,16 @@
         <v>0</v>
       </c>
       <c r="E65" s="47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" s="47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G65" s="47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H65" s="47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
@@ -4705,12 +4719,17 @@
         <v>49310</v>
       </c>
       <c r="E82" s="37" t="n">
-        <v>47300</v>
+        <v>46753</v>
       </c>
       <c r="F82" s="38">
         <f>IF(Assumptions!$E$5=2,E82,D82)</f>
         <v/>
       </c>
+      <c r="J82" s="28" t="inlineStr">
+        <is>
+          <t>aggressive: paid for in January 2027, so both lines run from early 2028 and most volume is built in-house</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="B83" s="6" t="inlineStr">
@@ -4746,15 +4765,20 @@
         </is>
       </c>
       <c r="D84" s="31" t="n">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="E84" s="31" t="n">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="F84" s="32">
         <f>IF(Assumptions!$E$5=2,E84,D84)</f>
         <v/>
       </c>
+      <c r="J84" s="28" t="inlineStr">
+        <is>
+          <t>EUR250 per unit of annual capacity; peers run EUR250 to 600</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="B85" s="6" t="inlineStr">
@@ -4768,15 +4792,20 @@
         </is>
       </c>
       <c r="D85" s="31" t="n">
-        <v>1000000</v>
+        <v>3000000</v>
       </c>
       <c r="E85" s="31" t="n">
-        <v>1000000</v>
+        <v>3000000</v>
       </c>
       <c r="F85" s="32">
         <f>IF(Assumptions!$E$5=2,E85,D85)</f>
         <v/>
       </c>
+      <c r="J85" s="28" t="inlineStr">
+        <is>
+          <t>automated test, balancing and handling, which is why a line runs on 25 operators rather than 35</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="B86" s="6" t="inlineStr">
@@ -4817,10 +4846,10 @@
         </is>
       </c>
       <c r="D87" s="39" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E87" s="39" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F87" s="40">
         <f>IF(Assumptions!$E$5=2,E87,D87)</f>
@@ -4828,7 +4857,7 @@
       </c>
       <c r="J87" s="28" t="inlineStr">
         <is>
-          <t>assembly, balancing, leak test, run-in and electrical test</t>
+          <t>assembly, balancing, leak test, run-in and electrical test, with the automation above; Intergas and Remeha run leaner still</t>
         </is>
       </c>
     </row>
@@ -5092,16 +5121,16 @@
         <v>0</v>
       </c>
       <c r="E100" s="39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F100" s="39" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G100" s="39" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H100" s="39" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101">
@@ -5617,7 +5646,7 @@
     <row r="123">
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>OVERHEADS AND OTHER OPERATING COSTS</t>
+          <t>IN-HOUSE ASSEMBLY  (what building it ourselves saves)</t>
         </is>
       </c>
       <c r="C123" s="2" t="n"/>
@@ -5655,107 +5684,105 @@
     <row r="125">
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Offices and facilities per person</t>
+          <t>Assembly partner margin on top of its cost</t>
         </is>
       </c>
       <c r="C125" s="26" t="inlineStr">
         <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D125" s="31" t="n">
-        <v>700</v>
-      </c>
-      <c r="E125" s="31" t="n">
-        <v>700</v>
-      </c>
-      <c r="F125" s="32">
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D125" s="35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E125" s="35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F125" s="36">
         <f>IF(Assumptions!$E$5=2,E125,D125)</f>
         <v/>
+      </c>
+      <c r="J125" s="28" t="inlineStr">
+        <is>
+          <t>what a contract manufacturer adds to its own cost; the only new number in this block</t>
+        </is>
       </c>
     </row>
     <row r="126">
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>IT and software per person</t>
+          <t>Assembly cost inside the BOM, saved on units we build ourselves</t>
         </is>
       </c>
       <c r="C126" s="26" t="inlineStr">
         <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D126" s="31" t="n">
-        <v>250</v>
-      </c>
-      <c r="E126" s="31" t="n">
-        <v>250</v>
+          <t>EUR/unit</t>
+        </is>
       </c>
       <c r="F126" s="32">
-        <f>IF(Assumptions!$E$5=2,E126,D126)</f>
-        <v/>
+        <f>(Assumptions!$F$87*Assumptions!$F$118+Assumptions!$F$88)/Assumptions!$F$83*(1+Assumptions!$F$125)</f>
+        <v/>
+      </c>
+      <c r="J126" s="28" t="inlineStr">
+        <is>
+          <t>derived from the model: operators plus facility for one line, per unit at full capacity, plus the partner margin. The BOM tiers are partner-built prices, so an in-house unit saves this</t>
+        </is>
       </c>
     </row>
     <row r="127">
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>Travel per person</t>
-        </is>
-      </c>
-      <c r="C127" s="26" t="inlineStr">
-        <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D127" s="31" t="n">
-        <v>300</v>
-      </c>
-      <c r="E127" s="31" t="n">
-        <v>300</v>
-      </c>
-      <c r="F127" s="32">
-        <f>IF(Assumptions!$E$5=2,E127,D127)</f>
-        <v/>
-      </c>
+      <c r="B127" s="1" t="inlineStr">
+        <is>
+          <t>OVERHEADS AND OTHER OPERATING COSTS</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n"/>
+      <c r="E127" s="2" t="n"/>
+      <c r="F127" s="2" t="n"/>
+      <c r="G127" s="2" t="n"/>
+      <c r="H127" s="2" t="n"/>
+      <c r="I127" s="2" t="n"/>
+      <c r="J127" s="2" t="n"/>
     </row>
     <row r="128">
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>Recruitment per net new hire</t>
-        </is>
-      </c>
-      <c r="C128" s="26" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D128" s="31" t="n">
-        <v>8000</v>
-      </c>
-      <c r="E128" s="31" t="n">
-        <v>8000</v>
-      </c>
-      <c r="F128" s="32">
-        <f>IF(Assumptions!$E$5=2,E128,D128)</f>
-        <v/>
-      </c>
+      <c r="B128" s="29" t="n"/>
+      <c r="C128" s="29" t="n"/>
+      <c r="D128" s="30" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E128" s="30" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="F128" s="30" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G128" s="29" t="n"/>
+      <c r="H128" s="29" t="n"/>
+      <c r="I128" s="29" t="n"/>
+      <c r="J128" s="29" t="n"/>
     </row>
     <row r="129">
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>Installer training and demo unit per new partner</t>
+          <t>Offices and facilities per person</t>
         </is>
       </c>
       <c r="C129" s="26" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>EUR/month</t>
         </is>
       </c>
       <c r="D129" s="31" t="n">
-        <v>3500</v>
+        <v>700</v>
       </c>
       <c r="E129" s="31" t="n">
-        <v>3500</v>
+        <v>700</v>
       </c>
       <c r="F129" s="32">
         <f>IF(Assumptions!$E$5=2,E129,D129)</f>
@@ -5765,7 +5792,7 @@
     <row r="130">
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>Finance and legal</t>
+          <t>IT and software per person</t>
         </is>
       </c>
       <c r="C130" s="26" t="inlineStr">
@@ -5774,10 +5801,10 @@
         </is>
       </c>
       <c r="D130" s="31" t="n">
-        <v>7000</v>
+        <v>250</v>
       </c>
       <c r="E130" s="31" t="n">
-        <v>7000</v>
+        <v>250</v>
       </c>
       <c r="F130" s="32">
         <f>IF(Assumptions!$E$5=2,E130,D130)</f>
@@ -5787,7 +5814,7 @@
     <row r="131">
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>Other general</t>
+          <t>Travel per person</t>
         </is>
       </c>
       <c r="C131" s="26" t="inlineStr">
@@ -5796,10 +5823,10 @@
         </is>
       </c>
       <c r="D131" s="31" t="n">
-        <v>5000</v>
+        <v>300</v>
       </c>
       <c r="E131" s="31" t="n">
-        <v>5000</v>
+        <v>300</v>
       </c>
       <c r="F131" s="32">
         <f>IF(Assumptions!$E$5=2,E131,D131)</f>
@@ -5809,12 +5836,12 @@
     <row r="132">
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Ongoing development</t>
+          <t>Recruitment per net new hire</t>
         </is>
       </c>
       <c r="C132" s="26" t="inlineStr">
         <is>
-          <t>EUR/month</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D132" s="31" t="n">
@@ -5831,19 +5858,19 @@
     <row r="133">
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>Third party product development</t>
+          <t>Installer training and demo unit per new partner</t>
         </is>
       </c>
       <c r="C133" s="26" t="inlineStr">
         <is>
-          <t>EUR/month</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D133" s="31" t="n">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="E133" s="31" t="n">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="F133" s="32">
         <f>IF(Assumptions!$E$5=2,E133,D133)</f>
@@ -5853,81 +5880,87 @@
     <row r="134">
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>Annual increase on the costs above</t>
+          <t>Finance and legal</t>
         </is>
       </c>
       <c r="C134" s="26" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D134" s="35" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E134" s="35" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F134" s="36">
+          <t>EUR/month</t>
+        </is>
+      </c>
+      <c r="D134" s="31" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E134" s="31" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F134" s="32">
         <f>IF(Assumptions!$E$5=2,E134,D134)</f>
         <v/>
       </c>
     </row>
     <row r="135">
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>FUNDING</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n"/>
-      <c r="E135" s="2" t="n"/>
-      <c r="F135" s="2" t="n"/>
-      <c r="G135" s="2" t="n"/>
-      <c r="H135" s="2" t="n"/>
-      <c r="I135" s="2" t="n"/>
-      <c r="J135" s="2" t="n"/>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>Other general</t>
+        </is>
+      </c>
+      <c r="C135" s="26" t="inlineStr">
+        <is>
+          <t>EUR/month</t>
+        </is>
+      </c>
+      <c r="D135" s="31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E135" s="31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F135" s="32">
+        <f>IF(Assumptions!$E$5=2,E135,D135)</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
-      <c r="B136" s="29" t="n"/>
-      <c r="C136" s="29" t="n"/>
-      <c r="D136" s="30" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="E136" s="30" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-      <c r="F136" s="30" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G136" s="29" t="n"/>
-      <c r="H136" s="29" t="n"/>
-      <c r="I136" s="29" t="n"/>
-      <c r="J136" s="29" t="n"/>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>Ongoing development</t>
+        </is>
+      </c>
+      <c r="C136" s="26" t="inlineStr">
+        <is>
+          <t>EUR/month</t>
+        </is>
+      </c>
+      <c r="D136" s="31" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E136" s="31" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F136" s="32">
+        <f>IF(Assumptions!$E$5=2,E136,D136)</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>First round, money in</t>
+          <t>Third party product development</t>
         </is>
       </c>
       <c r="C137" s="26" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D137" s="37" t="n">
-        <v>46143</v>
-      </c>
-      <c r="E137" s="37" t="n">
-        <v>46143</v>
-      </c>
-      <c r="F137" s="38">
+          <t>EUR/month</t>
+        </is>
+      </c>
+      <c r="D137" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E137" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F137" s="32">
         <f>IF(Assumptions!$E$5=2,E137,D137)</f>
         <v/>
       </c>
@@ -5935,92 +5968,81 @@
     <row r="138">
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>First round, amount</t>
+          <t>Annual increase on the costs above</t>
         </is>
       </c>
       <c r="C138" s="26" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D138" s="31" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E138" s="31" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F138" s="32">
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D138" s="35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E138" s="35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F138" s="36">
         <f>IF(Assumptions!$E$5=2,E138,D138)</f>
         <v/>
       </c>
     </row>
     <row r="139">
-      <c r="B139" s="6" t="inlineStr">
-        <is>
-          <t>Second round, money in</t>
-        </is>
-      </c>
-      <c r="C139" s="26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D139" s="37" t="n">
-        <v>46296</v>
-      </c>
-      <c r="E139" s="37" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F139" s="38">
-        <f>IF(Assumptions!$E$5=2,E139,D139)</f>
-        <v/>
-      </c>
+      <c r="B139" s="1" t="inlineStr">
+        <is>
+          <t>FUNDING</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" s="2" t="n"/>
+      <c r="E139" s="2" t="n"/>
+      <c r="F139" s="2" t="n"/>
+      <c r="G139" s="2" t="n"/>
+      <c r="H139" s="2" t="n"/>
+      <c r="I139" s="2" t="n"/>
+      <c r="J139" s="2" t="n"/>
     </row>
     <row r="140">
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>Second round, amount</t>
-        </is>
-      </c>
-      <c r="C140" s="26" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D140" s="31" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="E140" s="31" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="F140" s="32">
-        <f>IF(Assumptions!$E$5=2,E140,D140)</f>
-        <v/>
-      </c>
-      <c r="J140" s="28" t="inlineStr">
-        <is>
-          <t>this is the raise the model is built to justify</t>
-        </is>
-      </c>
+      <c r="B140" s="29" t="n"/>
+      <c r="C140" s="29" t="n"/>
+      <c r="D140" s="30" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E140" s="30" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="F140" s="30" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G140" s="29" t="n"/>
+      <c r="H140" s="29" t="n"/>
+      <c r="I140" s="29" t="n"/>
+      <c r="J140" s="29" t="n"/>
     </row>
     <row r="141">
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Convertible loan drawn</t>
+          <t>First round, money in</t>
         </is>
       </c>
       <c r="C141" s="26" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D141" s="31" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E141" s="31" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F141" s="32">
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D141" s="37" t="n">
+        <v>46143</v>
+      </c>
+      <c r="E141" s="37" t="n">
+        <v>46143</v>
+      </c>
+      <c r="F141" s="38">
         <f>IF(Assumptions!$E$5=2,E141,D141)</f>
         <v/>
       </c>
@@ -6028,22 +6050,115 @@
     <row r="142">
       <c r="B142" s="6" t="inlineStr">
         <is>
+          <t>First round, amount</t>
+        </is>
+      </c>
+      <c r="C142" s="26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D142" s="31" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E142" s="31" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F142" s="32">
+        <f>IF(Assumptions!$E$5=2,E142,D142)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>Second round, money in</t>
+        </is>
+      </c>
+      <c r="C143" s="26" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D143" s="37" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E143" s="37" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F143" s="38">
+        <f>IF(Assumptions!$E$5=2,E143,D143)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>Second round, amount</t>
+        </is>
+      </c>
+      <c r="C144" s="26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D144" s="31" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E144" s="31" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F144" s="32">
+        <f>IF(Assumptions!$E$5=2,E144,D144)</f>
+        <v/>
+      </c>
+      <c r="J144" s="28" t="inlineStr">
+        <is>
+          <t>this is the raise the model is built to justify</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>Convertible loan drawn</t>
+        </is>
+      </c>
+      <c r="C145" s="26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D145" s="31" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E145" s="31" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F145" s="32">
+        <f>IF(Assumptions!$E$5=2,E145,D145)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" s="6" t="inlineStr">
+        <is>
           <t>Loan drawn on</t>
         </is>
       </c>
-      <c r="C142" s="26" t="inlineStr">
+      <c r="C146" s="26" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D142" s="37" t="n">
+      <c r="D146" s="37" t="n">
         <v>46204</v>
       </c>
-      <c r="E142" s="37" t="n">
+      <c r="E146" s="37" t="n">
         <v>46204</v>
       </c>
-      <c r="F142" s="38">
-        <f>IF(Assumptions!$E$5=2,E142,D142)</f>
+      <c r="F146" s="38">
+        <f>IF(Assumptions!$E$5=2,E146,D146)</f>
         <v/>
       </c>
     </row>
@@ -6785,243 +6900,243 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>-COGS!E19</f>
+        <f>-COGS!E20</f>
         <v/>
       </c>
       <c r="F7" s="10">
-        <f>-COGS!F19</f>
+        <f>-COGS!F20</f>
         <v/>
       </c>
       <c r="G7" s="10">
-        <f>-COGS!G19</f>
+        <f>-COGS!G20</f>
         <v/>
       </c>
       <c r="H7" s="10">
-        <f>-COGS!H19</f>
+        <f>-COGS!H20</f>
         <v/>
       </c>
       <c r="I7" s="10">
-        <f>-COGS!I19</f>
+        <f>-COGS!I20</f>
         <v/>
       </c>
       <c r="J7" s="10">
-        <f>-COGS!J19</f>
+        <f>-COGS!J20</f>
         <v/>
       </c>
       <c r="K7" s="10">
-        <f>-COGS!K19</f>
+        <f>-COGS!K20</f>
         <v/>
       </c>
       <c r="L7" s="10">
-        <f>-COGS!L19</f>
+        <f>-COGS!L20</f>
         <v/>
       </c>
       <c r="M7" s="10">
-        <f>-COGS!M19</f>
+        <f>-COGS!M20</f>
         <v/>
       </c>
       <c r="N7" s="10">
-        <f>-COGS!N19</f>
+        <f>-COGS!N20</f>
         <v/>
       </c>
       <c r="O7" s="10">
-        <f>-COGS!O19</f>
+        <f>-COGS!O20</f>
         <v/>
       </c>
       <c r="P7" s="10">
-        <f>-COGS!P19</f>
+        <f>-COGS!P20</f>
         <v/>
       </c>
       <c r="Q7" s="10">
-        <f>-COGS!Q19</f>
+        <f>-COGS!Q20</f>
         <v/>
       </c>
       <c r="R7" s="10">
-        <f>-COGS!R19</f>
+        <f>-COGS!R20</f>
         <v/>
       </c>
       <c r="S7" s="10">
-        <f>-COGS!S19</f>
+        <f>-COGS!S20</f>
         <v/>
       </c>
       <c r="T7" s="10">
-        <f>-COGS!T19</f>
+        <f>-COGS!T20</f>
         <v/>
       </c>
       <c r="U7" s="10">
-        <f>-COGS!U19</f>
+        <f>-COGS!U20</f>
         <v/>
       </c>
       <c r="V7" s="10">
-        <f>-COGS!V19</f>
+        <f>-COGS!V20</f>
         <v/>
       </c>
       <c r="W7" s="10">
-        <f>-COGS!W19</f>
+        <f>-COGS!W20</f>
         <v/>
       </c>
       <c r="X7" s="10">
-        <f>-COGS!X19</f>
+        <f>-COGS!X20</f>
         <v/>
       </c>
       <c r="Y7" s="10">
-        <f>-COGS!Y19</f>
+        <f>-COGS!Y20</f>
         <v/>
       </c>
       <c r="Z7" s="10">
-        <f>-COGS!Z19</f>
+        <f>-COGS!Z20</f>
         <v/>
       </c>
       <c r="AA7" s="10">
-        <f>-COGS!AA19</f>
+        <f>-COGS!AA20</f>
         <v/>
       </c>
       <c r="AB7" s="10">
-        <f>-COGS!AB19</f>
+        <f>-COGS!AB20</f>
         <v/>
       </c>
       <c r="AC7" s="10">
-        <f>-COGS!AC19</f>
+        <f>-COGS!AC20</f>
         <v/>
       </c>
       <c r="AD7" s="10">
-        <f>-COGS!AD19</f>
+        <f>-COGS!AD20</f>
         <v/>
       </c>
       <c r="AE7" s="10">
-        <f>-COGS!AE19</f>
+        <f>-COGS!AE20</f>
         <v/>
       </c>
       <c r="AF7" s="10">
-        <f>-COGS!AF19</f>
+        <f>-COGS!AF20</f>
         <v/>
       </c>
       <c r="AG7" s="10">
-        <f>-COGS!AG19</f>
+        <f>-COGS!AG20</f>
         <v/>
       </c>
       <c r="AH7" s="10">
-        <f>-COGS!AH19</f>
+        <f>-COGS!AH20</f>
         <v/>
       </c>
       <c r="AI7" s="10">
-        <f>-COGS!AI19</f>
+        <f>-COGS!AI20</f>
         <v/>
       </c>
       <c r="AJ7" s="10">
-        <f>-COGS!AJ19</f>
+        <f>-COGS!AJ20</f>
         <v/>
       </c>
       <c r="AK7" s="10">
-        <f>-COGS!AK19</f>
+        <f>-COGS!AK20</f>
         <v/>
       </c>
       <c r="AL7" s="10">
-        <f>-COGS!AL19</f>
+        <f>-COGS!AL20</f>
         <v/>
       </c>
       <c r="AM7" s="10">
-        <f>-COGS!AM19</f>
+        <f>-COGS!AM20</f>
         <v/>
       </c>
       <c r="AN7" s="10">
-        <f>-COGS!AN19</f>
+        <f>-COGS!AN20</f>
         <v/>
       </c>
       <c r="AO7" s="10">
-        <f>-COGS!AO19</f>
+        <f>-COGS!AO20</f>
         <v/>
       </c>
       <c r="AP7" s="10">
-        <f>-COGS!AP19</f>
+        <f>-COGS!AP20</f>
         <v/>
       </c>
       <c r="AQ7" s="10">
-        <f>-COGS!AQ19</f>
+        <f>-COGS!AQ20</f>
         <v/>
       </c>
       <c r="AR7" s="10">
-        <f>-COGS!AR19</f>
+        <f>-COGS!AR20</f>
         <v/>
       </c>
       <c r="AS7" s="10">
-        <f>-COGS!AS19</f>
+        <f>-COGS!AS20</f>
         <v/>
       </c>
       <c r="AT7" s="10">
-        <f>-COGS!AT19</f>
+        <f>-COGS!AT20</f>
         <v/>
       </c>
       <c r="AU7" s="10">
-        <f>-COGS!AU19</f>
+        <f>-COGS!AU20</f>
         <v/>
       </c>
       <c r="AV7" s="10">
-        <f>-COGS!AV19</f>
+        <f>-COGS!AV20</f>
         <v/>
       </c>
       <c r="AW7" s="10">
-        <f>-COGS!AW19</f>
+        <f>-COGS!AW20</f>
         <v/>
       </c>
       <c r="AX7" s="10">
-        <f>-COGS!AX19</f>
+        <f>-COGS!AX20</f>
         <v/>
       </c>
       <c r="AY7" s="10">
-        <f>-COGS!AY19</f>
+        <f>-COGS!AY20</f>
         <v/>
       </c>
       <c r="AZ7" s="10">
-        <f>-COGS!AZ19</f>
+        <f>-COGS!AZ20</f>
         <v/>
       </c>
       <c r="BA7" s="10">
-        <f>-COGS!BA19</f>
+        <f>-COGS!BA20</f>
         <v/>
       </c>
       <c r="BB7" s="10">
-        <f>-COGS!BB19</f>
+        <f>-COGS!BB20</f>
         <v/>
       </c>
       <c r="BC7" s="10">
-        <f>-COGS!BC19</f>
+        <f>-COGS!BC20</f>
         <v/>
       </c>
       <c r="BD7" s="10">
-        <f>-COGS!BD19</f>
+        <f>-COGS!BD20</f>
         <v/>
       </c>
       <c r="BE7" s="10">
-        <f>-COGS!BE19</f>
+        <f>-COGS!BE20</f>
         <v/>
       </c>
       <c r="BF7" s="10">
-        <f>-COGS!BF19</f>
+        <f>-COGS!BF20</f>
         <v/>
       </c>
       <c r="BG7" s="10">
-        <f>-COGS!BG19</f>
+        <f>-COGS!BG20</f>
         <v/>
       </c>
       <c r="BH7" s="10">
-        <f>-COGS!BH19</f>
+        <f>-COGS!BH20</f>
         <v/>
       </c>
       <c r="BI7" s="10">
-        <f>-COGS!BI19</f>
+        <f>-COGS!BI20</f>
         <v/>
       </c>
       <c r="BJ7" s="10">
-        <f>-COGS!BJ19</f>
+        <f>-COGS!BJ20</f>
         <v/>
       </c>
       <c r="BK7" s="10">
-        <f>-COGS!BK19</f>
+        <f>-COGS!BK20</f>
         <v/>
       </c>
       <c r="BL7" s="10">
-        <f>-COGS!BL19</f>
+        <f>-COGS!BL20</f>
         <v/>
       </c>
       <c r="BN7" s="53">
@@ -13136,243 +13251,243 @@
         </is>
       </c>
       <c r="E35" s="10">
-        <f>IF(AND(YEAR(E$3)=YEAR(Assumptions!$F$137),MONTH(E$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(E$3)=YEAR(Assumptions!$F$139),MONTH(E$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(E$3)=YEAR(Assumptions!$F$141),MONTH(E$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(E$3)=YEAR(Assumptions!$F$143),MONTH(E$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="F35" s="10">
-        <f>IF(AND(YEAR(F$3)=YEAR(Assumptions!$F$137),MONTH(F$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(F$3)=YEAR(Assumptions!$F$139),MONTH(F$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(F$3)=YEAR(Assumptions!$F$141),MONTH(F$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(F$3)=YEAR(Assumptions!$F$143),MONTH(F$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="G35" s="10">
-        <f>IF(AND(YEAR(G$3)=YEAR(Assumptions!$F$137),MONTH(G$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(G$3)=YEAR(Assumptions!$F$139),MONTH(G$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(G$3)=YEAR(Assumptions!$F$141),MONTH(G$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(G$3)=YEAR(Assumptions!$F$143),MONTH(G$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="H35" s="10">
-        <f>IF(AND(YEAR(H$3)=YEAR(Assumptions!$F$137),MONTH(H$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(H$3)=YEAR(Assumptions!$F$139),MONTH(H$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(H$3)=YEAR(Assumptions!$F$141),MONTH(H$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(H$3)=YEAR(Assumptions!$F$143),MONTH(H$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="I35" s="10">
-        <f>IF(AND(YEAR(I$3)=YEAR(Assumptions!$F$137),MONTH(I$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(I$3)=YEAR(Assumptions!$F$139),MONTH(I$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(I$3)=YEAR(Assumptions!$F$141),MONTH(I$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(I$3)=YEAR(Assumptions!$F$143),MONTH(I$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="J35" s="10">
-        <f>IF(AND(YEAR(J$3)=YEAR(Assumptions!$F$137),MONTH(J$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(J$3)=YEAR(Assumptions!$F$139),MONTH(J$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(J$3)=YEAR(Assumptions!$F$141),MONTH(J$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(J$3)=YEAR(Assumptions!$F$143),MONTH(J$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="K35" s="10">
-        <f>IF(AND(YEAR(K$3)=YEAR(Assumptions!$F$137),MONTH(K$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(K$3)=YEAR(Assumptions!$F$139),MONTH(K$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(K$3)=YEAR(Assumptions!$F$141),MONTH(K$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(K$3)=YEAR(Assumptions!$F$143),MONTH(K$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="L35" s="10">
-        <f>IF(AND(YEAR(L$3)=YEAR(Assumptions!$F$137),MONTH(L$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(L$3)=YEAR(Assumptions!$F$139),MONTH(L$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(L$3)=YEAR(Assumptions!$F$141),MONTH(L$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(L$3)=YEAR(Assumptions!$F$143),MONTH(L$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="M35" s="10">
-        <f>IF(AND(YEAR(M$3)=YEAR(Assumptions!$F$137),MONTH(M$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(M$3)=YEAR(Assumptions!$F$139),MONTH(M$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(M$3)=YEAR(Assumptions!$F$141),MONTH(M$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(M$3)=YEAR(Assumptions!$F$143),MONTH(M$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="N35" s="10">
-        <f>IF(AND(YEAR(N$3)=YEAR(Assumptions!$F$137),MONTH(N$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(N$3)=YEAR(Assumptions!$F$139),MONTH(N$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(N$3)=YEAR(Assumptions!$F$141),MONTH(N$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(N$3)=YEAR(Assumptions!$F$143),MONTH(N$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="O35" s="10">
-        <f>IF(AND(YEAR(O$3)=YEAR(Assumptions!$F$137),MONTH(O$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(O$3)=YEAR(Assumptions!$F$139),MONTH(O$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(O$3)=YEAR(Assumptions!$F$141),MONTH(O$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(O$3)=YEAR(Assumptions!$F$143),MONTH(O$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="P35" s="10">
-        <f>IF(AND(YEAR(P$3)=YEAR(Assumptions!$F$137),MONTH(P$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(P$3)=YEAR(Assumptions!$F$139),MONTH(P$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(P$3)=YEAR(Assumptions!$F$141),MONTH(P$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(P$3)=YEAR(Assumptions!$F$143),MONTH(P$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="Q35" s="10">
-        <f>IF(AND(YEAR(Q$3)=YEAR(Assumptions!$F$137),MONTH(Q$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(Q$3)=YEAR(Assumptions!$F$139),MONTH(Q$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(Q$3)=YEAR(Assumptions!$F$141),MONTH(Q$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(Q$3)=YEAR(Assumptions!$F$143),MONTH(Q$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="R35" s="10">
-        <f>IF(AND(YEAR(R$3)=YEAR(Assumptions!$F$137),MONTH(R$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(R$3)=YEAR(Assumptions!$F$139),MONTH(R$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(R$3)=YEAR(Assumptions!$F$141),MONTH(R$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(R$3)=YEAR(Assumptions!$F$143),MONTH(R$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="S35" s="10">
-        <f>IF(AND(YEAR(S$3)=YEAR(Assumptions!$F$137),MONTH(S$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(S$3)=YEAR(Assumptions!$F$139),MONTH(S$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(S$3)=YEAR(Assumptions!$F$141),MONTH(S$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(S$3)=YEAR(Assumptions!$F$143),MONTH(S$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="T35" s="10">
-        <f>IF(AND(YEAR(T$3)=YEAR(Assumptions!$F$137),MONTH(T$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(T$3)=YEAR(Assumptions!$F$139),MONTH(T$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(T$3)=YEAR(Assumptions!$F$141),MONTH(T$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(T$3)=YEAR(Assumptions!$F$143),MONTH(T$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="U35" s="10">
-        <f>IF(AND(YEAR(U$3)=YEAR(Assumptions!$F$137),MONTH(U$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(U$3)=YEAR(Assumptions!$F$139),MONTH(U$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(U$3)=YEAR(Assumptions!$F$141),MONTH(U$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(U$3)=YEAR(Assumptions!$F$143),MONTH(U$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="V35" s="10">
-        <f>IF(AND(YEAR(V$3)=YEAR(Assumptions!$F$137),MONTH(V$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(V$3)=YEAR(Assumptions!$F$139),MONTH(V$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(V$3)=YEAR(Assumptions!$F$141),MONTH(V$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(V$3)=YEAR(Assumptions!$F$143),MONTH(V$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="W35" s="10">
-        <f>IF(AND(YEAR(W$3)=YEAR(Assumptions!$F$137),MONTH(W$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(W$3)=YEAR(Assumptions!$F$139),MONTH(W$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(W$3)=YEAR(Assumptions!$F$141),MONTH(W$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(W$3)=YEAR(Assumptions!$F$143),MONTH(W$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="X35" s="10">
-        <f>IF(AND(YEAR(X$3)=YEAR(Assumptions!$F$137),MONTH(X$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(X$3)=YEAR(Assumptions!$F$139),MONTH(X$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(X$3)=YEAR(Assumptions!$F$141),MONTH(X$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(X$3)=YEAR(Assumptions!$F$143),MONTH(X$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="Y35" s="10">
-        <f>IF(AND(YEAR(Y$3)=YEAR(Assumptions!$F$137),MONTH(Y$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(Y$3)=YEAR(Assumptions!$F$139),MONTH(Y$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(Y$3)=YEAR(Assumptions!$F$141),MONTH(Y$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(Y$3)=YEAR(Assumptions!$F$143),MONTH(Y$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="Z35" s="10">
-        <f>IF(AND(YEAR(Z$3)=YEAR(Assumptions!$F$137),MONTH(Z$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(Z$3)=YEAR(Assumptions!$F$139),MONTH(Z$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(Z$3)=YEAR(Assumptions!$F$141),MONTH(Z$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(Z$3)=YEAR(Assumptions!$F$143),MONTH(Z$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AA35" s="10">
-        <f>IF(AND(YEAR(AA$3)=YEAR(Assumptions!$F$137),MONTH(AA$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AA$3)=YEAR(Assumptions!$F$139),MONTH(AA$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AA$3)=YEAR(Assumptions!$F$141),MONTH(AA$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AA$3)=YEAR(Assumptions!$F$143),MONTH(AA$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AB35" s="10">
-        <f>IF(AND(YEAR(AB$3)=YEAR(Assumptions!$F$137),MONTH(AB$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AB$3)=YEAR(Assumptions!$F$139),MONTH(AB$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AB$3)=YEAR(Assumptions!$F$141),MONTH(AB$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AB$3)=YEAR(Assumptions!$F$143),MONTH(AB$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AC35" s="10">
-        <f>IF(AND(YEAR(AC$3)=YEAR(Assumptions!$F$137),MONTH(AC$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AC$3)=YEAR(Assumptions!$F$139),MONTH(AC$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AC$3)=YEAR(Assumptions!$F$141),MONTH(AC$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AC$3)=YEAR(Assumptions!$F$143),MONTH(AC$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AD35" s="10">
-        <f>IF(AND(YEAR(AD$3)=YEAR(Assumptions!$F$137),MONTH(AD$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AD$3)=YEAR(Assumptions!$F$139),MONTH(AD$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AD$3)=YEAR(Assumptions!$F$141),MONTH(AD$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AD$3)=YEAR(Assumptions!$F$143),MONTH(AD$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AE35" s="10">
-        <f>IF(AND(YEAR(AE$3)=YEAR(Assumptions!$F$137),MONTH(AE$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AE$3)=YEAR(Assumptions!$F$139),MONTH(AE$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AE$3)=YEAR(Assumptions!$F$141),MONTH(AE$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AE$3)=YEAR(Assumptions!$F$143),MONTH(AE$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AF35" s="10">
-        <f>IF(AND(YEAR(AF$3)=YEAR(Assumptions!$F$137),MONTH(AF$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AF$3)=YEAR(Assumptions!$F$139),MONTH(AF$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AF$3)=YEAR(Assumptions!$F$141),MONTH(AF$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AF$3)=YEAR(Assumptions!$F$143),MONTH(AF$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AG35" s="10">
-        <f>IF(AND(YEAR(AG$3)=YEAR(Assumptions!$F$137),MONTH(AG$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AG$3)=YEAR(Assumptions!$F$139),MONTH(AG$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AG$3)=YEAR(Assumptions!$F$141),MONTH(AG$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AG$3)=YEAR(Assumptions!$F$143),MONTH(AG$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AH35" s="10">
-        <f>IF(AND(YEAR(AH$3)=YEAR(Assumptions!$F$137),MONTH(AH$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AH$3)=YEAR(Assumptions!$F$139),MONTH(AH$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AH$3)=YEAR(Assumptions!$F$141),MONTH(AH$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AH$3)=YEAR(Assumptions!$F$143),MONTH(AH$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AI35" s="10">
-        <f>IF(AND(YEAR(AI$3)=YEAR(Assumptions!$F$137),MONTH(AI$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AI$3)=YEAR(Assumptions!$F$139),MONTH(AI$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AI$3)=YEAR(Assumptions!$F$141),MONTH(AI$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AI$3)=YEAR(Assumptions!$F$143),MONTH(AI$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AJ35" s="10">
-        <f>IF(AND(YEAR(AJ$3)=YEAR(Assumptions!$F$137),MONTH(AJ$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AJ$3)=YEAR(Assumptions!$F$139),MONTH(AJ$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AJ$3)=YEAR(Assumptions!$F$141),MONTH(AJ$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AJ$3)=YEAR(Assumptions!$F$143),MONTH(AJ$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AK35" s="10">
-        <f>IF(AND(YEAR(AK$3)=YEAR(Assumptions!$F$137),MONTH(AK$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AK$3)=YEAR(Assumptions!$F$139),MONTH(AK$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AK$3)=YEAR(Assumptions!$F$141),MONTH(AK$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AK$3)=YEAR(Assumptions!$F$143),MONTH(AK$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AL35" s="10">
-        <f>IF(AND(YEAR(AL$3)=YEAR(Assumptions!$F$137),MONTH(AL$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AL$3)=YEAR(Assumptions!$F$139),MONTH(AL$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AL$3)=YEAR(Assumptions!$F$141),MONTH(AL$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AL$3)=YEAR(Assumptions!$F$143),MONTH(AL$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AM35" s="10">
-        <f>IF(AND(YEAR(AM$3)=YEAR(Assumptions!$F$137),MONTH(AM$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AM$3)=YEAR(Assumptions!$F$139),MONTH(AM$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AM$3)=YEAR(Assumptions!$F$141),MONTH(AM$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AM$3)=YEAR(Assumptions!$F$143),MONTH(AM$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AN35" s="10">
-        <f>IF(AND(YEAR(AN$3)=YEAR(Assumptions!$F$137),MONTH(AN$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AN$3)=YEAR(Assumptions!$F$139),MONTH(AN$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AN$3)=YEAR(Assumptions!$F$141),MONTH(AN$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AN$3)=YEAR(Assumptions!$F$143),MONTH(AN$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AO35" s="10">
-        <f>IF(AND(YEAR(AO$3)=YEAR(Assumptions!$F$137),MONTH(AO$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AO$3)=YEAR(Assumptions!$F$139),MONTH(AO$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AO$3)=YEAR(Assumptions!$F$141),MONTH(AO$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AO$3)=YEAR(Assumptions!$F$143),MONTH(AO$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AP35" s="10">
-        <f>IF(AND(YEAR(AP$3)=YEAR(Assumptions!$F$137),MONTH(AP$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AP$3)=YEAR(Assumptions!$F$139),MONTH(AP$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AP$3)=YEAR(Assumptions!$F$141),MONTH(AP$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AP$3)=YEAR(Assumptions!$F$143),MONTH(AP$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AQ35" s="10">
-        <f>IF(AND(YEAR(AQ$3)=YEAR(Assumptions!$F$137),MONTH(AQ$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AQ$3)=YEAR(Assumptions!$F$139),MONTH(AQ$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AQ$3)=YEAR(Assumptions!$F$141),MONTH(AQ$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AQ$3)=YEAR(Assumptions!$F$143),MONTH(AQ$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AR35" s="10">
-        <f>IF(AND(YEAR(AR$3)=YEAR(Assumptions!$F$137),MONTH(AR$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AR$3)=YEAR(Assumptions!$F$139),MONTH(AR$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AR$3)=YEAR(Assumptions!$F$141),MONTH(AR$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AR$3)=YEAR(Assumptions!$F$143),MONTH(AR$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AS35" s="10">
-        <f>IF(AND(YEAR(AS$3)=YEAR(Assumptions!$F$137),MONTH(AS$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AS$3)=YEAR(Assumptions!$F$139),MONTH(AS$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AS$3)=YEAR(Assumptions!$F$141),MONTH(AS$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AS$3)=YEAR(Assumptions!$F$143),MONTH(AS$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AT35" s="10">
-        <f>IF(AND(YEAR(AT$3)=YEAR(Assumptions!$F$137),MONTH(AT$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AT$3)=YEAR(Assumptions!$F$139),MONTH(AT$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AT$3)=YEAR(Assumptions!$F$141),MONTH(AT$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AT$3)=YEAR(Assumptions!$F$143),MONTH(AT$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AU35" s="10">
-        <f>IF(AND(YEAR(AU$3)=YEAR(Assumptions!$F$137),MONTH(AU$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AU$3)=YEAR(Assumptions!$F$139),MONTH(AU$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AU$3)=YEAR(Assumptions!$F$141),MONTH(AU$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AU$3)=YEAR(Assumptions!$F$143),MONTH(AU$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AV35" s="10">
-        <f>IF(AND(YEAR(AV$3)=YEAR(Assumptions!$F$137),MONTH(AV$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AV$3)=YEAR(Assumptions!$F$139),MONTH(AV$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AV$3)=YEAR(Assumptions!$F$141),MONTH(AV$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AV$3)=YEAR(Assumptions!$F$143),MONTH(AV$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AW35" s="10">
-        <f>IF(AND(YEAR(AW$3)=YEAR(Assumptions!$F$137),MONTH(AW$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AW$3)=YEAR(Assumptions!$F$139),MONTH(AW$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AW$3)=YEAR(Assumptions!$F$141),MONTH(AW$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AW$3)=YEAR(Assumptions!$F$143),MONTH(AW$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AX35" s="10">
-        <f>IF(AND(YEAR(AX$3)=YEAR(Assumptions!$F$137),MONTH(AX$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AX$3)=YEAR(Assumptions!$F$139),MONTH(AX$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AX$3)=YEAR(Assumptions!$F$141),MONTH(AX$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AX$3)=YEAR(Assumptions!$F$143),MONTH(AX$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AY35" s="10">
-        <f>IF(AND(YEAR(AY$3)=YEAR(Assumptions!$F$137),MONTH(AY$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AY$3)=YEAR(Assumptions!$F$139),MONTH(AY$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AY$3)=YEAR(Assumptions!$F$141),MONTH(AY$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AY$3)=YEAR(Assumptions!$F$143),MONTH(AY$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="AZ35" s="10">
-        <f>IF(AND(YEAR(AZ$3)=YEAR(Assumptions!$F$137),MONTH(AZ$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AZ$3)=YEAR(Assumptions!$F$139),MONTH(AZ$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(AZ$3)=YEAR(Assumptions!$F$141),MONTH(AZ$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AZ$3)=YEAR(Assumptions!$F$143),MONTH(AZ$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="BA35" s="10">
-        <f>IF(AND(YEAR(BA$3)=YEAR(Assumptions!$F$137),MONTH(BA$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BA$3)=YEAR(Assumptions!$F$139),MONTH(BA$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(BA$3)=YEAR(Assumptions!$F$141),MONTH(BA$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BA$3)=YEAR(Assumptions!$F$143),MONTH(BA$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="BB35" s="10">
-        <f>IF(AND(YEAR(BB$3)=YEAR(Assumptions!$F$137),MONTH(BB$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BB$3)=YEAR(Assumptions!$F$139),MONTH(BB$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(BB$3)=YEAR(Assumptions!$F$141),MONTH(BB$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BB$3)=YEAR(Assumptions!$F$143),MONTH(BB$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="BC35" s="10">
-        <f>IF(AND(YEAR(BC$3)=YEAR(Assumptions!$F$137),MONTH(BC$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BC$3)=YEAR(Assumptions!$F$139),MONTH(BC$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(BC$3)=YEAR(Assumptions!$F$141),MONTH(BC$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BC$3)=YEAR(Assumptions!$F$143),MONTH(BC$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="BD35" s="10">
-        <f>IF(AND(YEAR(BD$3)=YEAR(Assumptions!$F$137),MONTH(BD$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BD$3)=YEAR(Assumptions!$F$139),MONTH(BD$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(BD$3)=YEAR(Assumptions!$F$141),MONTH(BD$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BD$3)=YEAR(Assumptions!$F$143),MONTH(BD$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="BE35" s="10">
-        <f>IF(AND(YEAR(BE$3)=YEAR(Assumptions!$F$137),MONTH(BE$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BE$3)=YEAR(Assumptions!$F$139),MONTH(BE$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(BE$3)=YEAR(Assumptions!$F$141),MONTH(BE$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BE$3)=YEAR(Assumptions!$F$143),MONTH(BE$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="BF35" s="10">
-        <f>IF(AND(YEAR(BF$3)=YEAR(Assumptions!$F$137),MONTH(BF$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BF$3)=YEAR(Assumptions!$F$139),MONTH(BF$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(BF$3)=YEAR(Assumptions!$F$141),MONTH(BF$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BF$3)=YEAR(Assumptions!$F$143),MONTH(BF$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="BG35" s="10">
-        <f>IF(AND(YEAR(BG$3)=YEAR(Assumptions!$F$137),MONTH(BG$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BG$3)=YEAR(Assumptions!$F$139),MONTH(BG$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(BG$3)=YEAR(Assumptions!$F$141),MONTH(BG$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BG$3)=YEAR(Assumptions!$F$143),MONTH(BG$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="BH35" s="10">
-        <f>IF(AND(YEAR(BH$3)=YEAR(Assumptions!$F$137),MONTH(BH$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BH$3)=YEAR(Assumptions!$F$139),MONTH(BH$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(BH$3)=YEAR(Assumptions!$F$141),MONTH(BH$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BH$3)=YEAR(Assumptions!$F$143),MONTH(BH$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="BI35" s="10">
-        <f>IF(AND(YEAR(BI$3)=YEAR(Assumptions!$F$137),MONTH(BI$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BI$3)=YEAR(Assumptions!$F$139),MONTH(BI$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(BI$3)=YEAR(Assumptions!$F$141),MONTH(BI$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BI$3)=YEAR(Assumptions!$F$143),MONTH(BI$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="BJ35" s="10">
-        <f>IF(AND(YEAR(BJ$3)=YEAR(Assumptions!$F$137),MONTH(BJ$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BJ$3)=YEAR(Assumptions!$F$139),MONTH(BJ$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(BJ$3)=YEAR(Assumptions!$F$141),MONTH(BJ$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BJ$3)=YEAR(Assumptions!$F$143),MONTH(BJ$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="BK35" s="10">
-        <f>IF(AND(YEAR(BK$3)=YEAR(Assumptions!$F$137),MONTH(BK$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BK$3)=YEAR(Assumptions!$F$139),MONTH(BK$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(BK$3)=YEAR(Assumptions!$F$141),MONTH(BK$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BK$3)=YEAR(Assumptions!$F$143),MONTH(BK$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="BL35" s="10">
-        <f>IF(AND(YEAR(BL$3)=YEAR(Assumptions!$F$137),MONTH(BL$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BL$3)=YEAR(Assumptions!$F$139),MONTH(BL$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
+        <f>IF(AND(YEAR(BL$3)=YEAR(Assumptions!$F$141),MONTH(BL$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BL$3)=YEAR(Assumptions!$F$143),MONTH(BL$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
         <v/>
       </c>
       <c r="BN35" s="53">
@@ -13413,243 +13528,243 @@
         </is>
       </c>
       <c r="E36" s="10">
-        <f>IF(AND(YEAR(E$3)=YEAR(Assumptions!$F$142),MONTH(E$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(E$3)=YEAR(Assumptions!$F$146),MONTH(E$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="F36" s="10">
-        <f>IF(AND(YEAR(F$3)=YEAR(Assumptions!$F$142),MONTH(F$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(F$3)=YEAR(Assumptions!$F$146),MONTH(F$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="G36" s="10">
-        <f>IF(AND(YEAR(G$3)=YEAR(Assumptions!$F$142),MONTH(G$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(G$3)=YEAR(Assumptions!$F$146),MONTH(G$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="H36" s="10">
-        <f>IF(AND(YEAR(H$3)=YEAR(Assumptions!$F$142),MONTH(H$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(H$3)=YEAR(Assumptions!$F$146),MONTH(H$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="I36" s="10">
-        <f>IF(AND(YEAR(I$3)=YEAR(Assumptions!$F$142),MONTH(I$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(I$3)=YEAR(Assumptions!$F$146),MONTH(I$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="J36" s="10">
-        <f>IF(AND(YEAR(J$3)=YEAR(Assumptions!$F$142),MONTH(J$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(J$3)=YEAR(Assumptions!$F$146),MONTH(J$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="K36" s="10">
-        <f>IF(AND(YEAR(K$3)=YEAR(Assumptions!$F$142),MONTH(K$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(K$3)=YEAR(Assumptions!$F$146),MONTH(K$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="L36" s="10">
-        <f>IF(AND(YEAR(L$3)=YEAR(Assumptions!$F$142),MONTH(L$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(L$3)=YEAR(Assumptions!$F$146),MONTH(L$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="M36" s="10">
-        <f>IF(AND(YEAR(M$3)=YEAR(Assumptions!$F$142),MONTH(M$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(M$3)=YEAR(Assumptions!$F$146),MONTH(M$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="N36" s="10">
-        <f>IF(AND(YEAR(N$3)=YEAR(Assumptions!$F$142),MONTH(N$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(N$3)=YEAR(Assumptions!$F$146),MONTH(N$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="O36" s="10">
-        <f>IF(AND(YEAR(O$3)=YEAR(Assumptions!$F$142),MONTH(O$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(O$3)=YEAR(Assumptions!$F$146),MONTH(O$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="P36" s="10">
-        <f>IF(AND(YEAR(P$3)=YEAR(Assumptions!$F$142),MONTH(P$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(P$3)=YEAR(Assumptions!$F$146),MONTH(P$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="Q36" s="10">
-        <f>IF(AND(YEAR(Q$3)=YEAR(Assumptions!$F$142),MONTH(Q$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(Q$3)=YEAR(Assumptions!$F$146),MONTH(Q$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="R36" s="10">
-        <f>IF(AND(YEAR(R$3)=YEAR(Assumptions!$F$142),MONTH(R$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(R$3)=YEAR(Assumptions!$F$146),MONTH(R$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="S36" s="10">
-        <f>IF(AND(YEAR(S$3)=YEAR(Assumptions!$F$142),MONTH(S$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(S$3)=YEAR(Assumptions!$F$146),MONTH(S$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="T36" s="10">
-        <f>IF(AND(YEAR(T$3)=YEAR(Assumptions!$F$142),MONTH(T$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(T$3)=YEAR(Assumptions!$F$146),MONTH(T$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="U36" s="10">
-        <f>IF(AND(YEAR(U$3)=YEAR(Assumptions!$F$142),MONTH(U$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(U$3)=YEAR(Assumptions!$F$146),MONTH(U$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="V36" s="10">
-        <f>IF(AND(YEAR(V$3)=YEAR(Assumptions!$F$142),MONTH(V$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(V$3)=YEAR(Assumptions!$F$146),MONTH(V$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="W36" s="10">
-        <f>IF(AND(YEAR(W$3)=YEAR(Assumptions!$F$142),MONTH(W$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(W$3)=YEAR(Assumptions!$F$146),MONTH(W$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="X36" s="10">
-        <f>IF(AND(YEAR(X$3)=YEAR(Assumptions!$F$142),MONTH(X$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(X$3)=YEAR(Assumptions!$F$146),MONTH(X$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="Y36" s="10">
-        <f>IF(AND(YEAR(Y$3)=YEAR(Assumptions!$F$142),MONTH(Y$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(Y$3)=YEAR(Assumptions!$F$146),MONTH(Y$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="Z36" s="10">
-        <f>IF(AND(YEAR(Z$3)=YEAR(Assumptions!$F$142),MONTH(Z$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(Z$3)=YEAR(Assumptions!$F$146),MONTH(Z$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AA36" s="10">
-        <f>IF(AND(YEAR(AA$3)=YEAR(Assumptions!$F$142),MONTH(AA$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AA$3)=YEAR(Assumptions!$F$146),MONTH(AA$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AB36" s="10">
-        <f>IF(AND(YEAR(AB$3)=YEAR(Assumptions!$F$142),MONTH(AB$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AB$3)=YEAR(Assumptions!$F$146),MONTH(AB$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AC36" s="10">
-        <f>IF(AND(YEAR(AC$3)=YEAR(Assumptions!$F$142),MONTH(AC$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AC$3)=YEAR(Assumptions!$F$146),MONTH(AC$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AD36" s="10">
-        <f>IF(AND(YEAR(AD$3)=YEAR(Assumptions!$F$142),MONTH(AD$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AD$3)=YEAR(Assumptions!$F$146),MONTH(AD$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AE36" s="10">
-        <f>IF(AND(YEAR(AE$3)=YEAR(Assumptions!$F$142),MONTH(AE$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AE$3)=YEAR(Assumptions!$F$146),MONTH(AE$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AF36" s="10">
-        <f>IF(AND(YEAR(AF$3)=YEAR(Assumptions!$F$142),MONTH(AF$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AF$3)=YEAR(Assumptions!$F$146),MONTH(AF$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AG36" s="10">
-        <f>IF(AND(YEAR(AG$3)=YEAR(Assumptions!$F$142),MONTH(AG$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AG$3)=YEAR(Assumptions!$F$146),MONTH(AG$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AH36" s="10">
-        <f>IF(AND(YEAR(AH$3)=YEAR(Assumptions!$F$142),MONTH(AH$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AH$3)=YEAR(Assumptions!$F$146),MONTH(AH$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AI36" s="10">
-        <f>IF(AND(YEAR(AI$3)=YEAR(Assumptions!$F$142),MONTH(AI$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AI$3)=YEAR(Assumptions!$F$146),MONTH(AI$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AJ36" s="10">
-        <f>IF(AND(YEAR(AJ$3)=YEAR(Assumptions!$F$142),MONTH(AJ$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AJ$3)=YEAR(Assumptions!$F$146),MONTH(AJ$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AK36" s="10">
-        <f>IF(AND(YEAR(AK$3)=YEAR(Assumptions!$F$142),MONTH(AK$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AK$3)=YEAR(Assumptions!$F$146),MONTH(AK$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AL36" s="10">
-        <f>IF(AND(YEAR(AL$3)=YEAR(Assumptions!$F$142),MONTH(AL$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AL$3)=YEAR(Assumptions!$F$146),MONTH(AL$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AM36" s="10">
-        <f>IF(AND(YEAR(AM$3)=YEAR(Assumptions!$F$142),MONTH(AM$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AM$3)=YEAR(Assumptions!$F$146),MONTH(AM$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AN36" s="10">
-        <f>IF(AND(YEAR(AN$3)=YEAR(Assumptions!$F$142),MONTH(AN$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AN$3)=YEAR(Assumptions!$F$146),MONTH(AN$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AO36" s="10">
-        <f>IF(AND(YEAR(AO$3)=YEAR(Assumptions!$F$142),MONTH(AO$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AO$3)=YEAR(Assumptions!$F$146),MONTH(AO$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AP36" s="10">
-        <f>IF(AND(YEAR(AP$3)=YEAR(Assumptions!$F$142),MONTH(AP$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AP$3)=YEAR(Assumptions!$F$146),MONTH(AP$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AQ36" s="10">
-        <f>IF(AND(YEAR(AQ$3)=YEAR(Assumptions!$F$142),MONTH(AQ$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AQ$3)=YEAR(Assumptions!$F$146),MONTH(AQ$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AR36" s="10">
-        <f>IF(AND(YEAR(AR$3)=YEAR(Assumptions!$F$142),MONTH(AR$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AR$3)=YEAR(Assumptions!$F$146),MONTH(AR$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AS36" s="10">
-        <f>IF(AND(YEAR(AS$3)=YEAR(Assumptions!$F$142),MONTH(AS$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AS$3)=YEAR(Assumptions!$F$146),MONTH(AS$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AT36" s="10">
-        <f>IF(AND(YEAR(AT$3)=YEAR(Assumptions!$F$142),MONTH(AT$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AT$3)=YEAR(Assumptions!$F$146),MONTH(AT$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AU36" s="10">
-        <f>IF(AND(YEAR(AU$3)=YEAR(Assumptions!$F$142),MONTH(AU$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AU$3)=YEAR(Assumptions!$F$146),MONTH(AU$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AV36" s="10">
-        <f>IF(AND(YEAR(AV$3)=YEAR(Assumptions!$F$142),MONTH(AV$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AV$3)=YEAR(Assumptions!$F$146),MONTH(AV$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AW36" s="10">
-        <f>IF(AND(YEAR(AW$3)=YEAR(Assumptions!$F$142),MONTH(AW$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AW$3)=YEAR(Assumptions!$F$146),MONTH(AW$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AX36" s="10">
-        <f>IF(AND(YEAR(AX$3)=YEAR(Assumptions!$F$142),MONTH(AX$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AX$3)=YEAR(Assumptions!$F$146),MONTH(AX$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AY36" s="10">
-        <f>IF(AND(YEAR(AY$3)=YEAR(Assumptions!$F$142),MONTH(AY$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AY$3)=YEAR(Assumptions!$F$146),MONTH(AY$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="AZ36" s="10">
-        <f>IF(AND(YEAR(AZ$3)=YEAR(Assumptions!$F$142),MONTH(AZ$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(AZ$3)=YEAR(Assumptions!$F$146),MONTH(AZ$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="BA36" s="10">
-        <f>IF(AND(YEAR(BA$3)=YEAR(Assumptions!$F$142),MONTH(BA$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(BA$3)=YEAR(Assumptions!$F$146),MONTH(BA$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="BB36" s="10">
-        <f>IF(AND(YEAR(BB$3)=YEAR(Assumptions!$F$142),MONTH(BB$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(BB$3)=YEAR(Assumptions!$F$146),MONTH(BB$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="BC36" s="10">
-        <f>IF(AND(YEAR(BC$3)=YEAR(Assumptions!$F$142),MONTH(BC$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(BC$3)=YEAR(Assumptions!$F$146),MONTH(BC$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="BD36" s="10">
-        <f>IF(AND(YEAR(BD$3)=YEAR(Assumptions!$F$142),MONTH(BD$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(BD$3)=YEAR(Assumptions!$F$146),MONTH(BD$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="BE36" s="10">
-        <f>IF(AND(YEAR(BE$3)=YEAR(Assumptions!$F$142),MONTH(BE$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(BE$3)=YEAR(Assumptions!$F$146),MONTH(BE$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="BF36" s="10">
-        <f>IF(AND(YEAR(BF$3)=YEAR(Assumptions!$F$142),MONTH(BF$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(BF$3)=YEAR(Assumptions!$F$146),MONTH(BF$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="BG36" s="10">
-        <f>IF(AND(YEAR(BG$3)=YEAR(Assumptions!$F$142),MONTH(BG$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(BG$3)=YEAR(Assumptions!$F$146),MONTH(BG$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="BH36" s="10">
-        <f>IF(AND(YEAR(BH$3)=YEAR(Assumptions!$F$142),MONTH(BH$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(BH$3)=YEAR(Assumptions!$F$146),MONTH(BH$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="BI36" s="10">
-        <f>IF(AND(YEAR(BI$3)=YEAR(Assumptions!$F$142),MONTH(BI$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(BI$3)=YEAR(Assumptions!$F$146),MONTH(BI$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="BJ36" s="10">
-        <f>IF(AND(YEAR(BJ$3)=YEAR(Assumptions!$F$142),MONTH(BJ$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(BJ$3)=YEAR(Assumptions!$F$146),MONTH(BJ$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="BK36" s="10">
-        <f>IF(AND(YEAR(BK$3)=YEAR(Assumptions!$F$142),MONTH(BK$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(BK$3)=YEAR(Assumptions!$F$146),MONTH(BK$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="BL36" s="10">
-        <f>IF(AND(YEAR(BL$3)=YEAR(Assumptions!$F$142),MONTH(BL$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
+        <f>IF(AND(YEAR(BL$3)=YEAR(Assumptions!$F$146),MONTH(BL$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
         <v/>
       </c>
       <c r="BN36" s="53">
@@ -18667,243 +18782,243 @@
         </is>
       </c>
       <c r="E59" s="61">
-        <f>SUM($E$35:E35)+SUM($E$36:E36)-(IF((YEAR(E$3)*12+MONTH(E$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(E$3)*12+MONTH(E$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(E$3)*12+MONTH(E$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:E35)+SUM($E$36:E36)-(IF((YEAR(E$3)*12+MONTH(E$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(E$3)*12+MONTH(E$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(E$3)*12+MONTH(E$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="F59" s="61">
-        <f>SUM($E$35:F35)+SUM($E$36:F36)-(IF((YEAR(F$3)*12+MONTH(F$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(F$3)*12+MONTH(F$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(F$3)*12+MONTH(F$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:F35)+SUM($E$36:F36)-(IF((YEAR(F$3)*12+MONTH(F$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(F$3)*12+MONTH(F$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(F$3)*12+MONTH(F$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="G59" s="61">
-        <f>SUM($E$35:G35)+SUM($E$36:G36)-(IF((YEAR(G$3)*12+MONTH(G$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(G$3)*12+MONTH(G$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(G$3)*12+MONTH(G$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:G35)+SUM($E$36:G36)-(IF((YEAR(G$3)*12+MONTH(G$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(G$3)*12+MONTH(G$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(G$3)*12+MONTH(G$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="H59" s="61">
-        <f>SUM($E$35:H35)+SUM($E$36:H36)-(IF((YEAR(H$3)*12+MONTH(H$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(H$3)*12+MONTH(H$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(H$3)*12+MONTH(H$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:H35)+SUM($E$36:H36)-(IF((YEAR(H$3)*12+MONTH(H$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(H$3)*12+MONTH(H$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(H$3)*12+MONTH(H$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="I59" s="61">
-        <f>SUM($E$35:I35)+SUM($E$36:I36)-(IF((YEAR(I$3)*12+MONTH(I$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(I$3)*12+MONTH(I$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(I$3)*12+MONTH(I$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:I35)+SUM($E$36:I36)-(IF((YEAR(I$3)*12+MONTH(I$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(I$3)*12+MONTH(I$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(I$3)*12+MONTH(I$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="J59" s="61">
-        <f>SUM($E$35:J35)+SUM($E$36:J36)-(IF((YEAR(J$3)*12+MONTH(J$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(J$3)*12+MONTH(J$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(J$3)*12+MONTH(J$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:J35)+SUM($E$36:J36)-(IF((YEAR(J$3)*12+MONTH(J$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(J$3)*12+MONTH(J$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(J$3)*12+MONTH(J$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="K59" s="61">
-        <f>SUM($E$35:K35)+SUM($E$36:K36)-(IF((YEAR(K$3)*12+MONTH(K$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(K$3)*12+MONTH(K$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(K$3)*12+MONTH(K$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:K35)+SUM($E$36:K36)-(IF((YEAR(K$3)*12+MONTH(K$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(K$3)*12+MONTH(K$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(K$3)*12+MONTH(K$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="L59" s="61">
-        <f>SUM($E$35:L35)+SUM($E$36:L36)-(IF((YEAR(L$3)*12+MONTH(L$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(L$3)*12+MONTH(L$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(L$3)*12+MONTH(L$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:L35)+SUM($E$36:L36)-(IF((YEAR(L$3)*12+MONTH(L$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(L$3)*12+MONTH(L$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(L$3)*12+MONTH(L$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="M59" s="61">
-        <f>SUM($E$35:M35)+SUM($E$36:M36)-(IF((YEAR(M$3)*12+MONTH(M$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(M$3)*12+MONTH(M$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(M$3)*12+MONTH(M$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:M35)+SUM($E$36:M36)-(IF((YEAR(M$3)*12+MONTH(M$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(M$3)*12+MONTH(M$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(M$3)*12+MONTH(M$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="N59" s="61">
-        <f>SUM($E$35:N35)+SUM($E$36:N36)-(IF((YEAR(N$3)*12+MONTH(N$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(N$3)*12+MONTH(N$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(N$3)*12+MONTH(N$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:N35)+SUM($E$36:N36)-(IF((YEAR(N$3)*12+MONTH(N$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(N$3)*12+MONTH(N$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(N$3)*12+MONTH(N$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="O59" s="61">
-        <f>SUM($E$35:O35)+SUM($E$36:O36)-(IF((YEAR(O$3)*12+MONTH(O$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(O$3)*12+MONTH(O$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(O$3)*12+MONTH(O$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:O35)+SUM($E$36:O36)-(IF((YEAR(O$3)*12+MONTH(O$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(O$3)*12+MONTH(O$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(O$3)*12+MONTH(O$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="P59" s="61">
-        <f>SUM($E$35:P35)+SUM($E$36:P36)-(IF((YEAR(P$3)*12+MONTH(P$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(P$3)*12+MONTH(P$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(P$3)*12+MONTH(P$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:P35)+SUM($E$36:P36)-(IF((YEAR(P$3)*12+MONTH(P$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(P$3)*12+MONTH(P$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(P$3)*12+MONTH(P$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="Q59" s="61">
-        <f>SUM($E$35:Q35)+SUM($E$36:Q36)-(IF((YEAR(Q$3)*12+MONTH(Q$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(Q$3)*12+MONTH(Q$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(Q$3)*12+MONTH(Q$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:Q35)+SUM($E$36:Q36)-(IF((YEAR(Q$3)*12+MONTH(Q$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(Q$3)*12+MONTH(Q$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(Q$3)*12+MONTH(Q$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="R59" s="61">
-        <f>SUM($E$35:R35)+SUM($E$36:R36)-(IF((YEAR(R$3)*12+MONTH(R$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(R$3)*12+MONTH(R$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(R$3)*12+MONTH(R$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:R35)+SUM($E$36:R36)-(IF((YEAR(R$3)*12+MONTH(R$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(R$3)*12+MONTH(R$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(R$3)*12+MONTH(R$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="S59" s="61">
-        <f>SUM($E$35:S35)+SUM($E$36:S36)-(IF((YEAR(S$3)*12+MONTH(S$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(S$3)*12+MONTH(S$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(S$3)*12+MONTH(S$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:S35)+SUM($E$36:S36)-(IF((YEAR(S$3)*12+MONTH(S$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(S$3)*12+MONTH(S$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(S$3)*12+MONTH(S$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="T59" s="61">
-        <f>SUM($E$35:T35)+SUM($E$36:T36)-(IF((YEAR(T$3)*12+MONTH(T$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(T$3)*12+MONTH(T$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(T$3)*12+MONTH(T$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:T35)+SUM($E$36:T36)-(IF((YEAR(T$3)*12+MONTH(T$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(T$3)*12+MONTH(T$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(T$3)*12+MONTH(T$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="U59" s="61">
-        <f>SUM($E$35:U35)+SUM($E$36:U36)-(IF((YEAR(U$3)*12+MONTH(U$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(U$3)*12+MONTH(U$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(U$3)*12+MONTH(U$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:U35)+SUM($E$36:U36)-(IF((YEAR(U$3)*12+MONTH(U$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(U$3)*12+MONTH(U$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(U$3)*12+MONTH(U$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="V59" s="61">
-        <f>SUM($E$35:V35)+SUM($E$36:V36)-(IF((YEAR(V$3)*12+MONTH(V$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(V$3)*12+MONTH(V$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(V$3)*12+MONTH(V$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:V35)+SUM($E$36:V36)-(IF((YEAR(V$3)*12+MONTH(V$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(V$3)*12+MONTH(V$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(V$3)*12+MONTH(V$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="W59" s="61">
-        <f>SUM($E$35:W35)+SUM($E$36:W36)-(IF((YEAR(W$3)*12+MONTH(W$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(W$3)*12+MONTH(W$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(W$3)*12+MONTH(W$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:W35)+SUM($E$36:W36)-(IF((YEAR(W$3)*12+MONTH(W$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(W$3)*12+MONTH(W$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(W$3)*12+MONTH(W$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="X59" s="61">
-        <f>SUM($E$35:X35)+SUM($E$36:X36)-(IF((YEAR(X$3)*12+MONTH(X$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(X$3)*12+MONTH(X$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(X$3)*12+MONTH(X$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:X35)+SUM($E$36:X36)-(IF((YEAR(X$3)*12+MONTH(X$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(X$3)*12+MONTH(X$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(X$3)*12+MONTH(X$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="Y59" s="61">
-        <f>SUM($E$35:Y35)+SUM($E$36:Y36)-(IF((YEAR(Y$3)*12+MONTH(Y$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(Y$3)*12+MONTH(Y$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(Y$3)*12+MONTH(Y$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:Y35)+SUM($E$36:Y36)-(IF((YEAR(Y$3)*12+MONTH(Y$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(Y$3)*12+MONTH(Y$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(Y$3)*12+MONTH(Y$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="Z59" s="61">
-        <f>SUM($E$35:Z35)+SUM($E$36:Z36)-(IF((YEAR(Z$3)*12+MONTH(Z$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(Z$3)*12+MONTH(Z$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(Z$3)*12+MONTH(Z$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:Z35)+SUM($E$36:Z36)-(IF((YEAR(Z$3)*12+MONTH(Z$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(Z$3)*12+MONTH(Z$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(Z$3)*12+MONTH(Z$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AA59" s="61">
-        <f>SUM($E$35:AA35)+SUM($E$36:AA36)-(IF((YEAR(AA$3)*12+MONTH(AA$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AA$3)*12+MONTH(AA$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AA$3)*12+MONTH(AA$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AA35)+SUM($E$36:AA36)-(IF((YEAR(AA$3)*12+MONTH(AA$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AA$3)*12+MONTH(AA$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AA$3)*12+MONTH(AA$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AB59" s="61">
-        <f>SUM($E$35:AB35)+SUM($E$36:AB36)-(IF((YEAR(AB$3)*12+MONTH(AB$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AB$3)*12+MONTH(AB$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AB$3)*12+MONTH(AB$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AB35)+SUM($E$36:AB36)-(IF((YEAR(AB$3)*12+MONTH(AB$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AB$3)*12+MONTH(AB$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AB$3)*12+MONTH(AB$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AC59" s="61">
-        <f>SUM($E$35:AC35)+SUM($E$36:AC36)-(IF((YEAR(AC$3)*12+MONTH(AC$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AC$3)*12+MONTH(AC$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AC$3)*12+MONTH(AC$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AC35)+SUM($E$36:AC36)-(IF((YEAR(AC$3)*12+MONTH(AC$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AC$3)*12+MONTH(AC$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AC$3)*12+MONTH(AC$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AD59" s="61">
-        <f>SUM($E$35:AD35)+SUM($E$36:AD36)-(IF((YEAR(AD$3)*12+MONTH(AD$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AD$3)*12+MONTH(AD$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AD$3)*12+MONTH(AD$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AD35)+SUM($E$36:AD36)-(IF((YEAR(AD$3)*12+MONTH(AD$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AD$3)*12+MONTH(AD$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AD$3)*12+MONTH(AD$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AE59" s="61">
-        <f>SUM($E$35:AE35)+SUM($E$36:AE36)-(IF((YEAR(AE$3)*12+MONTH(AE$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AE$3)*12+MONTH(AE$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AE$3)*12+MONTH(AE$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AE35)+SUM($E$36:AE36)-(IF((YEAR(AE$3)*12+MONTH(AE$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AE$3)*12+MONTH(AE$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AE$3)*12+MONTH(AE$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AF59" s="61">
-        <f>SUM($E$35:AF35)+SUM($E$36:AF36)-(IF((YEAR(AF$3)*12+MONTH(AF$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AF$3)*12+MONTH(AF$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AF$3)*12+MONTH(AF$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AF35)+SUM($E$36:AF36)-(IF((YEAR(AF$3)*12+MONTH(AF$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AF$3)*12+MONTH(AF$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AF$3)*12+MONTH(AF$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AG59" s="61">
-        <f>SUM($E$35:AG35)+SUM($E$36:AG36)-(IF((YEAR(AG$3)*12+MONTH(AG$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AG$3)*12+MONTH(AG$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AG$3)*12+MONTH(AG$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AG35)+SUM($E$36:AG36)-(IF((YEAR(AG$3)*12+MONTH(AG$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AG$3)*12+MONTH(AG$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AG$3)*12+MONTH(AG$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AH59" s="61">
-        <f>SUM($E$35:AH35)+SUM($E$36:AH36)-(IF((YEAR(AH$3)*12+MONTH(AH$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AH$3)*12+MONTH(AH$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AH$3)*12+MONTH(AH$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AH35)+SUM($E$36:AH36)-(IF((YEAR(AH$3)*12+MONTH(AH$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AH$3)*12+MONTH(AH$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AH$3)*12+MONTH(AH$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AI59" s="61">
-        <f>SUM($E$35:AI35)+SUM($E$36:AI36)-(IF((YEAR(AI$3)*12+MONTH(AI$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AI$3)*12+MONTH(AI$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AI$3)*12+MONTH(AI$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AI35)+SUM($E$36:AI36)-(IF((YEAR(AI$3)*12+MONTH(AI$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AI$3)*12+MONTH(AI$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AI$3)*12+MONTH(AI$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AJ59" s="61">
-        <f>SUM($E$35:AJ35)+SUM($E$36:AJ36)-(IF((YEAR(AJ$3)*12+MONTH(AJ$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AJ$3)*12+MONTH(AJ$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AJ$3)*12+MONTH(AJ$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AJ35)+SUM($E$36:AJ36)-(IF((YEAR(AJ$3)*12+MONTH(AJ$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AJ$3)*12+MONTH(AJ$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AJ$3)*12+MONTH(AJ$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AK59" s="61">
-        <f>SUM($E$35:AK35)+SUM($E$36:AK36)-(IF((YEAR(AK$3)*12+MONTH(AK$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AK$3)*12+MONTH(AK$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AK$3)*12+MONTH(AK$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AK35)+SUM($E$36:AK36)-(IF((YEAR(AK$3)*12+MONTH(AK$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AK$3)*12+MONTH(AK$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AK$3)*12+MONTH(AK$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AL59" s="61">
-        <f>SUM($E$35:AL35)+SUM($E$36:AL36)-(IF((YEAR(AL$3)*12+MONTH(AL$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AL$3)*12+MONTH(AL$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AL$3)*12+MONTH(AL$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AL35)+SUM($E$36:AL36)-(IF((YEAR(AL$3)*12+MONTH(AL$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AL$3)*12+MONTH(AL$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AL$3)*12+MONTH(AL$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AM59" s="61">
-        <f>SUM($E$35:AM35)+SUM($E$36:AM36)-(IF((YEAR(AM$3)*12+MONTH(AM$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AM$3)*12+MONTH(AM$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AM$3)*12+MONTH(AM$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AM35)+SUM($E$36:AM36)-(IF((YEAR(AM$3)*12+MONTH(AM$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AM$3)*12+MONTH(AM$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AM$3)*12+MONTH(AM$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AN59" s="61">
-        <f>SUM($E$35:AN35)+SUM($E$36:AN36)-(IF((YEAR(AN$3)*12+MONTH(AN$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AN$3)*12+MONTH(AN$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AN$3)*12+MONTH(AN$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AN35)+SUM($E$36:AN36)-(IF((YEAR(AN$3)*12+MONTH(AN$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AN$3)*12+MONTH(AN$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AN$3)*12+MONTH(AN$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AO59" s="61">
-        <f>SUM($E$35:AO35)+SUM($E$36:AO36)-(IF((YEAR(AO$3)*12+MONTH(AO$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AO$3)*12+MONTH(AO$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AO$3)*12+MONTH(AO$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AO35)+SUM($E$36:AO36)-(IF((YEAR(AO$3)*12+MONTH(AO$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AO$3)*12+MONTH(AO$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AO$3)*12+MONTH(AO$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AP59" s="61">
-        <f>SUM($E$35:AP35)+SUM($E$36:AP36)-(IF((YEAR(AP$3)*12+MONTH(AP$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AP$3)*12+MONTH(AP$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AP$3)*12+MONTH(AP$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AP35)+SUM($E$36:AP36)-(IF((YEAR(AP$3)*12+MONTH(AP$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AP$3)*12+MONTH(AP$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AP$3)*12+MONTH(AP$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AQ59" s="61">
-        <f>SUM($E$35:AQ35)+SUM($E$36:AQ36)-(IF((YEAR(AQ$3)*12+MONTH(AQ$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AQ$3)*12+MONTH(AQ$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AQ$3)*12+MONTH(AQ$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AQ35)+SUM($E$36:AQ36)-(IF((YEAR(AQ$3)*12+MONTH(AQ$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AQ$3)*12+MONTH(AQ$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AQ$3)*12+MONTH(AQ$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AR59" s="61">
-        <f>SUM($E$35:AR35)+SUM($E$36:AR36)-(IF((YEAR(AR$3)*12+MONTH(AR$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AR$3)*12+MONTH(AR$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AR$3)*12+MONTH(AR$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AR35)+SUM($E$36:AR36)-(IF((YEAR(AR$3)*12+MONTH(AR$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AR$3)*12+MONTH(AR$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AR$3)*12+MONTH(AR$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AS59" s="61">
-        <f>SUM($E$35:AS35)+SUM($E$36:AS36)-(IF((YEAR(AS$3)*12+MONTH(AS$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AS$3)*12+MONTH(AS$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AS$3)*12+MONTH(AS$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AS35)+SUM($E$36:AS36)-(IF((YEAR(AS$3)*12+MONTH(AS$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AS$3)*12+MONTH(AS$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AS$3)*12+MONTH(AS$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AT59" s="61">
-        <f>SUM($E$35:AT35)+SUM($E$36:AT36)-(IF((YEAR(AT$3)*12+MONTH(AT$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AT$3)*12+MONTH(AT$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AT$3)*12+MONTH(AT$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AT35)+SUM($E$36:AT36)-(IF((YEAR(AT$3)*12+MONTH(AT$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AT$3)*12+MONTH(AT$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AT$3)*12+MONTH(AT$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AU59" s="61">
-        <f>SUM($E$35:AU35)+SUM($E$36:AU36)-(IF((YEAR(AU$3)*12+MONTH(AU$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AU$3)*12+MONTH(AU$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AU$3)*12+MONTH(AU$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AU35)+SUM($E$36:AU36)-(IF((YEAR(AU$3)*12+MONTH(AU$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AU$3)*12+MONTH(AU$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AU$3)*12+MONTH(AU$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AV59" s="61">
-        <f>SUM($E$35:AV35)+SUM($E$36:AV36)-(IF((YEAR(AV$3)*12+MONTH(AV$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AV$3)*12+MONTH(AV$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AV$3)*12+MONTH(AV$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AV35)+SUM($E$36:AV36)-(IF((YEAR(AV$3)*12+MONTH(AV$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AV$3)*12+MONTH(AV$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AV$3)*12+MONTH(AV$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AW59" s="61">
-        <f>SUM($E$35:AW35)+SUM($E$36:AW36)-(IF((YEAR(AW$3)*12+MONTH(AW$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AW$3)*12+MONTH(AW$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AW$3)*12+MONTH(AW$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AW35)+SUM($E$36:AW36)-(IF((YEAR(AW$3)*12+MONTH(AW$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AW$3)*12+MONTH(AW$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AW$3)*12+MONTH(AW$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AX59" s="61">
-        <f>SUM($E$35:AX35)+SUM($E$36:AX36)-(IF((YEAR(AX$3)*12+MONTH(AX$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AX$3)*12+MONTH(AX$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AX$3)*12+MONTH(AX$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AX35)+SUM($E$36:AX36)-(IF((YEAR(AX$3)*12+MONTH(AX$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AX$3)*12+MONTH(AX$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AX$3)*12+MONTH(AX$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AY59" s="61">
-        <f>SUM($E$35:AY35)+SUM($E$36:AY36)-(IF((YEAR(AY$3)*12+MONTH(AY$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AY$3)*12+MONTH(AY$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AY$3)*12+MONTH(AY$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AY35)+SUM($E$36:AY36)-(IF((YEAR(AY$3)*12+MONTH(AY$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AY$3)*12+MONTH(AY$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AY$3)*12+MONTH(AY$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="AZ59" s="61">
-        <f>SUM($E$35:AZ35)+SUM($E$36:AZ36)-(IF((YEAR(AZ$3)*12+MONTH(AZ$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AZ$3)*12+MONTH(AZ$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AZ$3)*12+MONTH(AZ$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:AZ35)+SUM($E$36:AZ36)-(IF((YEAR(AZ$3)*12+MONTH(AZ$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AZ$3)*12+MONTH(AZ$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AZ$3)*12+MONTH(AZ$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="BA59" s="61">
-        <f>SUM($E$35:BA35)+SUM($E$36:BA36)-(IF((YEAR(BA$3)*12+MONTH(BA$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BA$3)*12+MONTH(BA$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BA$3)*12+MONTH(BA$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:BA35)+SUM($E$36:BA36)-(IF((YEAR(BA$3)*12+MONTH(BA$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BA$3)*12+MONTH(BA$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BA$3)*12+MONTH(BA$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="BB59" s="61">
-        <f>SUM($E$35:BB35)+SUM($E$36:BB36)-(IF((YEAR(BB$3)*12+MONTH(BB$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BB$3)*12+MONTH(BB$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BB$3)*12+MONTH(BB$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:BB35)+SUM($E$36:BB36)-(IF((YEAR(BB$3)*12+MONTH(BB$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BB$3)*12+MONTH(BB$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BB$3)*12+MONTH(BB$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="BC59" s="61">
-        <f>SUM($E$35:BC35)+SUM($E$36:BC36)-(IF((YEAR(BC$3)*12+MONTH(BC$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BC$3)*12+MONTH(BC$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BC$3)*12+MONTH(BC$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:BC35)+SUM($E$36:BC36)-(IF((YEAR(BC$3)*12+MONTH(BC$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BC$3)*12+MONTH(BC$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BC$3)*12+MONTH(BC$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="BD59" s="61">
-        <f>SUM($E$35:BD35)+SUM($E$36:BD36)-(IF((YEAR(BD$3)*12+MONTH(BD$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BD$3)*12+MONTH(BD$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BD$3)*12+MONTH(BD$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:BD35)+SUM($E$36:BD36)-(IF((YEAR(BD$3)*12+MONTH(BD$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BD$3)*12+MONTH(BD$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BD$3)*12+MONTH(BD$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="BE59" s="61">
-        <f>SUM($E$35:BE35)+SUM($E$36:BE36)-(IF((YEAR(BE$3)*12+MONTH(BE$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BE$3)*12+MONTH(BE$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BE$3)*12+MONTH(BE$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:BE35)+SUM($E$36:BE36)-(IF((YEAR(BE$3)*12+MONTH(BE$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BE$3)*12+MONTH(BE$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BE$3)*12+MONTH(BE$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="BF59" s="61">
-        <f>SUM($E$35:BF35)+SUM($E$36:BF36)-(IF((YEAR(BF$3)*12+MONTH(BF$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BF$3)*12+MONTH(BF$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BF$3)*12+MONTH(BF$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:BF35)+SUM($E$36:BF36)-(IF((YEAR(BF$3)*12+MONTH(BF$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BF$3)*12+MONTH(BF$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BF$3)*12+MONTH(BF$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="BG59" s="61">
-        <f>SUM($E$35:BG35)+SUM($E$36:BG36)-(IF((YEAR(BG$3)*12+MONTH(BG$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BG$3)*12+MONTH(BG$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BG$3)*12+MONTH(BG$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:BG35)+SUM($E$36:BG36)-(IF((YEAR(BG$3)*12+MONTH(BG$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BG$3)*12+MONTH(BG$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BG$3)*12+MONTH(BG$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="BH59" s="61">
-        <f>SUM($E$35:BH35)+SUM($E$36:BH36)-(IF((YEAR(BH$3)*12+MONTH(BH$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BH$3)*12+MONTH(BH$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BH$3)*12+MONTH(BH$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:BH35)+SUM($E$36:BH36)-(IF((YEAR(BH$3)*12+MONTH(BH$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BH$3)*12+MONTH(BH$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BH$3)*12+MONTH(BH$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="BI59" s="61">
-        <f>SUM($E$35:BI35)+SUM($E$36:BI36)-(IF((YEAR(BI$3)*12+MONTH(BI$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BI$3)*12+MONTH(BI$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BI$3)*12+MONTH(BI$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:BI35)+SUM($E$36:BI36)-(IF((YEAR(BI$3)*12+MONTH(BI$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BI$3)*12+MONTH(BI$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BI$3)*12+MONTH(BI$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="BJ59" s="61">
-        <f>SUM($E$35:BJ35)+SUM($E$36:BJ36)-(IF((YEAR(BJ$3)*12+MONTH(BJ$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BJ$3)*12+MONTH(BJ$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BJ$3)*12+MONTH(BJ$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:BJ35)+SUM($E$36:BJ36)-(IF((YEAR(BJ$3)*12+MONTH(BJ$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BJ$3)*12+MONTH(BJ$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BJ$3)*12+MONTH(BJ$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="BK59" s="61">
-        <f>SUM($E$35:BK35)+SUM($E$36:BK36)-(IF((YEAR(BK$3)*12+MONTH(BK$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BK$3)*12+MONTH(BK$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BK$3)*12+MONTH(BK$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:BK35)+SUM($E$36:BK36)-(IF((YEAR(BK$3)*12+MONTH(BK$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BK$3)*12+MONTH(BK$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BK$3)*12+MONTH(BK$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="BL59" s="61">
-        <f>SUM($E$35:BL35)+SUM($E$36:BL36)-(IF((YEAR(BL$3)*12+MONTH(BL$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BL$3)*12+MONTH(BL$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BL$3)*12+MONTH(BL$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
+        <f>SUM($E$35:BL35)+SUM($E$36:BL36)-(IF((YEAR(BL$3)*12+MONTH(BL$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BL$3)*12+MONTH(BL$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BL$3)*12+MONTH(BL$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
         <v/>
       </c>
       <c r="BN59" s="62">
@@ -30295,7 +30410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:BT21"/>
+  <dimension ref="B1:BT22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -32113,6 +32228,283 @@
         <v/>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Units built on our own lines</t>
+        </is>
+      </c>
+      <c r="C11" s="52" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="E11" s="9">
+        <f>MIN('Revenue Forecast'!E34,'Revenue Forecast'!E30)</f>
+        <v/>
+      </c>
+      <c r="F11" s="9">
+        <f>MIN('Revenue Forecast'!F34,'Revenue Forecast'!F30)</f>
+        <v/>
+      </c>
+      <c r="G11" s="9">
+        <f>MIN('Revenue Forecast'!G34,'Revenue Forecast'!G30)</f>
+        <v/>
+      </c>
+      <c r="H11" s="9">
+        <f>MIN('Revenue Forecast'!H34,'Revenue Forecast'!H30)</f>
+        <v/>
+      </c>
+      <c r="I11" s="9">
+        <f>MIN('Revenue Forecast'!I34,'Revenue Forecast'!I30)</f>
+        <v/>
+      </c>
+      <c r="J11" s="9">
+        <f>MIN('Revenue Forecast'!J34,'Revenue Forecast'!J30)</f>
+        <v/>
+      </c>
+      <c r="K11" s="9">
+        <f>MIN('Revenue Forecast'!K34,'Revenue Forecast'!K30)</f>
+        <v/>
+      </c>
+      <c r="L11" s="9">
+        <f>MIN('Revenue Forecast'!L34,'Revenue Forecast'!L30)</f>
+        <v/>
+      </c>
+      <c r="M11" s="9">
+        <f>MIN('Revenue Forecast'!M34,'Revenue Forecast'!M30)</f>
+        <v/>
+      </c>
+      <c r="N11" s="9">
+        <f>MIN('Revenue Forecast'!N34,'Revenue Forecast'!N30)</f>
+        <v/>
+      </c>
+      <c r="O11" s="9">
+        <f>MIN('Revenue Forecast'!O34,'Revenue Forecast'!O30)</f>
+        <v/>
+      </c>
+      <c r="P11" s="9">
+        <f>MIN('Revenue Forecast'!P34,'Revenue Forecast'!P30)</f>
+        <v/>
+      </c>
+      <c r="Q11" s="9">
+        <f>MIN('Revenue Forecast'!Q34,'Revenue Forecast'!Q30)</f>
+        <v/>
+      </c>
+      <c r="R11" s="9">
+        <f>MIN('Revenue Forecast'!R34,'Revenue Forecast'!R30)</f>
+        <v/>
+      </c>
+      <c r="S11" s="9">
+        <f>MIN('Revenue Forecast'!S34,'Revenue Forecast'!S30)</f>
+        <v/>
+      </c>
+      <c r="T11" s="9">
+        <f>MIN('Revenue Forecast'!T34,'Revenue Forecast'!T30)</f>
+        <v/>
+      </c>
+      <c r="U11" s="9">
+        <f>MIN('Revenue Forecast'!U34,'Revenue Forecast'!U30)</f>
+        <v/>
+      </c>
+      <c r="V11" s="9">
+        <f>MIN('Revenue Forecast'!V34,'Revenue Forecast'!V30)</f>
+        <v/>
+      </c>
+      <c r="W11" s="9">
+        <f>MIN('Revenue Forecast'!W34,'Revenue Forecast'!W30)</f>
+        <v/>
+      </c>
+      <c r="X11" s="9">
+        <f>MIN('Revenue Forecast'!X34,'Revenue Forecast'!X30)</f>
+        <v/>
+      </c>
+      <c r="Y11" s="9">
+        <f>MIN('Revenue Forecast'!Y34,'Revenue Forecast'!Y30)</f>
+        <v/>
+      </c>
+      <c r="Z11" s="9">
+        <f>MIN('Revenue Forecast'!Z34,'Revenue Forecast'!Z30)</f>
+        <v/>
+      </c>
+      <c r="AA11" s="9">
+        <f>MIN('Revenue Forecast'!AA34,'Revenue Forecast'!AA30)</f>
+        <v/>
+      </c>
+      <c r="AB11" s="9">
+        <f>MIN('Revenue Forecast'!AB34,'Revenue Forecast'!AB30)</f>
+        <v/>
+      </c>
+      <c r="AC11" s="9">
+        <f>MIN('Revenue Forecast'!AC34,'Revenue Forecast'!AC30)</f>
+        <v/>
+      </c>
+      <c r="AD11" s="9">
+        <f>MIN('Revenue Forecast'!AD34,'Revenue Forecast'!AD30)</f>
+        <v/>
+      </c>
+      <c r="AE11" s="9">
+        <f>MIN('Revenue Forecast'!AE34,'Revenue Forecast'!AE30)</f>
+        <v/>
+      </c>
+      <c r="AF11" s="9">
+        <f>MIN('Revenue Forecast'!AF34,'Revenue Forecast'!AF30)</f>
+        <v/>
+      </c>
+      <c r="AG11" s="9">
+        <f>MIN('Revenue Forecast'!AG34,'Revenue Forecast'!AG30)</f>
+        <v/>
+      </c>
+      <c r="AH11" s="9">
+        <f>MIN('Revenue Forecast'!AH34,'Revenue Forecast'!AH30)</f>
+        <v/>
+      </c>
+      <c r="AI11" s="9">
+        <f>MIN('Revenue Forecast'!AI34,'Revenue Forecast'!AI30)</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="9">
+        <f>MIN('Revenue Forecast'!AJ34,'Revenue Forecast'!AJ30)</f>
+        <v/>
+      </c>
+      <c r="AK11" s="9">
+        <f>MIN('Revenue Forecast'!AK34,'Revenue Forecast'!AK30)</f>
+        <v/>
+      </c>
+      <c r="AL11" s="9">
+        <f>MIN('Revenue Forecast'!AL34,'Revenue Forecast'!AL30)</f>
+        <v/>
+      </c>
+      <c r="AM11" s="9">
+        <f>MIN('Revenue Forecast'!AM34,'Revenue Forecast'!AM30)</f>
+        <v/>
+      </c>
+      <c r="AN11" s="9">
+        <f>MIN('Revenue Forecast'!AN34,'Revenue Forecast'!AN30)</f>
+        <v/>
+      </c>
+      <c r="AO11" s="9">
+        <f>MIN('Revenue Forecast'!AO34,'Revenue Forecast'!AO30)</f>
+        <v/>
+      </c>
+      <c r="AP11" s="9">
+        <f>MIN('Revenue Forecast'!AP34,'Revenue Forecast'!AP30)</f>
+        <v/>
+      </c>
+      <c r="AQ11" s="9">
+        <f>MIN('Revenue Forecast'!AQ34,'Revenue Forecast'!AQ30)</f>
+        <v/>
+      </c>
+      <c r="AR11" s="9">
+        <f>MIN('Revenue Forecast'!AR34,'Revenue Forecast'!AR30)</f>
+        <v/>
+      </c>
+      <c r="AS11" s="9">
+        <f>MIN('Revenue Forecast'!AS34,'Revenue Forecast'!AS30)</f>
+        <v/>
+      </c>
+      <c r="AT11" s="9">
+        <f>MIN('Revenue Forecast'!AT34,'Revenue Forecast'!AT30)</f>
+        <v/>
+      </c>
+      <c r="AU11" s="9">
+        <f>MIN('Revenue Forecast'!AU34,'Revenue Forecast'!AU30)</f>
+        <v/>
+      </c>
+      <c r="AV11" s="9">
+        <f>MIN('Revenue Forecast'!AV34,'Revenue Forecast'!AV30)</f>
+        <v/>
+      </c>
+      <c r="AW11" s="9">
+        <f>MIN('Revenue Forecast'!AW34,'Revenue Forecast'!AW30)</f>
+        <v/>
+      </c>
+      <c r="AX11" s="9">
+        <f>MIN('Revenue Forecast'!AX34,'Revenue Forecast'!AX30)</f>
+        <v/>
+      </c>
+      <c r="AY11" s="9">
+        <f>MIN('Revenue Forecast'!AY34,'Revenue Forecast'!AY30)</f>
+        <v/>
+      </c>
+      <c r="AZ11" s="9">
+        <f>MIN('Revenue Forecast'!AZ34,'Revenue Forecast'!AZ30)</f>
+        <v/>
+      </c>
+      <c r="BA11" s="9">
+        <f>MIN('Revenue Forecast'!BA34,'Revenue Forecast'!BA30)</f>
+        <v/>
+      </c>
+      <c r="BB11" s="9">
+        <f>MIN('Revenue Forecast'!BB34,'Revenue Forecast'!BB30)</f>
+        <v/>
+      </c>
+      <c r="BC11" s="9">
+        <f>MIN('Revenue Forecast'!BC34,'Revenue Forecast'!BC30)</f>
+        <v/>
+      </c>
+      <c r="BD11" s="9">
+        <f>MIN('Revenue Forecast'!BD34,'Revenue Forecast'!BD30)</f>
+        <v/>
+      </c>
+      <c r="BE11" s="9">
+        <f>MIN('Revenue Forecast'!BE34,'Revenue Forecast'!BE30)</f>
+        <v/>
+      </c>
+      <c r="BF11" s="9">
+        <f>MIN('Revenue Forecast'!BF34,'Revenue Forecast'!BF30)</f>
+        <v/>
+      </c>
+      <c r="BG11" s="9">
+        <f>MIN('Revenue Forecast'!BG34,'Revenue Forecast'!BG30)</f>
+        <v/>
+      </c>
+      <c r="BH11" s="9">
+        <f>MIN('Revenue Forecast'!BH34,'Revenue Forecast'!BH30)</f>
+        <v/>
+      </c>
+      <c r="BI11" s="9">
+        <f>MIN('Revenue Forecast'!BI34,'Revenue Forecast'!BI30)</f>
+        <v/>
+      </c>
+      <c r="BJ11" s="9">
+        <f>MIN('Revenue Forecast'!BJ34,'Revenue Forecast'!BJ30)</f>
+        <v/>
+      </c>
+      <c r="BK11" s="9">
+        <f>MIN('Revenue Forecast'!BK34,'Revenue Forecast'!BK30)</f>
+        <v/>
+      </c>
+      <c r="BL11" s="9">
+        <f>MIN('Revenue Forecast'!BL34,'Revenue Forecast'!BL30)</f>
+        <v/>
+      </c>
+      <c r="BN11" s="63">
+        <f>SUM(E11:P11)</f>
+        <v/>
+      </c>
+      <c r="BO11" s="63">
+        <f>SUM(Q11:AB11)</f>
+        <v/>
+      </c>
+      <c r="BP11" s="63">
+        <f>SUM(AC11:AN11)</f>
+        <v/>
+      </c>
+      <c r="BQ11" s="63">
+        <f>SUM(AO11:AZ11)</f>
+        <v/>
+      </c>
+      <c r="BR11" s="63">
+        <f>SUM(BA11:BL11)</f>
+        <v/>
+      </c>
+      <c r="BT11" s="28" t="inlineStr">
+        <is>
+          <t>our lines are filled first, the assembly partner takes the rest</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="B12" s="49" t="inlineStr">
         <is>
@@ -33842,552 +34234,829 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="49" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>In-house assembly saving</t>
+        </is>
+      </c>
+      <c r="C19" s="52" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E19" s="10">
+        <f>-E11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="F19" s="10">
+        <f>-F11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="G19" s="10">
+        <f>-G11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="H19" s="10">
+        <f>-H11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="I19" s="10">
+        <f>-I11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="J19" s="10">
+        <f>-J11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="K19" s="10">
+        <f>-K11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="L19" s="10">
+        <f>-L11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="M19" s="10">
+        <f>-M11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="N19" s="10">
+        <f>-N11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="O19" s="10">
+        <f>-O11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="P19" s="10">
+        <f>-P11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="Q19" s="10">
+        <f>-Q11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="R19" s="10">
+        <f>-R11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="S19" s="10">
+        <f>-S11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="T19" s="10">
+        <f>-T11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="U19" s="10">
+        <f>-U11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="V19" s="10">
+        <f>-V11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="W19" s="10">
+        <f>-W11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="X19" s="10">
+        <f>-X11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="Y19" s="10">
+        <f>-Y11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="Z19" s="10">
+        <f>-Z11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AA19" s="10">
+        <f>-AA11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AB19" s="10">
+        <f>-AB11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AC19" s="10">
+        <f>-AC11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AD19" s="10">
+        <f>-AD11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AE19" s="10">
+        <f>-AE11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AF19" s="10">
+        <f>-AF11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AG19" s="10">
+        <f>-AG11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AH19" s="10">
+        <f>-AH11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AI19" s="10">
+        <f>-AI11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AJ19" s="10">
+        <f>-AJ11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AK19" s="10">
+        <f>-AK11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AL19" s="10">
+        <f>-AL11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AM19" s="10">
+        <f>-AM11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AN19" s="10">
+        <f>-AN11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AO19" s="10">
+        <f>-AO11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AP19" s="10">
+        <f>-AP11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AQ19" s="10">
+        <f>-AQ11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AR19" s="10">
+        <f>-AR11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AS19" s="10">
+        <f>-AS11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AT19" s="10">
+        <f>-AT11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AU19" s="10">
+        <f>-AU11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AV19" s="10">
+        <f>-AV11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AW19" s="10">
+        <f>-AW11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AX19" s="10">
+        <f>-AX11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AY19" s="10">
+        <f>-AY11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="AZ19" s="10">
+        <f>-AZ11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="BA19" s="10">
+        <f>-BA11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="BB19" s="10">
+        <f>-BB11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="BC19" s="10">
+        <f>-BC11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="BD19" s="10">
+        <f>-BD11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="BE19" s="10">
+        <f>-BE11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="BF19" s="10">
+        <f>-BF11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="BG19" s="10">
+        <f>-BG11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="BH19" s="10">
+        <f>-BH11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="BI19" s="10">
+        <f>-BI11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="BJ19" s="10">
+        <f>-BJ11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="BK19" s="10">
+        <f>-BK11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="BL19" s="10">
+        <f>-BL11*Assumptions!$F$126</f>
+        <v/>
+      </c>
+      <c r="BN19" s="53">
+        <f>SUM(E19:P19)</f>
+        <v/>
+      </c>
+      <c r="BO19" s="53">
+        <f>SUM(Q19:AB19)</f>
+        <v/>
+      </c>
+      <c r="BP19" s="53">
+        <f>SUM(AC19:AN19)</f>
+        <v/>
+      </c>
+      <c r="BQ19" s="53">
+        <f>SUM(AO19:AZ19)</f>
+        <v/>
+      </c>
+      <c r="BR19" s="53">
+        <f>SUM(BA19:BL19)</f>
+        <v/>
+      </c>
+      <c r="BT19" s="28" t="inlineStr">
+        <is>
+          <t>units built on our own lines do not pay the assembly partner; their operators and facility are in OPEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="49" t="inlineStr">
         <is>
           <t>Total cost of goods sold</t>
         </is>
       </c>
-      <c r="C19" s="54" t="inlineStr">
+      <c r="C20" s="54" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="55">
-        <f>SUM(E13:E18)</f>
-        <v/>
-      </c>
-      <c r="F19" s="55">
-        <f>SUM(F13:F18)</f>
-        <v/>
-      </c>
-      <c r="G19" s="55">
-        <f>SUM(G13:G18)</f>
-        <v/>
-      </c>
-      <c r="H19" s="55">
-        <f>SUM(H13:H18)</f>
-        <v/>
-      </c>
-      <c r="I19" s="55">
-        <f>SUM(I13:I18)</f>
-        <v/>
-      </c>
-      <c r="J19" s="55">
-        <f>SUM(J13:J18)</f>
-        <v/>
-      </c>
-      <c r="K19" s="55">
-        <f>SUM(K13:K18)</f>
-        <v/>
-      </c>
-      <c r="L19" s="55">
-        <f>SUM(L13:L18)</f>
-        <v/>
-      </c>
-      <c r="M19" s="55">
-        <f>SUM(M13:M18)</f>
-        <v/>
-      </c>
-      <c r="N19" s="55">
-        <f>SUM(N13:N18)</f>
-        <v/>
-      </c>
-      <c r="O19" s="55">
-        <f>SUM(O13:O18)</f>
-        <v/>
-      </c>
-      <c r="P19" s="55">
-        <f>SUM(P13:P18)</f>
-        <v/>
-      </c>
-      <c r="Q19" s="55">
-        <f>SUM(Q13:Q18)</f>
-        <v/>
-      </c>
-      <c r="R19" s="55">
-        <f>SUM(R13:R18)</f>
-        <v/>
-      </c>
-      <c r="S19" s="55">
-        <f>SUM(S13:S18)</f>
-        <v/>
-      </c>
-      <c r="T19" s="55">
-        <f>SUM(T13:T18)</f>
-        <v/>
-      </c>
-      <c r="U19" s="55">
-        <f>SUM(U13:U18)</f>
-        <v/>
-      </c>
-      <c r="V19" s="55">
-        <f>SUM(V13:V18)</f>
-        <v/>
-      </c>
-      <c r="W19" s="55">
-        <f>SUM(W13:W18)</f>
-        <v/>
-      </c>
-      <c r="X19" s="55">
-        <f>SUM(X13:X18)</f>
-        <v/>
-      </c>
-      <c r="Y19" s="55">
-        <f>SUM(Y13:Y18)</f>
-        <v/>
-      </c>
-      <c r="Z19" s="55">
-        <f>SUM(Z13:Z18)</f>
-        <v/>
-      </c>
-      <c r="AA19" s="55">
-        <f>SUM(AA13:AA18)</f>
-        <v/>
-      </c>
-      <c r="AB19" s="55">
-        <f>SUM(AB13:AB18)</f>
-        <v/>
-      </c>
-      <c r="AC19" s="55">
-        <f>SUM(AC13:AC18)</f>
-        <v/>
-      </c>
-      <c r="AD19" s="55">
-        <f>SUM(AD13:AD18)</f>
-        <v/>
-      </c>
-      <c r="AE19" s="55">
-        <f>SUM(AE13:AE18)</f>
-        <v/>
-      </c>
-      <c r="AF19" s="55">
-        <f>SUM(AF13:AF18)</f>
-        <v/>
-      </c>
-      <c r="AG19" s="55">
-        <f>SUM(AG13:AG18)</f>
-        <v/>
-      </c>
-      <c r="AH19" s="55">
-        <f>SUM(AH13:AH18)</f>
-        <v/>
-      </c>
-      <c r="AI19" s="55">
-        <f>SUM(AI13:AI18)</f>
-        <v/>
-      </c>
-      <c r="AJ19" s="55">
-        <f>SUM(AJ13:AJ18)</f>
-        <v/>
-      </c>
-      <c r="AK19" s="55">
-        <f>SUM(AK13:AK18)</f>
-        <v/>
-      </c>
-      <c r="AL19" s="55">
-        <f>SUM(AL13:AL18)</f>
-        <v/>
-      </c>
-      <c r="AM19" s="55">
-        <f>SUM(AM13:AM18)</f>
-        <v/>
-      </c>
-      <c r="AN19" s="55">
-        <f>SUM(AN13:AN18)</f>
-        <v/>
-      </c>
-      <c r="AO19" s="55">
-        <f>SUM(AO13:AO18)</f>
-        <v/>
-      </c>
-      <c r="AP19" s="55">
-        <f>SUM(AP13:AP18)</f>
-        <v/>
-      </c>
-      <c r="AQ19" s="55">
-        <f>SUM(AQ13:AQ18)</f>
-        <v/>
-      </c>
-      <c r="AR19" s="55">
-        <f>SUM(AR13:AR18)</f>
-        <v/>
-      </c>
-      <c r="AS19" s="55">
-        <f>SUM(AS13:AS18)</f>
-        <v/>
-      </c>
-      <c r="AT19" s="55">
-        <f>SUM(AT13:AT18)</f>
-        <v/>
-      </c>
-      <c r="AU19" s="55">
-        <f>SUM(AU13:AU18)</f>
-        <v/>
-      </c>
-      <c r="AV19" s="55">
-        <f>SUM(AV13:AV18)</f>
-        <v/>
-      </c>
-      <c r="AW19" s="55">
-        <f>SUM(AW13:AW18)</f>
-        <v/>
-      </c>
-      <c r="AX19" s="55">
-        <f>SUM(AX13:AX18)</f>
-        <v/>
-      </c>
-      <c r="AY19" s="55">
-        <f>SUM(AY13:AY18)</f>
-        <v/>
-      </c>
-      <c r="AZ19" s="55">
-        <f>SUM(AZ13:AZ18)</f>
-        <v/>
-      </c>
-      <c r="BA19" s="55">
-        <f>SUM(BA13:BA18)</f>
-        <v/>
-      </c>
-      <c r="BB19" s="55">
-        <f>SUM(BB13:BB18)</f>
-        <v/>
-      </c>
-      <c r="BC19" s="55">
-        <f>SUM(BC13:BC18)</f>
-        <v/>
-      </c>
-      <c r="BD19" s="55">
-        <f>SUM(BD13:BD18)</f>
-        <v/>
-      </c>
-      <c r="BE19" s="55">
-        <f>SUM(BE13:BE18)</f>
-        <v/>
-      </c>
-      <c r="BF19" s="55">
-        <f>SUM(BF13:BF18)</f>
-        <v/>
-      </c>
-      <c r="BG19" s="55">
-        <f>SUM(BG13:BG18)</f>
-        <v/>
-      </c>
-      <c r="BH19" s="55">
-        <f>SUM(BH13:BH18)</f>
-        <v/>
-      </c>
-      <c r="BI19" s="55">
-        <f>SUM(BI13:BI18)</f>
-        <v/>
-      </c>
-      <c r="BJ19" s="55">
-        <f>SUM(BJ13:BJ18)</f>
-        <v/>
-      </c>
-      <c r="BK19" s="55">
-        <f>SUM(BK13:BK18)</f>
-        <v/>
-      </c>
-      <c r="BL19" s="55">
-        <f>SUM(BL13:BL18)</f>
-        <v/>
-      </c>
-      <c r="BM19" s="2" t="n"/>
-      <c r="BN19" s="55">
-        <f>SUM(E19:P19)</f>
-        <v/>
-      </c>
-      <c r="BO19" s="55">
-        <f>SUM(Q19:AB19)</f>
-        <v/>
-      </c>
-      <c r="BP19" s="55">
-        <f>SUM(AC19:AN19)</f>
-        <v/>
-      </c>
-      <c r="BQ19" s="55">
-        <f>SUM(AO19:AZ19)</f>
-        <v/>
-      </c>
-      <c r="BR19" s="55">
-        <f>SUM(BA19:BL19)</f>
-        <v/>
-      </c>
-      <c r="BS19" s="2" t="n"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="56" t="inlineStr">
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="55">
+        <f>SUM(E13:E19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="55">
+        <f>SUM(F13:F19)</f>
+        <v/>
+      </c>
+      <c r="G20" s="55">
+        <f>SUM(G13:G19)</f>
+        <v/>
+      </c>
+      <c r="H20" s="55">
+        <f>SUM(H13:H19)</f>
+        <v/>
+      </c>
+      <c r="I20" s="55">
+        <f>SUM(I13:I19)</f>
+        <v/>
+      </c>
+      <c r="J20" s="55">
+        <f>SUM(J13:J19)</f>
+        <v/>
+      </c>
+      <c r="K20" s="55">
+        <f>SUM(K13:K19)</f>
+        <v/>
+      </c>
+      <c r="L20" s="55">
+        <f>SUM(L13:L19)</f>
+        <v/>
+      </c>
+      <c r="M20" s="55">
+        <f>SUM(M13:M19)</f>
+        <v/>
+      </c>
+      <c r="N20" s="55">
+        <f>SUM(N13:N19)</f>
+        <v/>
+      </c>
+      <c r="O20" s="55">
+        <f>SUM(O13:O19)</f>
+        <v/>
+      </c>
+      <c r="P20" s="55">
+        <f>SUM(P13:P19)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="55">
+        <f>SUM(Q13:Q19)</f>
+        <v/>
+      </c>
+      <c r="R20" s="55">
+        <f>SUM(R13:R19)</f>
+        <v/>
+      </c>
+      <c r="S20" s="55">
+        <f>SUM(S13:S19)</f>
+        <v/>
+      </c>
+      <c r="T20" s="55">
+        <f>SUM(T13:T19)</f>
+        <v/>
+      </c>
+      <c r="U20" s="55">
+        <f>SUM(U13:U19)</f>
+        <v/>
+      </c>
+      <c r="V20" s="55">
+        <f>SUM(V13:V19)</f>
+        <v/>
+      </c>
+      <c r="W20" s="55">
+        <f>SUM(W13:W19)</f>
+        <v/>
+      </c>
+      <c r="X20" s="55">
+        <f>SUM(X13:X19)</f>
+        <v/>
+      </c>
+      <c r="Y20" s="55">
+        <f>SUM(Y13:Y19)</f>
+        <v/>
+      </c>
+      <c r="Z20" s="55">
+        <f>SUM(Z13:Z19)</f>
+        <v/>
+      </c>
+      <c r="AA20" s="55">
+        <f>SUM(AA13:AA19)</f>
+        <v/>
+      </c>
+      <c r="AB20" s="55">
+        <f>SUM(AB13:AB19)</f>
+        <v/>
+      </c>
+      <c r="AC20" s="55">
+        <f>SUM(AC13:AC19)</f>
+        <v/>
+      </c>
+      <c r="AD20" s="55">
+        <f>SUM(AD13:AD19)</f>
+        <v/>
+      </c>
+      <c r="AE20" s="55">
+        <f>SUM(AE13:AE19)</f>
+        <v/>
+      </c>
+      <c r="AF20" s="55">
+        <f>SUM(AF13:AF19)</f>
+        <v/>
+      </c>
+      <c r="AG20" s="55">
+        <f>SUM(AG13:AG19)</f>
+        <v/>
+      </c>
+      <c r="AH20" s="55">
+        <f>SUM(AH13:AH19)</f>
+        <v/>
+      </c>
+      <c r="AI20" s="55">
+        <f>SUM(AI13:AI19)</f>
+        <v/>
+      </c>
+      <c r="AJ20" s="55">
+        <f>SUM(AJ13:AJ19)</f>
+        <v/>
+      </c>
+      <c r="AK20" s="55">
+        <f>SUM(AK13:AK19)</f>
+        <v/>
+      </c>
+      <c r="AL20" s="55">
+        <f>SUM(AL13:AL19)</f>
+        <v/>
+      </c>
+      <c r="AM20" s="55">
+        <f>SUM(AM13:AM19)</f>
+        <v/>
+      </c>
+      <c r="AN20" s="55">
+        <f>SUM(AN13:AN19)</f>
+        <v/>
+      </c>
+      <c r="AO20" s="55">
+        <f>SUM(AO13:AO19)</f>
+        <v/>
+      </c>
+      <c r="AP20" s="55">
+        <f>SUM(AP13:AP19)</f>
+        <v/>
+      </c>
+      <c r="AQ20" s="55">
+        <f>SUM(AQ13:AQ19)</f>
+        <v/>
+      </c>
+      <c r="AR20" s="55">
+        <f>SUM(AR13:AR19)</f>
+        <v/>
+      </c>
+      <c r="AS20" s="55">
+        <f>SUM(AS13:AS19)</f>
+        <v/>
+      </c>
+      <c r="AT20" s="55">
+        <f>SUM(AT13:AT19)</f>
+        <v/>
+      </c>
+      <c r="AU20" s="55">
+        <f>SUM(AU13:AU19)</f>
+        <v/>
+      </c>
+      <c r="AV20" s="55">
+        <f>SUM(AV13:AV19)</f>
+        <v/>
+      </c>
+      <c r="AW20" s="55">
+        <f>SUM(AW13:AW19)</f>
+        <v/>
+      </c>
+      <c r="AX20" s="55">
+        <f>SUM(AX13:AX19)</f>
+        <v/>
+      </c>
+      <c r="AY20" s="55">
+        <f>SUM(AY13:AY19)</f>
+        <v/>
+      </c>
+      <c r="AZ20" s="55">
+        <f>SUM(AZ13:AZ19)</f>
+        <v/>
+      </c>
+      <c r="BA20" s="55">
+        <f>SUM(BA13:BA19)</f>
+        <v/>
+      </c>
+      <c r="BB20" s="55">
+        <f>SUM(BB13:BB19)</f>
+        <v/>
+      </c>
+      <c r="BC20" s="55">
+        <f>SUM(BC13:BC19)</f>
+        <v/>
+      </c>
+      <c r="BD20" s="55">
+        <f>SUM(BD13:BD19)</f>
+        <v/>
+      </c>
+      <c r="BE20" s="55">
+        <f>SUM(BE13:BE19)</f>
+        <v/>
+      </c>
+      <c r="BF20" s="55">
+        <f>SUM(BF13:BF19)</f>
+        <v/>
+      </c>
+      <c r="BG20" s="55">
+        <f>SUM(BG13:BG19)</f>
+        <v/>
+      </c>
+      <c r="BH20" s="55">
+        <f>SUM(BH13:BH19)</f>
+        <v/>
+      </c>
+      <c r="BI20" s="55">
+        <f>SUM(BI13:BI19)</f>
+        <v/>
+      </c>
+      <c r="BJ20" s="55">
+        <f>SUM(BJ13:BJ19)</f>
+        <v/>
+      </c>
+      <c r="BK20" s="55">
+        <f>SUM(BK13:BK19)</f>
+        <v/>
+      </c>
+      <c r="BL20" s="55">
+        <f>SUM(BL13:BL19)</f>
+        <v/>
+      </c>
+      <c r="BM20" s="2" t="n"/>
+      <c r="BN20" s="55">
+        <f>SUM(E20:P20)</f>
+        <v/>
+      </c>
+      <c r="BO20" s="55">
+        <f>SUM(Q20:AB20)</f>
+        <v/>
+      </c>
+      <c r="BP20" s="55">
+        <f>SUM(AC20:AN20)</f>
+        <v/>
+      </c>
+      <c r="BQ20" s="55">
+        <f>SUM(AO20:AZ20)</f>
+        <v/>
+      </c>
+      <c r="BR20" s="55">
+        <f>SUM(BA20:BL20)</f>
+        <v/>
+      </c>
+      <c r="BS20" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="56" t="inlineStr">
         <is>
           <t>Gross profit per unit</t>
         </is>
       </c>
-      <c r="C21" s="52" t="inlineStr">
+      <c r="C22" s="52" t="inlineStr">
         <is>
           <t>EUR/unit</t>
         </is>
       </c>
-      <c r="E21" s="72">
-        <f>IFERROR(('Revenue Forecast'!E50-'Revenue Forecast'!E49-E19)/'Revenue Forecast'!E34,0)</f>
-        <v/>
-      </c>
-      <c r="F21" s="72">
-        <f>IFERROR(('Revenue Forecast'!F50-'Revenue Forecast'!F49-F19)/'Revenue Forecast'!F34,0)</f>
-        <v/>
-      </c>
-      <c r="G21" s="72">
-        <f>IFERROR(('Revenue Forecast'!G50-'Revenue Forecast'!G49-G19)/'Revenue Forecast'!G34,0)</f>
-        <v/>
-      </c>
-      <c r="H21" s="72">
-        <f>IFERROR(('Revenue Forecast'!H50-'Revenue Forecast'!H49-H19)/'Revenue Forecast'!H34,0)</f>
-        <v/>
-      </c>
-      <c r="I21" s="72">
-        <f>IFERROR(('Revenue Forecast'!I50-'Revenue Forecast'!I49-I19)/'Revenue Forecast'!I34,0)</f>
-        <v/>
-      </c>
-      <c r="J21" s="72">
-        <f>IFERROR(('Revenue Forecast'!J50-'Revenue Forecast'!J49-J19)/'Revenue Forecast'!J34,0)</f>
-        <v/>
-      </c>
-      <c r="K21" s="72">
-        <f>IFERROR(('Revenue Forecast'!K50-'Revenue Forecast'!K49-K19)/'Revenue Forecast'!K34,0)</f>
-        <v/>
-      </c>
-      <c r="L21" s="72">
-        <f>IFERROR(('Revenue Forecast'!L50-'Revenue Forecast'!L49-L19)/'Revenue Forecast'!L34,0)</f>
-        <v/>
-      </c>
-      <c r="M21" s="72">
-        <f>IFERROR(('Revenue Forecast'!M50-'Revenue Forecast'!M49-M19)/'Revenue Forecast'!M34,0)</f>
-        <v/>
-      </c>
-      <c r="N21" s="72">
-        <f>IFERROR(('Revenue Forecast'!N50-'Revenue Forecast'!N49-N19)/'Revenue Forecast'!N34,0)</f>
-        <v/>
-      </c>
-      <c r="O21" s="72">
-        <f>IFERROR(('Revenue Forecast'!O50-'Revenue Forecast'!O49-O19)/'Revenue Forecast'!O34,0)</f>
-        <v/>
-      </c>
-      <c r="P21" s="72">
-        <f>IFERROR(('Revenue Forecast'!P50-'Revenue Forecast'!P49-P19)/'Revenue Forecast'!P34,0)</f>
-        <v/>
-      </c>
-      <c r="Q21" s="72">
-        <f>IFERROR(('Revenue Forecast'!Q50-'Revenue Forecast'!Q49-Q19)/'Revenue Forecast'!Q34,0)</f>
-        <v/>
-      </c>
-      <c r="R21" s="72">
-        <f>IFERROR(('Revenue Forecast'!R50-'Revenue Forecast'!R49-R19)/'Revenue Forecast'!R34,0)</f>
-        <v/>
-      </c>
-      <c r="S21" s="72">
-        <f>IFERROR(('Revenue Forecast'!S50-'Revenue Forecast'!S49-S19)/'Revenue Forecast'!S34,0)</f>
-        <v/>
-      </c>
-      <c r="T21" s="72">
-        <f>IFERROR(('Revenue Forecast'!T50-'Revenue Forecast'!T49-T19)/'Revenue Forecast'!T34,0)</f>
-        <v/>
-      </c>
-      <c r="U21" s="72">
-        <f>IFERROR(('Revenue Forecast'!U50-'Revenue Forecast'!U49-U19)/'Revenue Forecast'!U34,0)</f>
-        <v/>
-      </c>
-      <c r="V21" s="72">
-        <f>IFERROR(('Revenue Forecast'!V50-'Revenue Forecast'!V49-V19)/'Revenue Forecast'!V34,0)</f>
-        <v/>
-      </c>
-      <c r="W21" s="72">
-        <f>IFERROR(('Revenue Forecast'!W50-'Revenue Forecast'!W49-W19)/'Revenue Forecast'!W34,0)</f>
-        <v/>
-      </c>
-      <c r="X21" s="72">
-        <f>IFERROR(('Revenue Forecast'!X50-'Revenue Forecast'!X49-X19)/'Revenue Forecast'!X34,0)</f>
-        <v/>
-      </c>
-      <c r="Y21" s="72">
-        <f>IFERROR(('Revenue Forecast'!Y50-'Revenue Forecast'!Y49-Y19)/'Revenue Forecast'!Y34,0)</f>
-        <v/>
-      </c>
-      <c r="Z21" s="72">
-        <f>IFERROR(('Revenue Forecast'!Z50-'Revenue Forecast'!Z49-Z19)/'Revenue Forecast'!Z34,0)</f>
-        <v/>
-      </c>
-      <c r="AA21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AA50-'Revenue Forecast'!AA49-AA19)/'Revenue Forecast'!AA34,0)</f>
-        <v/>
-      </c>
-      <c r="AB21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AB50-'Revenue Forecast'!AB49-AB19)/'Revenue Forecast'!AB34,0)</f>
-        <v/>
-      </c>
-      <c r="AC21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AC50-'Revenue Forecast'!AC49-AC19)/'Revenue Forecast'!AC34,0)</f>
-        <v/>
-      </c>
-      <c r="AD21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AD50-'Revenue Forecast'!AD49-AD19)/'Revenue Forecast'!AD34,0)</f>
-        <v/>
-      </c>
-      <c r="AE21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AE50-'Revenue Forecast'!AE49-AE19)/'Revenue Forecast'!AE34,0)</f>
-        <v/>
-      </c>
-      <c r="AF21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AF50-'Revenue Forecast'!AF49-AF19)/'Revenue Forecast'!AF34,0)</f>
-        <v/>
-      </c>
-      <c r="AG21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AG50-'Revenue Forecast'!AG49-AG19)/'Revenue Forecast'!AG34,0)</f>
-        <v/>
-      </c>
-      <c r="AH21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AH50-'Revenue Forecast'!AH49-AH19)/'Revenue Forecast'!AH34,0)</f>
-        <v/>
-      </c>
-      <c r="AI21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AI50-'Revenue Forecast'!AI49-AI19)/'Revenue Forecast'!AI34,0)</f>
-        <v/>
-      </c>
-      <c r="AJ21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AJ50-'Revenue Forecast'!AJ49-AJ19)/'Revenue Forecast'!AJ34,0)</f>
-        <v/>
-      </c>
-      <c r="AK21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AK50-'Revenue Forecast'!AK49-AK19)/'Revenue Forecast'!AK34,0)</f>
-        <v/>
-      </c>
-      <c r="AL21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AL50-'Revenue Forecast'!AL49-AL19)/'Revenue Forecast'!AL34,0)</f>
-        <v/>
-      </c>
-      <c r="AM21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AM50-'Revenue Forecast'!AM49-AM19)/'Revenue Forecast'!AM34,0)</f>
-        <v/>
-      </c>
-      <c r="AN21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AN50-'Revenue Forecast'!AN49-AN19)/'Revenue Forecast'!AN34,0)</f>
-        <v/>
-      </c>
-      <c r="AO21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AO50-'Revenue Forecast'!AO49-AO19)/'Revenue Forecast'!AO34,0)</f>
-        <v/>
-      </c>
-      <c r="AP21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AP50-'Revenue Forecast'!AP49-AP19)/'Revenue Forecast'!AP34,0)</f>
-        <v/>
-      </c>
-      <c r="AQ21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AQ50-'Revenue Forecast'!AQ49-AQ19)/'Revenue Forecast'!AQ34,0)</f>
-        <v/>
-      </c>
-      <c r="AR21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AR50-'Revenue Forecast'!AR49-AR19)/'Revenue Forecast'!AR34,0)</f>
-        <v/>
-      </c>
-      <c r="AS21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AS50-'Revenue Forecast'!AS49-AS19)/'Revenue Forecast'!AS34,0)</f>
-        <v/>
-      </c>
-      <c r="AT21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AT50-'Revenue Forecast'!AT49-AT19)/'Revenue Forecast'!AT34,0)</f>
-        <v/>
-      </c>
-      <c r="AU21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AU50-'Revenue Forecast'!AU49-AU19)/'Revenue Forecast'!AU34,0)</f>
-        <v/>
-      </c>
-      <c r="AV21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AV50-'Revenue Forecast'!AV49-AV19)/'Revenue Forecast'!AV34,0)</f>
-        <v/>
-      </c>
-      <c r="AW21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AW50-'Revenue Forecast'!AW49-AW19)/'Revenue Forecast'!AW34,0)</f>
-        <v/>
-      </c>
-      <c r="AX21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AX50-'Revenue Forecast'!AX49-AX19)/'Revenue Forecast'!AX34,0)</f>
-        <v/>
-      </c>
-      <c r="AY21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AY50-'Revenue Forecast'!AY49-AY19)/'Revenue Forecast'!AY34,0)</f>
-        <v/>
-      </c>
-      <c r="AZ21" s="72">
-        <f>IFERROR(('Revenue Forecast'!AZ50-'Revenue Forecast'!AZ49-AZ19)/'Revenue Forecast'!AZ34,0)</f>
-        <v/>
-      </c>
-      <c r="BA21" s="72">
-        <f>IFERROR(('Revenue Forecast'!BA50-'Revenue Forecast'!BA49-BA19)/'Revenue Forecast'!BA34,0)</f>
-        <v/>
-      </c>
-      <c r="BB21" s="72">
-        <f>IFERROR(('Revenue Forecast'!BB50-'Revenue Forecast'!BB49-BB19)/'Revenue Forecast'!BB34,0)</f>
-        <v/>
-      </c>
-      <c r="BC21" s="72">
-        <f>IFERROR(('Revenue Forecast'!BC50-'Revenue Forecast'!BC49-BC19)/'Revenue Forecast'!BC34,0)</f>
-        <v/>
-      </c>
-      <c r="BD21" s="72">
-        <f>IFERROR(('Revenue Forecast'!BD50-'Revenue Forecast'!BD49-BD19)/'Revenue Forecast'!BD34,0)</f>
-        <v/>
-      </c>
-      <c r="BE21" s="72">
-        <f>IFERROR(('Revenue Forecast'!BE50-'Revenue Forecast'!BE49-BE19)/'Revenue Forecast'!BE34,0)</f>
-        <v/>
-      </c>
-      <c r="BF21" s="72">
-        <f>IFERROR(('Revenue Forecast'!BF50-'Revenue Forecast'!BF49-BF19)/'Revenue Forecast'!BF34,0)</f>
-        <v/>
-      </c>
-      <c r="BG21" s="72">
-        <f>IFERROR(('Revenue Forecast'!BG50-'Revenue Forecast'!BG49-BG19)/'Revenue Forecast'!BG34,0)</f>
-        <v/>
-      </c>
-      <c r="BH21" s="72">
-        <f>IFERROR(('Revenue Forecast'!BH50-'Revenue Forecast'!BH49-BH19)/'Revenue Forecast'!BH34,0)</f>
-        <v/>
-      </c>
-      <c r="BI21" s="72">
-        <f>IFERROR(('Revenue Forecast'!BI50-'Revenue Forecast'!BI49-BI19)/'Revenue Forecast'!BI34,0)</f>
-        <v/>
-      </c>
-      <c r="BJ21" s="72">
-        <f>IFERROR(('Revenue Forecast'!BJ50-'Revenue Forecast'!BJ49-BJ19)/'Revenue Forecast'!BJ34,0)</f>
-        <v/>
-      </c>
-      <c r="BK21" s="72">
-        <f>IFERROR(('Revenue Forecast'!BK50-'Revenue Forecast'!BK49-BK19)/'Revenue Forecast'!BK34,0)</f>
-        <v/>
-      </c>
-      <c r="BL21" s="72">
-        <f>IFERROR(('Revenue Forecast'!BL50-'Revenue Forecast'!BL49-BL19)/'Revenue Forecast'!BL34,0)</f>
-        <v/>
-      </c>
-      <c r="BN21" s="73">
-        <f>IFERROR(('Revenue Forecast'!BN50-'Revenue Forecast'!BN49-BN19)/'Revenue Forecast'!BN34,0)</f>
-        <v/>
-      </c>
-      <c r="BO21" s="73">
-        <f>IFERROR(('Revenue Forecast'!BO50-'Revenue Forecast'!BO49-BO19)/'Revenue Forecast'!BO34,0)</f>
-        <v/>
-      </c>
-      <c r="BP21" s="73">
-        <f>IFERROR(('Revenue Forecast'!BP50-'Revenue Forecast'!BP49-BP19)/'Revenue Forecast'!BP34,0)</f>
-        <v/>
-      </c>
-      <c r="BQ21" s="73">
-        <f>IFERROR(('Revenue Forecast'!BQ50-'Revenue Forecast'!BQ49-BQ19)/'Revenue Forecast'!BQ34,0)</f>
-        <v/>
-      </c>
-      <c r="BR21" s="73">
-        <f>IFERROR(('Revenue Forecast'!BR50-'Revenue Forecast'!BR49-BR19)/'Revenue Forecast'!BR34,0)</f>
-        <v/>
-      </c>
-      <c r="BT21" s="28" t="inlineStr">
+      <c r="E22" s="72">
+        <f>IFERROR(('Revenue Forecast'!E50-'Revenue Forecast'!E49-E20)/'Revenue Forecast'!E34,0)</f>
+        <v/>
+      </c>
+      <c r="F22" s="72">
+        <f>IFERROR(('Revenue Forecast'!F50-'Revenue Forecast'!F49-F20)/'Revenue Forecast'!F34,0)</f>
+        <v/>
+      </c>
+      <c r="G22" s="72">
+        <f>IFERROR(('Revenue Forecast'!G50-'Revenue Forecast'!G49-G20)/'Revenue Forecast'!G34,0)</f>
+        <v/>
+      </c>
+      <c r="H22" s="72">
+        <f>IFERROR(('Revenue Forecast'!H50-'Revenue Forecast'!H49-H20)/'Revenue Forecast'!H34,0)</f>
+        <v/>
+      </c>
+      <c r="I22" s="72">
+        <f>IFERROR(('Revenue Forecast'!I50-'Revenue Forecast'!I49-I20)/'Revenue Forecast'!I34,0)</f>
+        <v/>
+      </c>
+      <c r="J22" s="72">
+        <f>IFERROR(('Revenue Forecast'!J50-'Revenue Forecast'!J49-J20)/'Revenue Forecast'!J34,0)</f>
+        <v/>
+      </c>
+      <c r="K22" s="72">
+        <f>IFERROR(('Revenue Forecast'!K50-'Revenue Forecast'!K49-K20)/'Revenue Forecast'!K34,0)</f>
+        <v/>
+      </c>
+      <c r="L22" s="72">
+        <f>IFERROR(('Revenue Forecast'!L50-'Revenue Forecast'!L49-L20)/'Revenue Forecast'!L34,0)</f>
+        <v/>
+      </c>
+      <c r="M22" s="72">
+        <f>IFERROR(('Revenue Forecast'!M50-'Revenue Forecast'!M49-M20)/'Revenue Forecast'!M34,0)</f>
+        <v/>
+      </c>
+      <c r="N22" s="72">
+        <f>IFERROR(('Revenue Forecast'!N50-'Revenue Forecast'!N49-N20)/'Revenue Forecast'!N34,0)</f>
+        <v/>
+      </c>
+      <c r="O22" s="72">
+        <f>IFERROR(('Revenue Forecast'!O50-'Revenue Forecast'!O49-O20)/'Revenue Forecast'!O34,0)</f>
+        <v/>
+      </c>
+      <c r="P22" s="72">
+        <f>IFERROR(('Revenue Forecast'!P50-'Revenue Forecast'!P49-P20)/'Revenue Forecast'!P34,0)</f>
+        <v/>
+      </c>
+      <c r="Q22" s="72">
+        <f>IFERROR(('Revenue Forecast'!Q50-'Revenue Forecast'!Q49-Q20)/'Revenue Forecast'!Q34,0)</f>
+        <v/>
+      </c>
+      <c r="R22" s="72">
+        <f>IFERROR(('Revenue Forecast'!R50-'Revenue Forecast'!R49-R20)/'Revenue Forecast'!R34,0)</f>
+        <v/>
+      </c>
+      <c r="S22" s="72">
+        <f>IFERROR(('Revenue Forecast'!S50-'Revenue Forecast'!S49-S20)/'Revenue Forecast'!S34,0)</f>
+        <v/>
+      </c>
+      <c r="T22" s="72">
+        <f>IFERROR(('Revenue Forecast'!T50-'Revenue Forecast'!T49-T20)/'Revenue Forecast'!T34,0)</f>
+        <v/>
+      </c>
+      <c r="U22" s="72">
+        <f>IFERROR(('Revenue Forecast'!U50-'Revenue Forecast'!U49-U20)/'Revenue Forecast'!U34,0)</f>
+        <v/>
+      </c>
+      <c r="V22" s="72">
+        <f>IFERROR(('Revenue Forecast'!V50-'Revenue Forecast'!V49-V20)/'Revenue Forecast'!V34,0)</f>
+        <v/>
+      </c>
+      <c r="W22" s="72">
+        <f>IFERROR(('Revenue Forecast'!W50-'Revenue Forecast'!W49-W20)/'Revenue Forecast'!W34,0)</f>
+        <v/>
+      </c>
+      <c r="X22" s="72">
+        <f>IFERROR(('Revenue Forecast'!X50-'Revenue Forecast'!X49-X20)/'Revenue Forecast'!X34,0)</f>
+        <v/>
+      </c>
+      <c r="Y22" s="72">
+        <f>IFERROR(('Revenue Forecast'!Y50-'Revenue Forecast'!Y49-Y20)/'Revenue Forecast'!Y34,0)</f>
+        <v/>
+      </c>
+      <c r="Z22" s="72">
+        <f>IFERROR(('Revenue Forecast'!Z50-'Revenue Forecast'!Z49-Z20)/'Revenue Forecast'!Z34,0)</f>
+        <v/>
+      </c>
+      <c r="AA22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AA50-'Revenue Forecast'!AA49-AA20)/'Revenue Forecast'!AA34,0)</f>
+        <v/>
+      </c>
+      <c r="AB22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AB50-'Revenue Forecast'!AB49-AB20)/'Revenue Forecast'!AB34,0)</f>
+        <v/>
+      </c>
+      <c r="AC22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AC50-'Revenue Forecast'!AC49-AC20)/'Revenue Forecast'!AC34,0)</f>
+        <v/>
+      </c>
+      <c r="AD22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AD50-'Revenue Forecast'!AD49-AD20)/'Revenue Forecast'!AD34,0)</f>
+        <v/>
+      </c>
+      <c r="AE22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AE50-'Revenue Forecast'!AE49-AE20)/'Revenue Forecast'!AE34,0)</f>
+        <v/>
+      </c>
+      <c r="AF22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AF50-'Revenue Forecast'!AF49-AF20)/'Revenue Forecast'!AF34,0)</f>
+        <v/>
+      </c>
+      <c r="AG22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AG50-'Revenue Forecast'!AG49-AG20)/'Revenue Forecast'!AG34,0)</f>
+        <v/>
+      </c>
+      <c r="AH22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AH50-'Revenue Forecast'!AH49-AH20)/'Revenue Forecast'!AH34,0)</f>
+        <v/>
+      </c>
+      <c r="AI22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AI50-'Revenue Forecast'!AI49-AI20)/'Revenue Forecast'!AI34,0)</f>
+        <v/>
+      </c>
+      <c r="AJ22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AJ50-'Revenue Forecast'!AJ49-AJ20)/'Revenue Forecast'!AJ34,0)</f>
+        <v/>
+      </c>
+      <c r="AK22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AK50-'Revenue Forecast'!AK49-AK20)/'Revenue Forecast'!AK34,0)</f>
+        <v/>
+      </c>
+      <c r="AL22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AL50-'Revenue Forecast'!AL49-AL20)/'Revenue Forecast'!AL34,0)</f>
+        <v/>
+      </c>
+      <c r="AM22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AM50-'Revenue Forecast'!AM49-AM20)/'Revenue Forecast'!AM34,0)</f>
+        <v/>
+      </c>
+      <c r="AN22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AN50-'Revenue Forecast'!AN49-AN20)/'Revenue Forecast'!AN34,0)</f>
+        <v/>
+      </c>
+      <c r="AO22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AO50-'Revenue Forecast'!AO49-AO20)/'Revenue Forecast'!AO34,0)</f>
+        <v/>
+      </c>
+      <c r="AP22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AP50-'Revenue Forecast'!AP49-AP20)/'Revenue Forecast'!AP34,0)</f>
+        <v/>
+      </c>
+      <c r="AQ22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AQ50-'Revenue Forecast'!AQ49-AQ20)/'Revenue Forecast'!AQ34,0)</f>
+        <v/>
+      </c>
+      <c r="AR22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AR50-'Revenue Forecast'!AR49-AR20)/'Revenue Forecast'!AR34,0)</f>
+        <v/>
+      </c>
+      <c r="AS22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AS50-'Revenue Forecast'!AS49-AS20)/'Revenue Forecast'!AS34,0)</f>
+        <v/>
+      </c>
+      <c r="AT22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AT50-'Revenue Forecast'!AT49-AT20)/'Revenue Forecast'!AT34,0)</f>
+        <v/>
+      </c>
+      <c r="AU22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AU50-'Revenue Forecast'!AU49-AU20)/'Revenue Forecast'!AU34,0)</f>
+        <v/>
+      </c>
+      <c r="AV22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AV50-'Revenue Forecast'!AV49-AV20)/'Revenue Forecast'!AV34,0)</f>
+        <v/>
+      </c>
+      <c r="AW22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AW50-'Revenue Forecast'!AW49-AW20)/'Revenue Forecast'!AW34,0)</f>
+        <v/>
+      </c>
+      <c r="AX22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AX50-'Revenue Forecast'!AX49-AX20)/'Revenue Forecast'!AX34,0)</f>
+        <v/>
+      </c>
+      <c r="AY22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AY50-'Revenue Forecast'!AY49-AY20)/'Revenue Forecast'!AY34,0)</f>
+        <v/>
+      </c>
+      <c r="AZ22" s="72">
+        <f>IFERROR(('Revenue Forecast'!AZ50-'Revenue Forecast'!AZ49-AZ20)/'Revenue Forecast'!AZ34,0)</f>
+        <v/>
+      </c>
+      <c r="BA22" s="72">
+        <f>IFERROR(('Revenue Forecast'!BA50-'Revenue Forecast'!BA49-BA20)/'Revenue Forecast'!BA34,0)</f>
+        <v/>
+      </c>
+      <c r="BB22" s="72">
+        <f>IFERROR(('Revenue Forecast'!BB50-'Revenue Forecast'!BB49-BB20)/'Revenue Forecast'!BB34,0)</f>
+        <v/>
+      </c>
+      <c r="BC22" s="72">
+        <f>IFERROR(('Revenue Forecast'!BC50-'Revenue Forecast'!BC49-BC20)/'Revenue Forecast'!BC34,0)</f>
+        <v/>
+      </c>
+      <c r="BD22" s="72">
+        <f>IFERROR(('Revenue Forecast'!BD50-'Revenue Forecast'!BD49-BD20)/'Revenue Forecast'!BD34,0)</f>
+        <v/>
+      </c>
+      <c r="BE22" s="72">
+        <f>IFERROR(('Revenue Forecast'!BE50-'Revenue Forecast'!BE49-BE20)/'Revenue Forecast'!BE34,0)</f>
+        <v/>
+      </c>
+      <c r="BF22" s="72">
+        <f>IFERROR(('Revenue Forecast'!BF50-'Revenue Forecast'!BF49-BF20)/'Revenue Forecast'!BF34,0)</f>
+        <v/>
+      </c>
+      <c r="BG22" s="72">
+        <f>IFERROR(('Revenue Forecast'!BG50-'Revenue Forecast'!BG49-BG20)/'Revenue Forecast'!BG34,0)</f>
+        <v/>
+      </c>
+      <c r="BH22" s="72">
+        <f>IFERROR(('Revenue Forecast'!BH50-'Revenue Forecast'!BH49-BH20)/'Revenue Forecast'!BH34,0)</f>
+        <v/>
+      </c>
+      <c r="BI22" s="72">
+        <f>IFERROR(('Revenue Forecast'!BI50-'Revenue Forecast'!BI49-BI20)/'Revenue Forecast'!BI34,0)</f>
+        <v/>
+      </c>
+      <c r="BJ22" s="72">
+        <f>IFERROR(('Revenue Forecast'!BJ50-'Revenue Forecast'!BJ49-BJ20)/'Revenue Forecast'!BJ34,0)</f>
+        <v/>
+      </c>
+      <c r="BK22" s="72">
+        <f>IFERROR(('Revenue Forecast'!BK50-'Revenue Forecast'!BK49-BK20)/'Revenue Forecast'!BK34,0)</f>
+        <v/>
+      </c>
+      <c r="BL22" s="72">
+        <f>IFERROR(('Revenue Forecast'!BL50-'Revenue Forecast'!BL49-BL20)/'Revenue Forecast'!BL34,0)</f>
+        <v/>
+      </c>
+      <c r="BN22" s="73">
+        <f>IFERROR(('Revenue Forecast'!BN50-'Revenue Forecast'!BN49-BN20)/'Revenue Forecast'!BN34,0)</f>
+        <v/>
+      </c>
+      <c r="BO22" s="73">
+        <f>IFERROR(('Revenue Forecast'!BO50-'Revenue Forecast'!BO49-BO20)/'Revenue Forecast'!BO34,0)</f>
+        <v/>
+      </c>
+      <c r="BP22" s="73">
+        <f>IFERROR(('Revenue Forecast'!BP50-'Revenue Forecast'!BP49-BP20)/'Revenue Forecast'!BP34,0)</f>
+        <v/>
+      </c>
+      <c r="BQ22" s="73">
+        <f>IFERROR(('Revenue Forecast'!BQ50-'Revenue Forecast'!BQ49-BQ20)/'Revenue Forecast'!BQ34,0)</f>
+        <v/>
+      </c>
+      <c r="BR22" s="73">
+        <f>IFERROR(('Revenue Forecast'!BR50-'Revenue Forecast'!BR49-BR20)/'Revenue Forecast'!BR34,0)</f>
+        <v/>
+      </c>
+      <c r="BT22" s="28" t="inlineStr">
         <is>
           <t>trading revenue less cost of sales, per unit; the subsidy is left out</t>
         </is>
@@ -36300,243 +36969,243 @@
         </is>
       </c>
       <c r="E13" s="10">
-        <f>'Revenue Forecast'!E19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(E$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!E19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(E$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="F13" s="10">
-        <f>'Revenue Forecast'!F19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(F$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!F19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(F$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="G13" s="10">
-        <f>'Revenue Forecast'!G19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(G$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!G19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(G$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="H13" s="10">
-        <f>'Revenue Forecast'!H19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(H$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!H19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(H$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="I13" s="10">
-        <f>'Revenue Forecast'!I19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(I$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!I19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(I$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="J13" s="10">
-        <f>'Revenue Forecast'!J19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(J$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!J19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(J$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="K13" s="10">
-        <f>'Revenue Forecast'!K19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(K$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!K19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(K$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="L13" s="10">
-        <f>'Revenue Forecast'!L19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(L$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!L19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(L$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="M13" s="10">
-        <f>'Revenue Forecast'!M19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(M$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!M19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(M$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="N13" s="10">
-        <f>'Revenue Forecast'!N19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(N$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!N19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(N$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="O13" s="10">
-        <f>'Revenue Forecast'!O19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(O$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!O19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(O$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="P13" s="10">
-        <f>'Revenue Forecast'!P19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(P$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!P19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(P$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Q13" s="10">
-        <f>'Revenue Forecast'!Q19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(Q$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!Q19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(Q$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="R13" s="10">
-        <f>'Revenue Forecast'!R19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(R$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!R19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(R$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="S13" s="10">
-        <f>'Revenue Forecast'!S19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(S$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!S19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(S$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="T13" s="10">
-        <f>'Revenue Forecast'!T19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(T$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!T19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(T$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="U13" s="10">
-        <f>'Revenue Forecast'!U19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(U$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!U19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(U$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="V13" s="10">
-        <f>'Revenue Forecast'!V19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(V$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!V19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(V$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="W13" s="10">
-        <f>'Revenue Forecast'!W19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(W$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!W19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(W$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="X13" s="10">
-        <f>'Revenue Forecast'!X19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(X$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!X19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(X$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Y13" s="10">
-        <f>'Revenue Forecast'!Y19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(Y$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!Y19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(Y$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Z13" s="10">
-        <f>'Revenue Forecast'!Z19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(Z$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!Z19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(Z$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AA13" s="10">
-        <f>'Revenue Forecast'!AA19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AA$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AA19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AB13" s="10">
-        <f>'Revenue Forecast'!AB19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AB$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AB19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AC13" s="10">
-        <f>'Revenue Forecast'!AC19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AC$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AC19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AD13" s="10">
-        <f>'Revenue Forecast'!AD19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AD$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AD19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AE13" s="10">
-        <f>'Revenue Forecast'!AE19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AE$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AE19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AF13" s="10">
-        <f>'Revenue Forecast'!AF19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AF$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AF19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AG13" s="10">
-        <f>'Revenue Forecast'!AG19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AG$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AG19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AH13" s="10">
-        <f>'Revenue Forecast'!AH19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AH$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AH19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AI13" s="10">
-        <f>'Revenue Forecast'!AI19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AI$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AI19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AJ13" s="10">
-        <f>'Revenue Forecast'!AJ19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AJ19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AK13" s="10">
-        <f>'Revenue Forecast'!AK19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AK$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AK19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AL13" s="10">
-        <f>'Revenue Forecast'!AL19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AL$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AL19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AM13" s="10">
-        <f>'Revenue Forecast'!AM19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AM$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AM19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AM$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AN13" s="10">
-        <f>'Revenue Forecast'!AN19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AN$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AN19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AN$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AO13" s="10">
-        <f>'Revenue Forecast'!AO19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AO$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AO19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AO$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AP13" s="10">
-        <f>'Revenue Forecast'!AP19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AP$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AP19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AP$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AQ13" s="10">
-        <f>'Revenue Forecast'!AQ19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AQ19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AR13" s="10">
-        <f>'Revenue Forecast'!AR19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AR$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AR19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AR$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AS13" s="10">
-        <f>'Revenue Forecast'!AS19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AS$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AS19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AS$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AT13" s="10">
-        <f>'Revenue Forecast'!AT19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AT$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AT19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AT$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AU13" s="10">
-        <f>'Revenue Forecast'!AU19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AU$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AU19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AU$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AV13" s="10">
-        <f>'Revenue Forecast'!AV19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AV$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AV19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AV$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AW13" s="10">
-        <f>'Revenue Forecast'!AW19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AW$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AW19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AW$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AX13" s="10">
-        <f>'Revenue Forecast'!AX19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AX$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AX19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AX$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AY13" s="10">
-        <f>'Revenue Forecast'!AY19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AY$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AY19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AY$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AZ13" s="10">
-        <f>'Revenue Forecast'!AZ19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AZ19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BA13" s="10">
-        <f>'Revenue Forecast'!BA19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BA$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BA19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BB13" s="10">
-        <f>'Revenue Forecast'!BB19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BB$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BB19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BC13" s="10">
-        <f>'Revenue Forecast'!BC19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BC$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BC19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BD13" s="10">
-        <f>'Revenue Forecast'!BD19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BD$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BD19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BE13" s="10">
-        <f>'Revenue Forecast'!BE19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BE$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BE19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BF13" s="10">
-        <f>'Revenue Forecast'!BF19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BF$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BF19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BG13" s="10">
-        <f>'Revenue Forecast'!BG19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BG$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BG19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BH13" s="10">
-        <f>'Revenue Forecast'!BH19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BH$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BH19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BI13" s="10">
-        <f>'Revenue Forecast'!BI19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BI$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BI19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BJ13" s="10">
-        <f>'Revenue Forecast'!BJ19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BJ19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BK13" s="10">
-        <f>'Revenue Forecast'!BK19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BK$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BK19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BL13" s="10">
-        <f>'Revenue Forecast'!BL19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BL$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BL19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BN13" s="53">
@@ -36920,243 +37589,243 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(E$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(E$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="F17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(F$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(F$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="G17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(G$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(G$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="H17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(H$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(H$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="I17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(I$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(I$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="J17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(J$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(J$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="K17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(K$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(K$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="L17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(L$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(L$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="M17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(M$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(M$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="N17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(N$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(N$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="O17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(O$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(O$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="P17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(P$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(P$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Q17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(Q$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(Q$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="R17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(R$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(R$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="S17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(S$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(S$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="T17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(T$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(T$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="U17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(U$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(U$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="V17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(V$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(V$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="W17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(W$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(W$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="X17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(X$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(X$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Y17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(Y$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(Y$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Z17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(Z$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(Z$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AA17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AA$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AB17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AB$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AC17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AC$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AD17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AD$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AE17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AE$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AF17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AF$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AG17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AG$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AH17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AH$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AI17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AI$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AJ17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AK17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AK$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AL17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AL$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AM17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AM$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AM$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AN17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AN$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AN$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AO17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AO$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AO$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AP17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AP$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AP$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AQ17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AR17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AR$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AR$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AS17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AS$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AS$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AT17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AT$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AT$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AU17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AU$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AU$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AV17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AV$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AV$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AW17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AW$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AW$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AX17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AX$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AX$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AY17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AY$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AY$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AZ17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BA17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BA$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BB17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BB$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BC17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BC$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BD17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BD$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BE17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BE$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BF17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BF$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BG17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BG$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BH17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BH$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BI17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BI$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BJ17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BK17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BK$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BL17" s="10">
-        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BL$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BN17" s="53">
@@ -37192,243 +37861,243 @@
         </is>
       </c>
       <c r="E18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(E$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(E$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="F18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(F$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(F$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="G18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(G$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(G$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="H18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(H$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(H$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="I18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(I$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(I$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="J18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(J$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(J$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="K18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(K$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(K$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="L18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(L$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(L$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="M18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(M$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(M$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="N18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(N$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(N$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="O18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(O$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(O$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="P18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(P$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(P$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Q18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(Q$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(Q$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="R18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(R$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(R$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="S18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(S$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(S$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="T18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(T$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(T$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="U18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(U$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(U$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="V18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(V$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(V$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="W18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(W$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(W$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="X18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(X$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(X$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Y18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(Y$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(Y$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Z18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(Z$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(Z$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AA18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AA$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AB18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AB$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AC18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AC$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AD18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AD$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AE18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AE$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AF18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AF$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AG18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AG$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AH18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AH$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AI18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AI$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AJ18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AK18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AK$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AL18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AL$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AM18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AM$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AM$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AN18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AN$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AN$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AO18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AO$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AO$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AP18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AP$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AP$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AQ18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AR18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AR$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AR$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AS18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AS$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AS$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AT18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AT$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AT$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AU18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AU$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AU$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AV18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AV$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AV$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AW18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AW$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AW$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AX18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AX$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AX$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AY18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AY$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AY$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AZ18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BA18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BA$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BB18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BB$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BC18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BC$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BD18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BD$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BE18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BE$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BF18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BF$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BG18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BG$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BH18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BH$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BI18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BI$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BJ18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BK18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BK$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BL18" s="10">
-        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BL$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BN18" s="53">
@@ -37812,243 +38481,243 @@
         </is>
       </c>
       <c r="E22" s="10">
-        <f>Personnel!E20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(E$3)-Assumptions!$F$9)</f>
+        <f>Personnel!E20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(E$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="F22" s="10">
-        <f>Personnel!F20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(F$3)-Assumptions!$F$9)</f>
+        <f>Personnel!F20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(F$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="G22" s="10">
-        <f>Personnel!G20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(G$3)-Assumptions!$F$9)</f>
+        <f>Personnel!G20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(G$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="H22" s="10">
-        <f>Personnel!H20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(H$3)-Assumptions!$F$9)</f>
+        <f>Personnel!H20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(H$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="I22" s="10">
-        <f>Personnel!I20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(I$3)-Assumptions!$F$9)</f>
+        <f>Personnel!I20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(I$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="J22" s="10">
-        <f>Personnel!J20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(J$3)-Assumptions!$F$9)</f>
+        <f>Personnel!J20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(J$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="K22" s="10">
-        <f>Personnel!K20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(K$3)-Assumptions!$F$9)</f>
+        <f>Personnel!K20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(K$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="L22" s="10">
-        <f>Personnel!L20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(L$3)-Assumptions!$F$9)</f>
+        <f>Personnel!L20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(L$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="M22" s="10">
-        <f>Personnel!M20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(M$3)-Assumptions!$F$9)</f>
+        <f>Personnel!M20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(M$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="N22" s="10">
-        <f>Personnel!N20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(N$3)-Assumptions!$F$9)</f>
+        <f>Personnel!N20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(N$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="O22" s="10">
-        <f>Personnel!O20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(O$3)-Assumptions!$F$9)</f>
+        <f>Personnel!O20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(O$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="P22" s="10">
-        <f>Personnel!P20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(P$3)-Assumptions!$F$9)</f>
+        <f>Personnel!P20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(P$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Q22" s="10">
-        <f>Personnel!Q20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(Q$3)-Assumptions!$F$9)</f>
+        <f>Personnel!Q20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(Q$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="R22" s="10">
-        <f>Personnel!R20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(R$3)-Assumptions!$F$9)</f>
+        <f>Personnel!R20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(R$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="S22" s="10">
-        <f>Personnel!S20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(S$3)-Assumptions!$F$9)</f>
+        <f>Personnel!S20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(S$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="T22" s="10">
-        <f>Personnel!T20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(T$3)-Assumptions!$F$9)</f>
+        <f>Personnel!T20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(T$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="U22" s="10">
-        <f>Personnel!U20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(U$3)-Assumptions!$F$9)</f>
+        <f>Personnel!U20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(U$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="V22" s="10">
-        <f>Personnel!V20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(V$3)-Assumptions!$F$9)</f>
+        <f>Personnel!V20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(V$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="W22" s="10">
-        <f>Personnel!W20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(W$3)-Assumptions!$F$9)</f>
+        <f>Personnel!W20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(W$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="X22" s="10">
-        <f>Personnel!X20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(X$3)-Assumptions!$F$9)</f>
+        <f>Personnel!X20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(X$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Y22" s="10">
-        <f>Personnel!Y20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(Y$3)-Assumptions!$F$9)</f>
+        <f>Personnel!Y20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(Y$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Z22" s="10">
-        <f>Personnel!Z20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(Z$3)-Assumptions!$F$9)</f>
+        <f>Personnel!Z20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(Z$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AA22" s="10">
-        <f>Personnel!AA20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AA$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AA20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AB22" s="10">
-        <f>Personnel!AB20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AB$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AB20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AC22" s="10">
-        <f>Personnel!AC20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AC$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AC20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AD22" s="10">
-        <f>Personnel!AD20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AD$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AD20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AE22" s="10">
-        <f>Personnel!AE20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AE$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AE20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AF22" s="10">
-        <f>Personnel!AF20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AF$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AF20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AG22" s="10">
-        <f>Personnel!AG20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AG$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AG20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AH22" s="10">
-        <f>Personnel!AH20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AH$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AH20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AI22" s="10">
-        <f>Personnel!AI20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AI$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AI20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AJ22" s="10">
-        <f>Personnel!AJ20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AJ20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AK22" s="10">
-        <f>Personnel!AK20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AK$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AK20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AL22" s="10">
-        <f>Personnel!AL20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AL$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AL20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AM22" s="10">
-        <f>Personnel!AM20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AM$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AM20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AM$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AN22" s="10">
-        <f>Personnel!AN20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AN$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AN20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AN$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AO22" s="10">
-        <f>Personnel!AO20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AO$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AO20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AO$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AP22" s="10">
-        <f>Personnel!AP20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AP$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AP20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AP$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AQ22" s="10">
-        <f>Personnel!AQ20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AQ20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AR22" s="10">
-        <f>Personnel!AR20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AR$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AR20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AR$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AS22" s="10">
-        <f>Personnel!AS20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AS$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AS20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AS$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AT22" s="10">
-        <f>Personnel!AT20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AT$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AT20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AT$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AU22" s="10">
-        <f>Personnel!AU20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AU$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AU20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AU$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AV22" s="10">
-        <f>Personnel!AV20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AV$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AV20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AV$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AW22" s="10">
-        <f>Personnel!AW20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AW$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AW20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AW$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AX22" s="10">
-        <f>Personnel!AX20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AX$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AX20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AX$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AY22" s="10">
-        <f>Personnel!AY20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AY$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AY20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AY$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AZ22" s="10">
-        <f>Personnel!AZ20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AZ20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BA22" s="10">
-        <f>Personnel!BA20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BA$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BA20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BB22" s="10">
-        <f>Personnel!BB20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BB$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BB20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BC22" s="10">
-        <f>Personnel!BC20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BC$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BC20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BD22" s="10">
-        <f>Personnel!BD20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BD$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BD20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BE22" s="10">
-        <f>Personnel!BE20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BE$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BE20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BF22" s="10">
-        <f>Personnel!BF20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BF$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BF20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BG22" s="10">
-        <f>Personnel!BG20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BG$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BG20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BH22" s="10">
-        <f>Personnel!BH20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BH$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BH20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BI22" s="10">
-        <f>Personnel!BI20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BI$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BI20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BJ22" s="10">
-        <f>Personnel!BJ20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BJ20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BK22" s="10">
-        <f>Personnel!BK20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BK$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BK20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BL22" s="10">
-        <f>Personnel!BL20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BL$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BL20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BN22" s="53">
@@ -38093,239 +38762,239 @@
         <v/>
       </c>
       <c r="F23" s="10">
-        <f>MAX(0,Personnel!F20-Personnel!E20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(F$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!F20-Personnel!E20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(F$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="G23" s="10">
-        <f>MAX(0,Personnel!G20-Personnel!F20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(G$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!G20-Personnel!F20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(G$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="H23" s="10">
-        <f>MAX(0,Personnel!H20-Personnel!G20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(H$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!H20-Personnel!G20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(H$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="I23" s="10">
-        <f>MAX(0,Personnel!I20-Personnel!H20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(I$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!I20-Personnel!H20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(I$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="J23" s="10">
-        <f>MAX(0,Personnel!J20-Personnel!I20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(J$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!J20-Personnel!I20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(J$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="K23" s="10">
-        <f>MAX(0,Personnel!K20-Personnel!J20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(K$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!K20-Personnel!J20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(K$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="L23" s="10">
-        <f>MAX(0,Personnel!L20-Personnel!K20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(L$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!L20-Personnel!K20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(L$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="M23" s="10">
-        <f>MAX(0,Personnel!M20-Personnel!L20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(M$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!M20-Personnel!L20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(M$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="N23" s="10">
-        <f>MAX(0,Personnel!N20-Personnel!M20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(N$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!N20-Personnel!M20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(N$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="O23" s="10">
-        <f>MAX(0,Personnel!O20-Personnel!N20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(O$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!O20-Personnel!N20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(O$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="P23" s="10">
-        <f>MAX(0,Personnel!P20-Personnel!O20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(P$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!P20-Personnel!O20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(P$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Q23" s="10">
-        <f>MAX(0,Personnel!Q20-Personnel!P20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(Q$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!Q20-Personnel!P20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(Q$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="R23" s="10">
-        <f>MAX(0,Personnel!R20-Personnel!Q20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(R$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!R20-Personnel!Q20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(R$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="S23" s="10">
-        <f>MAX(0,Personnel!S20-Personnel!R20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(S$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!S20-Personnel!R20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(S$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="T23" s="10">
-        <f>MAX(0,Personnel!T20-Personnel!S20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(T$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!T20-Personnel!S20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(T$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="U23" s="10">
-        <f>MAX(0,Personnel!U20-Personnel!T20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(U$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!U20-Personnel!T20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(U$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="V23" s="10">
-        <f>MAX(0,Personnel!V20-Personnel!U20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(V$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!V20-Personnel!U20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(V$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="W23" s="10">
-        <f>MAX(0,Personnel!W20-Personnel!V20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(W$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!W20-Personnel!V20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(W$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="X23" s="10">
-        <f>MAX(0,Personnel!X20-Personnel!W20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(X$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!X20-Personnel!W20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(X$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Y23" s="10">
-        <f>MAX(0,Personnel!Y20-Personnel!X20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(Y$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!Y20-Personnel!X20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(Y$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Z23" s="10">
-        <f>MAX(0,Personnel!Z20-Personnel!Y20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(Z$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!Z20-Personnel!Y20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(Z$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AA23" s="10">
-        <f>MAX(0,Personnel!AA20-Personnel!Z20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AA$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AA20-Personnel!Z20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AB23" s="10">
-        <f>MAX(0,Personnel!AB20-Personnel!AA20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AB$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AB20-Personnel!AA20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AC23" s="10">
-        <f>MAX(0,Personnel!AC20-Personnel!AB20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AC$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AC20-Personnel!AB20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AD23" s="10">
-        <f>MAX(0,Personnel!AD20-Personnel!AC20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AD$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AD20-Personnel!AC20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AE23" s="10">
-        <f>MAX(0,Personnel!AE20-Personnel!AD20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AE$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AE20-Personnel!AD20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AF23" s="10">
-        <f>MAX(0,Personnel!AF20-Personnel!AE20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AF$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AF20-Personnel!AE20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AG23" s="10">
-        <f>MAX(0,Personnel!AG20-Personnel!AF20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AG$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AG20-Personnel!AF20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AH23" s="10">
-        <f>MAX(0,Personnel!AH20-Personnel!AG20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AH$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AH20-Personnel!AG20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AI23" s="10">
-        <f>MAX(0,Personnel!AI20-Personnel!AH20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AI$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AI20-Personnel!AH20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AJ23" s="10">
-        <f>MAX(0,Personnel!AJ20-Personnel!AI20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AJ20-Personnel!AI20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AK23" s="10">
-        <f>MAX(0,Personnel!AK20-Personnel!AJ20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AK$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AK20-Personnel!AJ20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AL23" s="10">
-        <f>MAX(0,Personnel!AL20-Personnel!AK20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AL$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AL20-Personnel!AK20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AM23" s="10">
-        <f>MAX(0,Personnel!AM20-Personnel!AL20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AM$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AM20-Personnel!AL20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AM$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AN23" s="10">
-        <f>MAX(0,Personnel!AN20-Personnel!AM20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AN$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AN20-Personnel!AM20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AN$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AO23" s="10">
-        <f>MAX(0,Personnel!AO20-Personnel!AN20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AO$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AO20-Personnel!AN20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AO$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AP23" s="10">
-        <f>MAX(0,Personnel!AP20-Personnel!AO20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AP$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AP20-Personnel!AO20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AP$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AQ23" s="10">
-        <f>MAX(0,Personnel!AQ20-Personnel!AP20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AQ20-Personnel!AP20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AR23" s="10">
-        <f>MAX(0,Personnel!AR20-Personnel!AQ20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AR$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AR20-Personnel!AQ20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AR$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AS23" s="10">
-        <f>MAX(0,Personnel!AS20-Personnel!AR20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AS$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AS20-Personnel!AR20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AS$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AT23" s="10">
-        <f>MAX(0,Personnel!AT20-Personnel!AS20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AT$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AT20-Personnel!AS20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AT$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AU23" s="10">
-        <f>MAX(0,Personnel!AU20-Personnel!AT20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AU$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AU20-Personnel!AT20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AU$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AV23" s="10">
-        <f>MAX(0,Personnel!AV20-Personnel!AU20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AV$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AV20-Personnel!AU20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AV$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AW23" s="10">
-        <f>MAX(0,Personnel!AW20-Personnel!AV20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AW$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AW20-Personnel!AV20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AW$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AX23" s="10">
-        <f>MAX(0,Personnel!AX20-Personnel!AW20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AX$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AX20-Personnel!AW20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AX$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AY23" s="10">
-        <f>MAX(0,Personnel!AY20-Personnel!AX20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AY$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AY20-Personnel!AX20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AY$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AZ23" s="10">
-        <f>MAX(0,Personnel!AZ20-Personnel!AY20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AZ20-Personnel!AY20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BA23" s="10">
-        <f>MAX(0,Personnel!BA20-Personnel!AZ20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BA$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BA20-Personnel!AZ20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BB23" s="10">
-        <f>MAX(0,Personnel!BB20-Personnel!BA20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BB$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BB20-Personnel!BA20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BC23" s="10">
-        <f>MAX(0,Personnel!BC20-Personnel!BB20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BC$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BC20-Personnel!BB20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BD23" s="10">
-        <f>MAX(0,Personnel!BD20-Personnel!BC20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BD$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BD20-Personnel!BC20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BE23" s="10">
-        <f>MAX(0,Personnel!BE20-Personnel!BD20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BE$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BE20-Personnel!BD20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BF23" s="10">
-        <f>MAX(0,Personnel!BF20-Personnel!BE20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BF$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BF20-Personnel!BE20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BG23" s="10">
-        <f>MAX(0,Personnel!BG20-Personnel!BF20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BG$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BG20-Personnel!BF20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BH23" s="10">
-        <f>MAX(0,Personnel!BH20-Personnel!BG20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BH$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BH20-Personnel!BG20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BI23" s="10">
-        <f>MAX(0,Personnel!BI20-Personnel!BH20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BI$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BI20-Personnel!BH20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BJ23" s="10">
-        <f>MAX(0,Personnel!BJ20-Personnel!BI20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BJ20-Personnel!BI20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BK23" s="10">
-        <f>MAX(0,Personnel!BK20-Personnel!BJ20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BK$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BK20-Personnel!BJ20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BL23" s="10">
-        <f>MAX(0,Personnel!BL20-Personnel!BK20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BL$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BL20-Personnel!BK20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BN23" s="53">
@@ -38638,243 +39307,243 @@
         </is>
       </c>
       <c r="E25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(E$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(E$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="F25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(F$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(F$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="G25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(G$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(G$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="H25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(H$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(H$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="I25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(I$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(I$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="J25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(J$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(J$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="K25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(K$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(K$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="L25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(L$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(L$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="M25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(M$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(M$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="N25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(N$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(N$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="O25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(O$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(O$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="P25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(P$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(P$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Q25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(Q$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(Q$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="R25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(R$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(R$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="S25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(S$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(S$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="T25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(T$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(T$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="U25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(U$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(U$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="V25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(V$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(V$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="W25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(W$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(W$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="X25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(X$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(X$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Y25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(Y$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(Y$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Z25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(Z$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(Z$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AA25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AA$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AB25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AB$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AC25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AC$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AD25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AD$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AE25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AE$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AF25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AF$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AG25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AG$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AH25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AH$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AI25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AI$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AJ25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AK25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AK$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AL25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AL$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AM25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AM$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AM$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AN25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AN$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AN$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AO25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AO$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AO$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AP25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AP$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AP$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AQ25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AR25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AR$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AR$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AS25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AS$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AS$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AT25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AT$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AT$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AU25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AU$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AU$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AV25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AV$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AV$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AW25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AW$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AW$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AX25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AX$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AX$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AY25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AY$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AY$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AZ25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BA25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BA$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BB25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BB$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BC25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BC$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BD25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BD$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BE25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BE$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BF25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BF$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BG25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BG$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BH25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BH$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BI25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BI$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BJ25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BK25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BK$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BL25" s="10">
-        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BL$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BN25" s="53">
@@ -38910,243 +39579,243 @@
         </is>
       </c>
       <c r="E26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(E$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(E$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="F26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(F$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(F$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="G26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(G$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(G$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="H26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(H$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(H$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="I26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(I$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(I$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="J26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(J$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(J$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="K26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(K$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(K$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="L26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(L$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(L$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="M26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(M$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(M$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="N26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(N$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(N$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="O26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(O$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(O$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="P26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(P$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(P$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Q26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(Q$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(Q$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="R26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(R$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(R$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="S26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(S$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(S$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="T26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(T$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(T$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="U26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(U$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(U$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="V26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(V$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(V$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="W26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(W$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(W$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="X26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(X$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(X$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Y26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(Y$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(Y$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Z26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(Z$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(Z$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AA26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AA$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AB26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AB$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AC26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AC$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AD26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AD$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AE26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AE$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AF26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AF$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AG26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AG$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AH26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AH$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AI26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AI$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AJ26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AK26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AK$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AL26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AL$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AM26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AM$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AM$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AN26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AN$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AN$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AO26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AO$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AO$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AP26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AP$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AP$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AQ26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AR26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AR$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AR$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AS26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AS$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AS$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AT26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AT$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AT$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AU26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AU$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AU$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AV26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AV$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AV$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AW26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AW$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AW$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AX26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AX$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AX$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AY26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AY$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AY$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AZ26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BA26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BA$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BB26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BB$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BC26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BC$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BD26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BD$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BE26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BE$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BF26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BF$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BG26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BG$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BH26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BH$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BI26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BI$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BJ26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BK26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BK$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BL26" s="10">
-        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BL$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BN26" s="53">

--- a/models/Tarnoc_v2_2026-09-07.xlsx
+++ b/models/Tarnoc_v2_2026-09-07.xlsx
@@ -906,7 +906,7 @@
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>3. Build capacity: the assembly partner's contracted volume, plus 1,000 a month per in-house line once it produces (aggressive case only). Own lines are filled first and save the partner's assembly cost.</t>
+          <t>3. Build capacity: the assembly partner's contracted volume, plus 1,000 a month per in-house line once it produces (aggressive case only).</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
     <row r="38">
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Aggressive, EUR10m: 2,800 / 6,900 / 11,700 / 18,800 units, EUR321m revenue in 2030, EBITDA positive from 2027 (EUR5m, then 25m, 49m, 85m), 289 people. EUR9m of capex in Nov 2026 and Jan 2027 for two automated lines; cash low EUR1.0m in January 2027, 90% of the raise used.</t>
+          <t>Aggressive, EUR10m: 2,800 / 6,900 / 11,700 / 18,800 units, EUR321m revenue in 2030, EBITDA positive from 2027 (EUR5m, then 23m, 45m, 80m), 289 people. EUR9m of capex in Nov 2026 and Jan 2027 for two automated lines; cash low EUR1.0m in January 2027, 90% of the raise used.</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
     <row r="56">
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>The in-house saving (EUR258 a unit) is derived from our own line cost plus a 20% partner margin, because nobody has told us what the assembly partner actually charges. If the BOM tiers do not include assembly, the saving is nil.</t>
+          <t>In-house lines add capacity and cost (operators, facility, capex) but the BOM is the same whether the partner or our line builds the unit, so the model gives the lines no cost advantage.</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
     <row r="63">
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>What the assembly partner charges per unit and whether it is inside the BOM tiers, so the in-house saving can be a real number.</t>
+          <t>What the assembly partner charges per unit and whether it is inside the BOM tiers, so building in-house can be given its real saving.</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="D37" s="10">
-        <f>MIN(INDEX('Financial Statements'!$E$40:$BL$40,MATCH(Assumptions!$F$143,'Financial Statements'!$E$3:$BL$3,0)):INDEX('Financial Statements'!$E$40:$BL$40,60))</f>
+        <f>MIN(INDEX('Financial Statements'!$E$40:$BL$40,MATCH(Assumptions!$F$139,'Financial Statements'!$E$3:$BL$3,0)):INDEX('Financial Statements'!$E$40:$BL$40,60))</f>
         <v/>
       </c>
       <c r="J37" s="28" t="inlineStr">
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="D38" s="78">
-        <f>INDEX('Financial Statements'!$E$3:$BL$3,MATCH(D37,INDEX('Financial Statements'!$E$40:$BL$40,MATCH(Assumptions!$F$143,'Financial Statements'!$E$3:$BL$3,0)):INDEX('Financial Statements'!$E$40:$BL$40,60),0)+MATCH(Assumptions!$F$143,'Financial Statements'!$E$3:$BL$3,0)-1)</f>
+        <f>INDEX('Financial Statements'!$E$3:$BL$3,MATCH(D37,INDEX('Financial Statements'!$E$40:$BL$40,MATCH(Assumptions!$F$139,'Financial Statements'!$E$3:$BL$3,0)):INDEX('Financial Statements'!$E$40:$BL$40,60),0)+MATCH(Assumptions!$F$139,'Financial Statements'!$E$3:$BL$3,0)-1)</f>
         <v/>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="D39" s="10">
-        <f>MIN(INDEX('Financial Statements'!$E$40:$BL$40,1):INDEX('Financial Statements'!$E$40:$BL$40,MATCH(Assumptions!$F$143,'Financial Statements'!$E$3:$BL$3,0)-1))</f>
+        <f>MIN(INDEX('Financial Statements'!$E$40:$BL$40,1):INDEX('Financial Statements'!$E$40:$BL$40,MATCH(Assumptions!$F$139,'Financial Statements'!$E$3:$BL$3,0)-1))</f>
         <v/>
       </c>
       <c r="J39" s="28" t="inlineStr">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="D50" s="10">
-        <f>INDEX('Financial Statements'!$E$40:$BL$40,MATCH(Assumptions!$F$143,'Financial Statements'!$E$3:$BL$3,0))</f>
+        <f>INDEX('Financial Statements'!$E$40:$BL$40,MATCH(Assumptions!$F$139,'Financial Statements'!$E$3:$BL$3,0))</f>
         <v/>
       </c>
     </row>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="D52" s="79">
-        <f>IFERROR(D51/SUM(INDEX('Financial Statements'!$E$35:$BL$35,MATCH(Assumptions!$F$143,'Financial Statements'!$E$3:$BL$3,0)):INDEX('Financial Statements'!$E$35:$BL$35,60)),0)</f>
+        <f>IFERROR(D51/SUM(INDEX('Financial Statements'!$E$35:$BL$35,MATCH(Assumptions!$F$139,'Financial Statements'!$E$3:$BL$3,0)):INDEX('Financial Statements'!$E$35:$BL$35,60)),0)</f>
         <v/>
       </c>
       <c r="J52" s="28" t="inlineStr">
@@ -2934,7 +2934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:J146"/>
+  <dimension ref="B1:J142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5646,7 +5646,7 @@
     <row r="123">
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>IN-HOUSE ASSEMBLY  (what building it ourselves saves)</t>
+          <t>OVERHEADS AND OTHER OPERATING COSTS</t>
         </is>
       </c>
       <c r="C123" s="2" t="n"/>
@@ -5684,105 +5684,107 @@
     <row r="125">
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Assembly partner margin on top of its cost</t>
+          <t>Offices and facilities per person</t>
         </is>
       </c>
       <c r="C125" s="26" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D125" s="35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E125" s="35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F125" s="36">
+          <t>EUR/month</t>
+        </is>
+      </c>
+      <c r="D125" s="31" t="n">
+        <v>700</v>
+      </c>
+      <c r="E125" s="31" t="n">
+        <v>700</v>
+      </c>
+      <c r="F125" s="32">
         <f>IF(Assumptions!$E$5=2,E125,D125)</f>
         <v/>
-      </c>
-      <c r="J125" s="28" t="inlineStr">
-        <is>
-          <t>what a contract manufacturer adds to its own cost; the only new number in this block</t>
-        </is>
       </c>
     </row>
     <row r="126">
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Assembly cost inside the BOM, saved on units we build ourselves</t>
+          <t>IT and software per person</t>
         </is>
       </c>
       <c r="C126" s="26" t="inlineStr">
         <is>
-          <t>EUR/unit</t>
-        </is>
+          <t>EUR/month</t>
+        </is>
+      </c>
+      <c r="D126" s="31" t="n">
+        <v>250</v>
+      </c>
+      <c r="E126" s="31" t="n">
+        <v>250</v>
       </c>
       <c r="F126" s="32">
-        <f>(Assumptions!$F$87*Assumptions!$F$118+Assumptions!$F$88)/Assumptions!$F$83*(1+Assumptions!$F$125)</f>
-        <v/>
-      </c>
-      <c r="J126" s="28" t="inlineStr">
-        <is>
-          <t>derived from the model: operators plus facility for one line, per unit at full capacity, plus the partner margin. The BOM tiers are partner-built prices, so an in-house unit saves this</t>
-        </is>
+        <f>IF(Assumptions!$E$5=2,E126,D126)</f>
+        <v/>
       </c>
     </row>
     <row r="127">
-      <c r="B127" s="1" t="inlineStr">
-        <is>
-          <t>OVERHEADS AND OTHER OPERATING COSTS</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n"/>
-      <c r="E127" s="2" t="n"/>
-      <c r="F127" s="2" t="n"/>
-      <c r="G127" s="2" t="n"/>
-      <c r="H127" s="2" t="n"/>
-      <c r="I127" s="2" t="n"/>
-      <c r="J127" s="2" t="n"/>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>Travel per person</t>
+        </is>
+      </c>
+      <c r="C127" s="26" t="inlineStr">
+        <is>
+          <t>EUR/month</t>
+        </is>
+      </c>
+      <c r="D127" s="31" t="n">
+        <v>300</v>
+      </c>
+      <c r="E127" s="31" t="n">
+        <v>300</v>
+      </c>
+      <c r="F127" s="32">
+        <f>IF(Assumptions!$E$5=2,E127,D127)</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
-      <c r="B128" s="29" t="n"/>
-      <c r="C128" s="29" t="n"/>
-      <c r="D128" s="30" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="E128" s="30" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-      <c r="F128" s="30" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G128" s="29" t="n"/>
-      <c r="H128" s="29" t="n"/>
-      <c r="I128" s="29" t="n"/>
-      <c r="J128" s="29" t="n"/>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>Recruitment per net new hire</t>
+        </is>
+      </c>
+      <c r="C128" s="26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D128" s="31" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E128" s="31" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F128" s="32">
+        <f>IF(Assumptions!$E$5=2,E128,D128)</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>Offices and facilities per person</t>
+          <t>Installer training and demo unit per new partner</t>
         </is>
       </c>
       <c r="C129" s="26" t="inlineStr">
         <is>
-          <t>EUR/month</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D129" s="31" t="n">
-        <v>700</v>
+        <v>3500</v>
       </c>
       <c r="E129" s="31" t="n">
-        <v>700</v>
+        <v>3500</v>
       </c>
       <c r="F129" s="32">
         <f>IF(Assumptions!$E$5=2,E129,D129)</f>
@@ -5792,7 +5794,7 @@
     <row r="130">
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>IT and software per person</t>
+          <t>Finance and legal</t>
         </is>
       </c>
       <c r="C130" s="26" t="inlineStr">
@@ -5801,10 +5803,10 @@
         </is>
       </c>
       <c r="D130" s="31" t="n">
-        <v>250</v>
+        <v>7000</v>
       </c>
       <c r="E130" s="31" t="n">
-        <v>250</v>
+        <v>7000</v>
       </c>
       <c r="F130" s="32">
         <f>IF(Assumptions!$E$5=2,E130,D130)</f>
@@ -5814,7 +5816,7 @@
     <row r="131">
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>Travel per person</t>
+          <t>Other general</t>
         </is>
       </c>
       <c r="C131" s="26" t="inlineStr">
@@ -5823,10 +5825,10 @@
         </is>
       </c>
       <c r="D131" s="31" t="n">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="E131" s="31" t="n">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="F131" s="32">
         <f>IF(Assumptions!$E$5=2,E131,D131)</f>
@@ -5836,12 +5838,12 @@
     <row r="132">
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Recruitment per net new hire</t>
+          <t>Ongoing development</t>
         </is>
       </c>
       <c r="C132" s="26" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>EUR/month</t>
         </is>
       </c>
       <c r="D132" s="31" t="n">
@@ -5858,19 +5860,19 @@
     <row r="133">
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>Installer training and demo unit per new partner</t>
+          <t>Third party product development</t>
         </is>
       </c>
       <c r="C133" s="26" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>EUR/month</t>
         </is>
       </c>
       <c r="D133" s="31" t="n">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="E133" s="31" t="n">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="F133" s="32">
         <f>IF(Assumptions!$E$5=2,E133,D133)</f>
@@ -5880,87 +5882,81 @@
     <row r="134">
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>Finance and legal</t>
+          <t>Annual increase on the costs above</t>
         </is>
       </c>
       <c r="C134" s="26" t="inlineStr">
         <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D134" s="31" t="n">
-        <v>7000</v>
-      </c>
-      <c r="E134" s="31" t="n">
-        <v>7000</v>
-      </c>
-      <c r="F134" s="32">
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D134" s="35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E134" s="35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F134" s="36">
         <f>IF(Assumptions!$E$5=2,E134,D134)</f>
         <v/>
       </c>
     </row>
     <row r="135">
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>Other general</t>
-        </is>
-      </c>
-      <c r="C135" s="26" t="inlineStr">
-        <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D135" s="31" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E135" s="31" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F135" s="32">
-        <f>IF(Assumptions!$E$5=2,E135,D135)</f>
-        <v/>
-      </c>
+      <c r="B135" s="1" t="inlineStr">
+        <is>
+          <t>FUNDING</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n"/>
+      <c r="E135" s="2" t="n"/>
+      <c r="F135" s="2" t="n"/>
+      <c r="G135" s="2" t="n"/>
+      <c r="H135" s="2" t="n"/>
+      <c r="I135" s="2" t="n"/>
+      <c r="J135" s="2" t="n"/>
     </row>
     <row r="136">
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>Ongoing development</t>
-        </is>
-      </c>
-      <c r="C136" s="26" t="inlineStr">
-        <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D136" s="31" t="n">
-        <v>8000</v>
-      </c>
-      <c r="E136" s="31" t="n">
-        <v>8000</v>
-      </c>
-      <c r="F136" s="32">
-        <f>IF(Assumptions!$E$5=2,E136,D136)</f>
-        <v/>
-      </c>
+      <c r="B136" s="29" t="n"/>
+      <c r="C136" s="29" t="n"/>
+      <c r="D136" s="30" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E136" s="30" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="F136" s="30" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G136" s="29" t="n"/>
+      <c r="H136" s="29" t="n"/>
+      <c r="I136" s="29" t="n"/>
+      <c r="J136" s="29" t="n"/>
     </row>
     <row r="137">
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Third party product development</t>
+          <t>First round, money in</t>
         </is>
       </c>
       <c r="C137" s="26" t="inlineStr">
         <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D137" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E137" s="31" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F137" s="32">
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D137" s="37" t="n">
+        <v>46143</v>
+      </c>
+      <c r="E137" s="37" t="n">
+        <v>46143</v>
+      </c>
+      <c r="F137" s="38">
         <f>IF(Assumptions!$E$5=2,E137,D137)</f>
         <v/>
       </c>
@@ -5968,81 +5964,92 @@
     <row r="138">
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Annual increase on the costs above</t>
+          <t>First round, amount</t>
         </is>
       </c>
       <c r="C138" s="26" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D138" s="35" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E138" s="35" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F138" s="36">
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D138" s="31" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E138" s="31" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F138" s="32">
         <f>IF(Assumptions!$E$5=2,E138,D138)</f>
         <v/>
       </c>
     </row>
     <row r="139">
-      <c r="B139" s="1" t="inlineStr">
-        <is>
-          <t>FUNDING</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n"/>
-      <c r="E139" s="2" t="n"/>
-      <c r="F139" s="2" t="n"/>
-      <c r="G139" s="2" t="n"/>
-      <c r="H139" s="2" t="n"/>
-      <c r="I139" s="2" t="n"/>
-      <c r="J139" s="2" t="n"/>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>Second round, money in</t>
+        </is>
+      </c>
+      <c r="C139" s="26" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D139" s="37" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E139" s="37" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F139" s="38">
+        <f>IF(Assumptions!$E$5=2,E139,D139)</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
-      <c r="B140" s="29" t="n"/>
-      <c r="C140" s="29" t="n"/>
-      <c r="D140" s="30" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="E140" s="30" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-      <c r="F140" s="30" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G140" s="29" t="n"/>
-      <c r="H140" s="29" t="n"/>
-      <c r="I140" s="29" t="n"/>
-      <c r="J140" s="29" t="n"/>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>Second round, amount</t>
+        </is>
+      </c>
+      <c r="C140" s="26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D140" s="31" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E140" s="31" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F140" s="32">
+        <f>IF(Assumptions!$E$5=2,E140,D140)</f>
+        <v/>
+      </c>
+      <c r="J140" s="28" t="inlineStr">
+        <is>
+          <t>this is the raise the model is built to justify</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>First round, money in</t>
+          <t>Convertible loan drawn</t>
         </is>
       </c>
       <c r="C141" s="26" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D141" s="37" t="n">
-        <v>46143</v>
-      </c>
-      <c r="E141" s="37" t="n">
-        <v>46143</v>
-      </c>
-      <c r="F141" s="38">
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D141" s="31" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E141" s="31" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F141" s="32">
         <f>IF(Assumptions!$E$5=2,E141,D141)</f>
         <v/>
       </c>
@@ -6050,115 +6057,22 @@
     <row r="142">
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>First round, amount</t>
+          <t>Loan drawn on</t>
         </is>
       </c>
       <c r="C142" s="26" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D142" s="31" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E142" s="31" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F142" s="32">
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D142" s="37" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E142" s="37" t="n">
+        <v>46204</v>
+      </c>
+      <c r="F142" s="38">
         <f>IF(Assumptions!$E$5=2,E142,D142)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="143">
-      <c r="B143" s="6" t="inlineStr">
-        <is>
-          <t>Second round, money in</t>
-        </is>
-      </c>
-      <c r="C143" s="26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D143" s="37" t="n">
-        <v>46296</v>
-      </c>
-      <c r="E143" s="37" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F143" s="38">
-        <f>IF(Assumptions!$E$5=2,E143,D143)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144">
-      <c r="B144" s="6" t="inlineStr">
-        <is>
-          <t>Second round, amount</t>
-        </is>
-      </c>
-      <c r="C144" s="26" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D144" s="31" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="E144" s="31" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="F144" s="32">
-        <f>IF(Assumptions!$E$5=2,E144,D144)</f>
-        <v/>
-      </c>
-      <c r="J144" s="28" t="inlineStr">
-        <is>
-          <t>this is the raise the model is built to justify</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="B145" s="6" t="inlineStr">
-        <is>
-          <t>Convertible loan drawn</t>
-        </is>
-      </c>
-      <c r="C145" s="26" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D145" s="31" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E145" s="31" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F145" s="32">
-        <f>IF(Assumptions!$E$5=2,E145,D145)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146">
-      <c r="B146" s="6" t="inlineStr">
-        <is>
-          <t>Loan drawn on</t>
-        </is>
-      </c>
-      <c r="C146" s="26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D146" s="37" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E146" s="37" t="n">
-        <v>46204</v>
-      </c>
-      <c r="F146" s="38">
-        <f>IF(Assumptions!$E$5=2,E146,D146)</f>
         <v/>
       </c>
     </row>
@@ -6900,243 +6814,243 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>-COGS!E20</f>
+        <f>-COGS!E19</f>
         <v/>
       </c>
       <c r="F7" s="10">
-        <f>-COGS!F20</f>
+        <f>-COGS!F19</f>
         <v/>
       </c>
       <c r="G7" s="10">
-        <f>-COGS!G20</f>
+        <f>-COGS!G19</f>
         <v/>
       </c>
       <c r="H7" s="10">
-        <f>-COGS!H20</f>
+        <f>-COGS!H19</f>
         <v/>
       </c>
       <c r="I7" s="10">
-        <f>-COGS!I20</f>
+        <f>-COGS!I19</f>
         <v/>
       </c>
       <c r="J7" s="10">
-        <f>-COGS!J20</f>
+        <f>-COGS!J19</f>
         <v/>
       </c>
       <c r="K7" s="10">
-        <f>-COGS!K20</f>
+        <f>-COGS!K19</f>
         <v/>
       </c>
       <c r="L7" s="10">
-        <f>-COGS!L20</f>
+        <f>-COGS!L19</f>
         <v/>
       </c>
       <c r="M7" s="10">
-        <f>-COGS!M20</f>
+        <f>-COGS!M19</f>
         <v/>
       </c>
       <c r="N7" s="10">
-        <f>-COGS!N20</f>
+        <f>-COGS!N19</f>
         <v/>
       </c>
       <c r="O7" s="10">
-        <f>-COGS!O20</f>
+        <f>-COGS!O19</f>
         <v/>
       </c>
       <c r="P7" s="10">
-        <f>-COGS!P20</f>
+        <f>-COGS!P19</f>
         <v/>
       </c>
       <c r="Q7" s="10">
-        <f>-COGS!Q20</f>
+        <f>-COGS!Q19</f>
         <v/>
       </c>
       <c r="R7" s="10">
-        <f>-COGS!R20</f>
+        <f>-COGS!R19</f>
         <v/>
       </c>
       <c r="S7" s="10">
-        <f>-COGS!S20</f>
+        <f>-COGS!S19</f>
         <v/>
       </c>
       <c r="T7" s="10">
-        <f>-COGS!T20</f>
+        <f>-COGS!T19</f>
         <v/>
       </c>
       <c r="U7" s="10">
-        <f>-COGS!U20</f>
+        <f>-COGS!U19</f>
         <v/>
       </c>
       <c r="V7" s="10">
-        <f>-COGS!V20</f>
+        <f>-COGS!V19</f>
         <v/>
       </c>
       <c r="W7" s="10">
-        <f>-COGS!W20</f>
+        <f>-COGS!W19</f>
         <v/>
       </c>
       <c r="X7" s="10">
-        <f>-COGS!X20</f>
+        <f>-COGS!X19</f>
         <v/>
       </c>
       <c r="Y7" s="10">
-        <f>-COGS!Y20</f>
+        <f>-COGS!Y19</f>
         <v/>
       </c>
       <c r="Z7" s="10">
-        <f>-COGS!Z20</f>
+        <f>-COGS!Z19</f>
         <v/>
       </c>
       <c r="AA7" s="10">
-        <f>-COGS!AA20</f>
+        <f>-COGS!AA19</f>
         <v/>
       </c>
       <c r="AB7" s="10">
-        <f>-COGS!AB20</f>
+        <f>-COGS!AB19</f>
         <v/>
       </c>
       <c r="AC7" s="10">
-        <f>-COGS!AC20</f>
+        <f>-COGS!AC19</f>
         <v/>
       </c>
       <c r="AD7" s="10">
-        <f>-COGS!AD20</f>
+        <f>-COGS!AD19</f>
         <v/>
       </c>
       <c r="AE7" s="10">
-        <f>-COGS!AE20</f>
+        <f>-COGS!AE19</f>
         <v/>
       </c>
       <c r="AF7" s="10">
-        <f>-COGS!AF20</f>
+        <f>-COGS!AF19</f>
         <v/>
       </c>
       <c r="AG7" s="10">
-        <f>-COGS!AG20</f>
+        <f>-COGS!AG19</f>
         <v/>
       </c>
       <c r="AH7" s="10">
-        <f>-COGS!AH20</f>
+        <f>-COGS!AH19</f>
         <v/>
       </c>
       <c r="AI7" s="10">
-        <f>-COGS!AI20</f>
+        <f>-COGS!AI19</f>
         <v/>
       </c>
       <c r="AJ7" s="10">
-        <f>-COGS!AJ20</f>
+        <f>-COGS!AJ19</f>
         <v/>
       </c>
       <c r="AK7" s="10">
-        <f>-COGS!AK20</f>
+        <f>-COGS!AK19</f>
         <v/>
       </c>
       <c r="AL7" s="10">
-        <f>-COGS!AL20</f>
+        <f>-COGS!AL19</f>
         <v/>
       </c>
       <c r="AM7" s="10">
-        <f>-COGS!AM20</f>
+        <f>-COGS!AM19</f>
         <v/>
       </c>
       <c r="AN7" s="10">
-        <f>-COGS!AN20</f>
+        <f>-COGS!AN19</f>
         <v/>
       </c>
       <c r="AO7" s="10">
-        <f>-COGS!AO20</f>
+        <f>-COGS!AO19</f>
         <v/>
       </c>
       <c r="AP7" s="10">
-        <f>-COGS!AP20</f>
+        <f>-COGS!AP19</f>
         <v/>
       </c>
       <c r="AQ7" s="10">
-        <f>-COGS!AQ20</f>
+        <f>-COGS!AQ19</f>
         <v/>
       </c>
       <c r="AR7" s="10">
-        <f>-COGS!AR20</f>
+        <f>-COGS!AR19</f>
         <v/>
       </c>
       <c r="AS7" s="10">
-        <f>-COGS!AS20</f>
+        <f>-COGS!AS19</f>
         <v/>
       </c>
       <c r="AT7" s="10">
-        <f>-COGS!AT20</f>
+        <f>-COGS!AT19</f>
         <v/>
       </c>
       <c r="AU7" s="10">
-        <f>-COGS!AU20</f>
+        <f>-COGS!AU19</f>
         <v/>
       </c>
       <c r="AV7" s="10">
-        <f>-COGS!AV20</f>
+        <f>-COGS!AV19</f>
         <v/>
       </c>
       <c r="AW7" s="10">
-        <f>-COGS!AW20</f>
+        <f>-COGS!AW19</f>
         <v/>
       </c>
       <c r="AX7" s="10">
-        <f>-COGS!AX20</f>
+        <f>-COGS!AX19</f>
         <v/>
       </c>
       <c r="AY7" s="10">
-        <f>-COGS!AY20</f>
+        <f>-COGS!AY19</f>
         <v/>
       </c>
       <c r="AZ7" s="10">
-        <f>-COGS!AZ20</f>
+        <f>-COGS!AZ19</f>
         <v/>
       </c>
       <c r="BA7" s="10">
-        <f>-COGS!BA20</f>
+        <f>-COGS!BA19</f>
         <v/>
       </c>
       <c r="BB7" s="10">
-        <f>-COGS!BB20</f>
+        <f>-COGS!BB19</f>
         <v/>
       </c>
       <c r="BC7" s="10">
-        <f>-COGS!BC20</f>
+        <f>-COGS!BC19</f>
         <v/>
       </c>
       <c r="BD7" s="10">
-        <f>-COGS!BD20</f>
+        <f>-COGS!BD19</f>
         <v/>
       </c>
       <c r="BE7" s="10">
-        <f>-COGS!BE20</f>
+        <f>-COGS!BE19</f>
         <v/>
       </c>
       <c r="BF7" s="10">
-        <f>-COGS!BF20</f>
+        <f>-COGS!BF19</f>
         <v/>
       </c>
       <c r="BG7" s="10">
-        <f>-COGS!BG20</f>
+        <f>-COGS!BG19</f>
         <v/>
       </c>
       <c r="BH7" s="10">
-        <f>-COGS!BH20</f>
+        <f>-COGS!BH19</f>
         <v/>
       </c>
       <c r="BI7" s="10">
-        <f>-COGS!BI20</f>
+        <f>-COGS!BI19</f>
         <v/>
       </c>
       <c r="BJ7" s="10">
-        <f>-COGS!BJ20</f>
+        <f>-COGS!BJ19</f>
         <v/>
       </c>
       <c r="BK7" s="10">
-        <f>-COGS!BK20</f>
+        <f>-COGS!BK19</f>
         <v/>
       </c>
       <c r="BL7" s="10">
-        <f>-COGS!BL20</f>
+        <f>-COGS!BL19</f>
         <v/>
       </c>
       <c r="BN7" s="53">
@@ -13251,243 +13165,243 @@
         </is>
       </c>
       <c r="E35" s="10">
-        <f>IF(AND(YEAR(E$3)=YEAR(Assumptions!$F$141),MONTH(E$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(E$3)=YEAR(Assumptions!$F$143),MONTH(E$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(E$3)=YEAR(Assumptions!$F$137),MONTH(E$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(E$3)=YEAR(Assumptions!$F$139),MONTH(E$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="F35" s="10">
-        <f>IF(AND(YEAR(F$3)=YEAR(Assumptions!$F$141),MONTH(F$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(F$3)=YEAR(Assumptions!$F$143),MONTH(F$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(F$3)=YEAR(Assumptions!$F$137),MONTH(F$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(F$3)=YEAR(Assumptions!$F$139),MONTH(F$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="G35" s="10">
-        <f>IF(AND(YEAR(G$3)=YEAR(Assumptions!$F$141),MONTH(G$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(G$3)=YEAR(Assumptions!$F$143),MONTH(G$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(G$3)=YEAR(Assumptions!$F$137),MONTH(G$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(G$3)=YEAR(Assumptions!$F$139),MONTH(G$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="H35" s="10">
-        <f>IF(AND(YEAR(H$3)=YEAR(Assumptions!$F$141),MONTH(H$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(H$3)=YEAR(Assumptions!$F$143),MONTH(H$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(H$3)=YEAR(Assumptions!$F$137),MONTH(H$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(H$3)=YEAR(Assumptions!$F$139),MONTH(H$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="I35" s="10">
-        <f>IF(AND(YEAR(I$3)=YEAR(Assumptions!$F$141),MONTH(I$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(I$3)=YEAR(Assumptions!$F$143),MONTH(I$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(I$3)=YEAR(Assumptions!$F$137),MONTH(I$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(I$3)=YEAR(Assumptions!$F$139),MONTH(I$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="J35" s="10">
-        <f>IF(AND(YEAR(J$3)=YEAR(Assumptions!$F$141),MONTH(J$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(J$3)=YEAR(Assumptions!$F$143),MONTH(J$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(J$3)=YEAR(Assumptions!$F$137),MONTH(J$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(J$3)=YEAR(Assumptions!$F$139),MONTH(J$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="K35" s="10">
-        <f>IF(AND(YEAR(K$3)=YEAR(Assumptions!$F$141),MONTH(K$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(K$3)=YEAR(Assumptions!$F$143),MONTH(K$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(K$3)=YEAR(Assumptions!$F$137),MONTH(K$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(K$3)=YEAR(Assumptions!$F$139),MONTH(K$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="L35" s="10">
-        <f>IF(AND(YEAR(L$3)=YEAR(Assumptions!$F$141),MONTH(L$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(L$3)=YEAR(Assumptions!$F$143),MONTH(L$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(L$3)=YEAR(Assumptions!$F$137),MONTH(L$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(L$3)=YEAR(Assumptions!$F$139),MONTH(L$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="M35" s="10">
-        <f>IF(AND(YEAR(M$3)=YEAR(Assumptions!$F$141),MONTH(M$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(M$3)=YEAR(Assumptions!$F$143),MONTH(M$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(M$3)=YEAR(Assumptions!$F$137),MONTH(M$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(M$3)=YEAR(Assumptions!$F$139),MONTH(M$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="N35" s="10">
-        <f>IF(AND(YEAR(N$3)=YEAR(Assumptions!$F$141),MONTH(N$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(N$3)=YEAR(Assumptions!$F$143),MONTH(N$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(N$3)=YEAR(Assumptions!$F$137),MONTH(N$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(N$3)=YEAR(Assumptions!$F$139),MONTH(N$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="O35" s="10">
-        <f>IF(AND(YEAR(O$3)=YEAR(Assumptions!$F$141),MONTH(O$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(O$3)=YEAR(Assumptions!$F$143),MONTH(O$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(O$3)=YEAR(Assumptions!$F$137),MONTH(O$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(O$3)=YEAR(Assumptions!$F$139),MONTH(O$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="P35" s="10">
-        <f>IF(AND(YEAR(P$3)=YEAR(Assumptions!$F$141),MONTH(P$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(P$3)=YEAR(Assumptions!$F$143),MONTH(P$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(P$3)=YEAR(Assumptions!$F$137),MONTH(P$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(P$3)=YEAR(Assumptions!$F$139),MONTH(P$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="Q35" s="10">
-        <f>IF(AND(YEAR(Q$3)=YEAR(Assumptions!$F$141),MONTH(Q$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(Q$3)=YEAR(Assumptions!$F$143),MONTH(Q$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(Q$3)=YEAR(Assumptions!$F$137),MONTH(Q$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(Q$3)=YEAR(Assumptions!$F$139),MONTH(Q$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="R35" s="10">
-        <f>IF(AND(YEAR(R$3)=YEAR(Assumptions!$F$141),MONTH(R$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(R$3)=YEAR(Assumptions!$F$143),MONTH(R$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(R$3)=YEAR(Assumptions!$F$137),MONTH(R$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(R$3)=YEAR(Assumptions!$F$139),MONTH(R$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="S35" s="10">
-        <f>IF(AND(YEAR(S$3)=YEAR(Assumptions!$F$141),MONTH(S$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(S$3)=YEAR(Assumptions!$F$143),MONTH(S$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(S$3)=YEAR(Assumptions!$F$137),MONTH(S$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(S$3)=YEAR(Assumptions!$F$139),MONTH(S$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="T35" s="10">
-        <f>IF(AND(YEAR(T$3)=YEAR(Assumptions!$F$141),MONTH(T$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(T$3)=YEAR(Assumptions!$F$143),MONTH(T$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(T$3)=YEAR(Assumptions!$F$137),MONTH(T$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(T$3)=YEAR(Assumptions!$F$139),MONTH(T$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="U35" s="10">
-        <f>IF(AND(YEAR(U$3)=YEAR(Assumptions!$F$141),MONTH(U$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(U$3)=YEAR(Assumptions!$F$143),MONTH(U$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(U$3)=YEAR(Assumptions!$F$137),MONTH(U$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(U$3)=YEAR(Assumptions!$F$139),MONTH(U$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="V35" s="10">
-        <f>IF(AND(YEAR(V$3)=YEAR(Assumptions!$F$141),MONTH(V$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(V$3)=YEAR(Assumptions!$F$143),MONTH(V$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(V$3)=YEAR(Assumptions!$F$137),MONTH(V$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(V$3)=YEAR(Assumptions!$F$139),MONTH(V$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="W35" s="10">
-        <f>IF(AND(YEAR(W$3)=YEAR(Assumptions!$F$141),MONTH(W$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(W$3)=YEAR(Assumptions!$F$143),MONTH(W$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(W$3)=YEAR(Assumptions!$F$137),MONTH(W$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(W$3)=YEAR(Assumptions!$F$139),MONTH(W$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="X35" s="10">
-        <f>IF(AND(YEAR(X$3)=YEAR(Assumptions!$F$141),MONTH(X$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(X$3)=YEAR(Assumptions!$F$143),MONTH(X$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(X$3)=YEAR(Assumptions!$F$137),MONTH(X$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(X$3)=YEAR(Assumptions!$F$139),MONTH(X$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="Y35" s="10">
-        <f>IF(AND(YEAR(Y$3)=YEAR(Assumptions!$F$141),MONTH(Y$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(Y$3)=YEAR(Assumptions!$F$143),MONTH(Y$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(Y$3)=YEAR(Assumptions!$F$137),MONTH(Y$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(Y$3)=YEAR(Assumptions!$F$139),MONTH(Y$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="Z35" s="10">
-        <f>IF(AND(YEAR(Z$3)=YEAR(Assumptions!$F$141),MONTH(Z$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(Z$3)=YEAR(Assumptions!$F$143),MONTH(Z$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(Z$3)=YEAR(Assumptions!$F$137),MONTH(Z$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(Z$3)=YEAR(Assumptions!$F$139),MONTH(Z$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AA35" s="10">
-        <f>IF(AND(YEAR(AA$3)=YEAR(Assumptions!$F$141),MONTH(AA$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AA$3)=YEAR(Assumptions!$F$143),MONTH(AA$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AA$3)=YEAR(Assumptions!$F$137),MONTH(AA$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AA$3)=YEAR(Assumptions!$F$139),MONTH(AA$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AB35" s="10">
-        <f>IF(AND(YEAR(AB$3)=YEAR(Assumptions!$F$141),MONTH(AB$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AB$3)=YEAR(Assumptions!$F$143),MONTH(AB$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AB$3)=YEAR(Assumptions!$F$137),MONTH(AB$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AB$3)=YEAR(Assumptions!$F$139),MONTH(AB$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AC35" s="10">
-        <f>IF(AND(YEAR(AC$3)=YEAR(Assumptions!$F$141),MONTH(AC$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AC$3)=YEAR(Assumptions!$F$143),MONTH(AC$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AC$3)=YEAR(Assumptions!$F$137),MONTH(AC$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AC$3)=YEAR(Assumptions!$F$139),MONTH(AC$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AD35" s="10">
-        <f>IF(AND(YEAR(AD$3)=YEAR(Assumptions!$F$141),MONTH(AD$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AD$3)=YEAR(Assumptions!$F$143),MONTH(AD$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AD$3)=YEAR(Assumptions!$F$137),MONTH(AD$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AD$3)=YEAR(Assumptions!$F$139),MONTH(AD$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AE35" s="10">
-        <f>IF(AND(YEAR(AE$3)=YEAR(Assumptions!$F$141),MONTH(AE$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AE$3)=YEAR(Assumptions!$F$143),MONTH(AE$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AE$3)=YEAR(Assumptions!$F$137),MONTH(AE$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AE$3)=YEAR(Assumptions!$F$139),MONTH(AE$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AF35" s="10">
-        <f>IF(AND(YEAR(AF$3)=YEAR(Assumptions!$F$141),MONTH(AF$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AF$3)=YEAR(Assumptions!$F$143),MONTH(AF$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AF$3)=YEAR(Assumptions!$F$137),MONTH(AF$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AF$3)=YEAR(Assumptions!$F$139),MONTH(AF$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AG35" s="10">
-        <f>IF(AND(YEAR(AG$3)=YEAR(Assumptions!$F$141),MONTH(AG$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AG$3)=YEAR(Assumptions!$F$143),MONTH(AG$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AG$3)=YEAR(Assumptions!$F$137),MONTH(AG$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AG$3)=YEAR(Assumptions!$F$139),MONTH(AG$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AH35" s="10">
-        <f>IF(AND(YEAR(AH$3)=YEAR(Assumptions!$F$141),MONTH(AH$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AH$3)=YEAR(Assumptions!$F$143),MONTH(AH$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AH$3)=YEAR(Assumptions!$F$137),MONTH(AH$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AH$3)=YEAR(Assumptions!$F$139),MONTH(AH$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AI35" s="10">
-        <f>IF(AND(YEAR(AI$3)=YEAR(Assumptions!$F$141),MONTH(AI$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AI$3)=YEAR(Assumptions!$F$143),MONTH(AI$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AI$3)=YEAR(Assumptions!$F$137),MONTH(AI$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AI$3)=YEAR(Assumptions!$F$139),MONTH(AI$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AJ35" s="10">
-        <f>IF(AND(YEAR(AJ$3)=YEAR(Assumptions!$F$141),MONTH(AJ$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AJ$3)=YEAR(Assumptions!$F$143),MONTH(AJ$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AJ$3)=YEAR(Assumptions!$F$137),MONTH(AJ$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AJ$3)=YEAR(Assumptions!$F$139),MONTH(AJ$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AK35" s="10">
-        <f>IF(AND(YEAR(AK$3)=YEAR(Assumptions!$F$141),MONTH(AK$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AK$3)=YEAR(Assumptions!$F$143),MONTH(AK$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AK$3)=YEAR(Assumptions!$F$137),MONTH(AK$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AK$3)=YEAR(Assumptions!$F$139),MONTH(AK$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AL35" s="10">
-        <f>IF(AND(YEAR(AL$3)=YEAR(Assumptions!$F$141),MONTH(AL$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AL$3)=YEAR(Assumptions!$F$143),MONTH(AL$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AL$3)=YEAR(Assumptions!$F$137),MONTH(AL$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AL$3)=YEAR(Assumptions!$F$139),MONTH(AL$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AM35" s="10">
-        <f>IF(AND(YEAR(AM$3)=YEAR(Assumptions!$F$141),MONTH(AM$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AM$3)=YEAR(Assumptions!$F$143),MONTH(AM$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AM$3)=YEAR(Assumptions!$F$137),MONTH(AM$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AM$3)=YEAR(Assumptions!$F$139),MONTH(AM$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AN35" s="10">
-        <f>IF(AND(YEAR(AN$3)=YEAR(Assumptions!$F$141),MONTH(AN$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AN$3)=YEAR(Assumptions!$F$143),MONTH(AN$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AN$3)=YEAR(Assumptions!$F$137),MONTH(AN$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AN$3)=YEAR(Assumptions!$F$139),MONTH(AN$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AO35" s="10">
-        <f>IF(AND(YEAR(AO$3)=YEAR(Assumptions!$F$141),MONTH(AO$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AO$3)=YEAR(Assumptions!$F$143),MONTH(AO$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AO$3)=YEAR(Assumptions!$F$137),MONTH(AO$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AO$3)=YEAR(Assumptions!$F$139),MONTH(AO$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AP35" s="10">
-        <f>IF(AND(YEAR(AP$3)=YEAR(Assumptions!$F$141),MONTH(AP$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AP$3)=YEAR(Assumptions!$F$143),MONTH(AP$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AP$3)=YEAR(Assumptions!$F$137),MONTH(AP$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AP$3)=YEAR(Assumptions!$F$139),MONTH(AP$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AQ35" s="10">
-        <f>IF(AND(YEAR(AQ$3)=YEAR(Assumptions!$F$141),MONTH(AQ$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AQ$3)=YEAR(Assumptions!$F$143),MONTH(AQ$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AQ$3)=YEAR(Assumptions!$F$137),MONTH(AQ$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AQ$3)=YEAR(Assumptions!$F$139),MONTH(AQ$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AR35" s="10">
-        <f>IF(AND(YEAR(AR$3)=YEAR(Assumptions!$F$141),MONTH(AR$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AR$3)=YEAR(Assumptions!$F$143),MONTH(AR$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AR$3)=YEAR(Assumptions!$F$137),MONTH(AR$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AR$3)=YEAR(Assumptions!$F$139),MONTH(AR$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AS35" s="10">
-        <f>IF(AND(YEAR(AS$3)=YEAR(Assumptions!$F$141),MONTH(AS$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AS$3)=YEAR(Assumptions!$F$143),MONTH(AS$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AS$3)=YEAR(Assumptions!$F$137),MONTH(AS$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AS$3)=YEAR(Assumptions!$F$139),MONTH(AS$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AT35" s="10">
-        <f>IF(AND(YEAR(AT$3)=YEAR(Assumptions!$F$141),MONTH(AT$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AT$3)=YEAR(Assumptions!$F$143),MONTH(AT$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AT$3)=YEAR(Assumptions!$F$137),MONTH(AT$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AT$3)=YEAR(Assumptions!$F$139),MONTH(AT$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AU35" s="10">
-        <f>IF(AND(YEAR(AU$3)=YEAR(Assumptions!$F$141),MONTH(AU$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AU$3)=YEAR(Assumptions!$F$143),MONTH(AU$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AU$3)=YEAR(Assumptions!$F$137),MONTH(AU$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AU$3)=YEAR(Assumptions!$F$139),MONTH(AU$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AV35" s="10">
-        <f>IF(AND(YEAR(AV$3)=YEAR(Assumptions!$F$141),MONTH(AV$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AV$3)=YEAR(Assumptions!$F$143),MONTH(AV$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AV$3)=YEAR(Assumptions!$F$137),MONTH(AV$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AV$3)=YEAR(Assumptions!$F$139),MONTH(AV$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AW35" s="10">
-        <f>IF(AND(YEAR(AW$3)=YEAR(Assumptions!$F$141),MONTH(AW$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AW$3)=YEAR(Assumptions!$F$143),MONTH(AW$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AW$3)=YEAR(Assumptions!$F$137),MONTH(AW$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AW$3)=YEAR(Assumptions!$F$139),MONTH(AW$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AX35" s="10">
-        <f>IF(AND(YEAR(AX$3)=YEAR(Assumptions!$F$141),MONTH(AX$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AX$3)=YEAR(Assumptions!$F$143),MONTH(AX$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AX$3)=YEAR(Assumptions!$F$137),MONTH(AX$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AX$3)=YEAR(Assumptions!$F$139),MONTH(AX$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AY35" s="10">
-        <f>IF(AND(YEAR(AY$3)=YEAR(Assumptions!$F$141),MONTH(AY$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AY$3)=YEAR(Assumptions!$F$143),MONTH(AY$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AY$3)=YEAR(Assumptions!$F$137),MONTH(AY$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AY$3)=YEAR(Assumptions!$F$139),MONTH(AY$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="AZ35" s="10">
-        <f>IF(AND(YEAR(AZ$3)=YEAR(Assumptions!$F$141),MONTH(AZ$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(AZ$3)=YEAR(Assumptions!$F$143),MONTH(AZ$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(AZ$3)=YEAR(Assumptions!$F$137),MONTH(AZ$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(AZ$3)=YEAR(Assumptions!$F$139),MONTH(AZ$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="BA35" s="10">
-        <f>IF(AND(YEAR(BA$3)=YEAR(Assumptions!$F$141),MONTH(BA$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BA$3)=YEAR(Assumptions!$F$143),MONTH(BA$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(BA$3)=YEAR(Assumptions!$F$137),MONTH(BA$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BA$3)=YEAR(Assumptions!$F$139),MONTH(BA$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="BB35" s="10">
-        <f>IF(AND(YEAR(BB$3)=YEAR(Assumptions!$F$141),MONTH(BB$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BB$3)=YEAR(Assumptions!$F$143),MONTH(BB$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(BB$3)=YEAR(Assumptions!$F$137),MONTH(BB$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BB$3)=YEAR(Assumptions!$F$139),MONTH(BB$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="BC35" s="10">
-        <f>IF(AND(YEAR(BC$3)=YEAR(Assumptions!$F$141),MONTH(BC$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BC$3)=YEAR(Assumptions!$F$143),MONTH(BC$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(BC$3)=YEAR(Assumptions!$F$137),MONTH(BC$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BC$3)=YEAR(Assumptions!$F$139),MONTH(BC$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="BD35" s="10">
-        <f>IF(AND(YEAR(BD$3)=YEAR(Assumptions!$F$141),MONTH(BD$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BD$3)=YEAR(Assumptions!$F$143),MONTH(BD$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(BD$3)=YEAR(Assumptions!$F$137),MONTH(BD$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BD$3)=YEAR(Assumptions!$F$139),MONTH(BD$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="BE35" s="10">
-        <f>IF(AND(YEAR(BE$3)=YEAR(Assumptions!$F$141),MONTH(BE$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BE$3)=YEAR(Assumptions!$F$143),MONTH(BE$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(BE$3)=YEAR(Assumptions!$F$137),MONTH(BE$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BE$3)=YEAR(Assumptions!$F$139),MONTH(BE$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="BF35" s="10">
-        <f>IF(AND(YEAR(BF$3)=YEAR(Assumptions!$F$141),MONTH(BF$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BF$3)=YEAR(Assumptions!$F$143),MONTH(BF$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(BF$3)=YEAR(Assumptions!$F$137),MONTH(BF$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BF$3)=YEAR(Assumptions!$F$139),MONTH(BF$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="BG35" s="10">
-        <f>IF(AND(YEAR(BG$3)=YEAR(Assumptions!$F$141),MONTH(BG$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BG$3)=YEAR(Assumptions!$F$143),MONTH(BG$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(BG$3)=YEAR(Assumptions!$F$137),MONTH(BG$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BG$3)=YEAR(Assumptions!$F$139),MONTH(BG$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="BH35" s="10">
-        <f>IF(AND(YEAR(BH$3)=YEAR(Assumptions!$F$141),MONTH(BH$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BH$3)=YEAR(Assumptions!$F$143),MONTH(BH$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(BH$3)=YEAR(Assumptions!$F$137),MONTH(BH$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BH$3)=YEAR(Assumptions!$F$139),MONTH(BH$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="BI35" s="10">
-        <f>IF(AND(YEAR(BI$3)=YEAR(Assumptions!$F$141),MONTH(BI$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BI$3)=YEAR(Assumptions!$F$143),MONTH(BI$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(BI$3)=YEAR(Assumptions!$F$137),MONTH(BI$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BI$3)=YEAR(Assumptions!$F$139),MONTH(BI$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="BJ35" s="10">
-        <f>IF(AND(YEAR(BJ$3)=YEAR(Assumptions!$F$141),MONTH(BJ$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BJ$3)=YEAR(Assumptions!$F$143),MONTH(BJ$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(BJ$3)=YEAR(Assumptions!$F$137),MONTH(BJ$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BJ$3)=YEAR(Assumptions!$F$139),MONTH(BJ$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="BK35" s="10">
-        <f>IF(AND(YEAR(BK$3)=YEAR(Assumptions!$F$141),MONTH(BK$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BK$3)=YEAR(Assumptions!$F$143),MONTH(BK$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(BK$3)=YEAR(Assumptions!$F$137),MONTH(BK$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BK$3)=YEAR(Assumptions!$F$139),MONTH(BK$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="BL35" s="10">
-        <f>IF(AND(YEAR(BL$3)=YEAR(Assumptions!$F$141),MONTH(BL$3)=MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF(AND(YEAR(BL$3)=YEAR(Assumptions!$F$143),MONTH(BL$3)=MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)</f>
+        <f>IF(AND(YEAR(BL$3)=YEAR(Assumptions!$F$137),MONTH(BL$3)=MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF(AND(YEAR(BL$3)=YEAR(Assumptions!$F$139),MONTH(BL$3)=MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)</f>
         <v/>
       </c>
       <c r="BN35" s="53">
@@ -13528,243 +13442,243 @@
         </is>
       </c>
       <c r="E36" s="10">
-        <f>IF(AND(YEAR(E$3)=YEAR(Assumptions!$F$146),MONTH(E$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(E$3)=YEAR(Assumptions!$F$142),MONTH(E$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="F36" s="10">
-        <f>IF(AND(YEAR(F$3)=YEAR(Assumptions!$F$146),MONTH(F$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(F$3)=YEAR(Assumptions!$F$142),MONTH(F$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="G36" s="10">
-        <f>IF(AND(YEAR(G$3)=YEAR(Assumptions!$F$146),MONTH(G$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(G$3)=YEAR(Assumptions!$F$142),MONTH(G$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="H36" s="10">
-        <f>IF(AND(YEAR(H$3)=YEAR(Assumptions!$F$146),MONTH(H$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(H$3)=YEAR(Assumptions!$F$142),MONTH(H$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="I36" s="10">
-        <f>IF(AND(YEAR(I$3)=YEAR(Assumptions!$F$146),MONTH(I$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(I$3)=YEAR(Assumptions!$F$142),MONTH(I$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="J36" s="10">
-        <f>IF(AND(YEAR(J$3)=YEAR(Assumptions!$F$146),MONTH(J$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(J$3)=YEAR(Assumptions!$F$142),MONTH(J$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="K36" s="10">
-        <f>IF(AND(YEAR(K$3)=YEAR(Assumptions!$F$146),MONTH(K$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(K$3)=YEAR(Assumptions!$F$142),MONTH(K$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="L36" s="10">
-        <f>IF(AND(YEAR(L$3)=YEAR(Assumptions!$F$146),MONTH(L$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(L$3)=YEAR(Assumptions!$F$142),MONTH(L$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="M36" s="10">
-        <f>IF(AND(YEAR(M$3)=YEAR(Assumptions!$F$146),MONTH(M$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(M$3)=YEAR(Assumptions!$F$142),MONTH(M$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="N36" s="10">
-        <f>IF(AND(YEAR(N$3)=YEAR(Assumptions!$F$146),MONTH(N$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(N$3)=YEAR(Assumptions!$F$142),MONTH(N$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="O36" s="10">
-        <f>IF(AND(YEAR(O$3)=YEAR(Assumptions!$F$146),MONTH(O$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(O$3)=YEAR(Assumptions!$F$142),MONTH(O$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="P36" s="10">
-        <f>IF(AND(YEAR(P$3)=YEAR(Assumptions!$F$146),MONTH(P$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(P$3)=YEAR(Assumptions!$F$142),MONTH(P$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="Q36" s="10">
-        <f>IF(AND(YEAR(Q$3)=YEAR(Assumptions!$F$146),MONTH(Q$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(Q$3)=YEAR(Assumptions!$F$142),MONTH(Q$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="R36" s="10">
-        <f>IF(AND(YEAR(R$3)=YEAR(Assumptions!$F$146),MONTH(R$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(R$3)=YEAR(Assumptions!$F$142),MONTH(R$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="S36" s="10">
-        <f>IF(AND(YEAR(S$3)=YEAR(Assumptions!$F$146),MONTH(S$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(S$3)=YEAR(Assumptions!$F$142),MONTH(S$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="T36" s="10">
-        <f>IF(AND(YEAR(T$3)=YEAR(Assumptions!$F$146),MONTH(T$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(T$3)=YEAR(Assumptions!$F$142),MONTH(T$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="U36" s="10">
-        <f>IF(AND(YEAR(U$3)=YEAR(Assumptions!$F$146),MONTH(U$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(U$3)=YEAR(Assumptions!$F$142),MONTH(U$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="V36" s="10">
-        <f>IF(AND(YEAR(V$3)=YEAR(Assumptions!$F$146),MONTH(V$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(V$3)=YEAR(Assumptions!$F$142),MONTH(V$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="W36" s="10">
-        <f>IF(AND(YEAR(W$3)=YEAR(Assumptions!$F$146),MONTH(W$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(W$3)=YEAR(Assumptions!$F$142),MONTH(W$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="X36" s="10">
-        <f>IF(AND(YEAR(X$3)=YEAR(Assumptions!$F$146),MONTH(X$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(X$3)=YEAR(Assumptions!$F$142),MONTH(X$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="Y36" s="10">
-        <f>IF(AND(YEAR(Y$3)=YEAR(Assumptions!$F$146),MONTH(Y$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(Y$3)=YEAR(Assumptions!$F$142),MONTH(Y$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="Z36" s="10">
-        <f>IF(AND(YEAR(Z$3)=YEAR(Assumptions!$F$146),MONTH(Z$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(Z$3)=YEAR(Assumptions!$F$142),MONTH(Z$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AA36" s="10">
-        <f>IF(AND(YEAR(AA$3)=YEAR(Assumptions!$F$146),MONTH(AA$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AA$3)=YEAR(Assumptions!$F$142),MONTH(AA$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AB36" s="10">
-        <f>IF(AND(YEAR(AB$3)=YEAR(Assumptions!$F$146),MONTH(AB$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AB$3)=YEAR(Assumptions!$F$142),MONTH(AB$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AC36" s="10">
-        <f>IF(AND(YEAR(AC$3)=YEAR(Assumptions!$F$146),MONTH(AC$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AC$3)=YEAR(Assumptions!$F$142),MONTH(AC$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AD36" s="10">
-        <f>IF(AND(YEAR(AD$3)=YEAR(Assumptions!$F$146),MONTH(AD$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AD$3)=YEAR(Assumptions!$F$142),MONTH(AD$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AE36" s="10">
-        <f>IF(AND(YEAR(AE$3)=YEAR(Assumptions!$F$146),MONTH(AE$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AE$3)=YEAR(Assumptions!$F$142),MONTH(AE$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AF36" s="10">
-        <f>IF(AND(YEAR(AF$3)=YEAR(Assumptions!$F$146),MONTH(AF$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AF$3)=YEAR(Assumptions!$F$142),MONTH(AF$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AG36" s="10">
-        <f>IF(AND(YEAR(AG$3)=YEAR(Assumptions!$F$146),MONTH(AG$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AG$3)=YEAR(Assumptions!$F$142),MONTH(AG$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AH36" s="10">
-        <f>IF(AND(YEAR(AH$3)=YEAR(Assumptions!$F$146),MONTH(AH$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AH$3)=YEAR(Assumptions!$F$142),MONTH(AH$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AI36" s="10">
-        <f>IF(AND(YEAR(AI$3)=YEAR(Assumptions!$F$146),MONTH(AI$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AI$3)=YEAR(Assumptions!$F$142),MONTH(AI$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AJ36" s="10">
-        <f>IF(AND(YEAR(AJ$3)=YEAR(Assumptions!$F$146),MONTH(AJ$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AJ$3)=YEAR(Assumptions!$F$142),MONTH(AJ$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AK36" s="10">
-        <f>IF(AND(YEAR(AK$3)=YEAR(Assumptions!$F$146),MONTH(AK$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AK$3)=YEAR(Assumptions!$F$142),MONTH(AK$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AL36" s="10">
-        <f>IF(AND(YEAR(AL$3)=YEAR(Assumptions!$F$146),MONTH(AL$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AL$3)=YEAR(Assumptions!$F$142),MONTH(AL$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AM36" s="10">
-        <f>IF(AND(YEAR(AM$3)=YEAR(Assumptions!$F$146),MONTH(AM$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AM$3)=YEAR(Assumptions!$F$142),MONTH(AM$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AN36" s="10">
-        <f>IF(AND(YEAR(AN$3)=YEAR(Assumptions!$F$146),MONTH(AN$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AN$3)=YEAR(Assumptions!$F$142),MONTH(AN$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AO36" s="10">
-        <f>IF(AND(YEAR(AO$3)=YEAR(Assumptions!$F$146),MONTH(AO$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AO$3)=YEAR(Assumptions!$F$142),MONTH(AO$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AP36" s="10">
-        <f>IF(AND(YEAR(AP$3)=YEAR(Assumptions!$F$146),MONTH(AP$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AP$3)=YEAR(Assumptions!$F$142),MONTH(AP$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AQ36" s="10">
-        <f>IF(AND(YEAR(AQ$3)=YEAR(Assumptions!$F$146),MONTH(AQ$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AQ$3)=YEAR(Assumptions!$F$142),MONTH(AQ$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AR36" s="10">
-        <f>IF(AND(YEAR(AR$3)=YEAR(Assumptions!$F$146),MONTH(AR$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AR$3)=YEAR(Assumptions!$F$142),MONTH(AR$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AS36" s="10">
-        <f>IF(AND(YEAR(AS$3)=YEAR(Assumptions!$F$146),MONTH(AS$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AS$3)=YEAR(Assumptions!$F$142),MONTH(AS$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AT36" s="10">
-        <f>IF(AND(YEAR(AT$3)=YEAR(Assumptions!$F$146),MONTH(AT$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AT$3)=YEAR(Assumptions!$F$142),MONTH(AT$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AU36" s="10">
-        <f>IF(AND(YEAR(AU$3)=YEAR(Assumptions!$F$146),MONTH(AU$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AU$3)=YEAR(Assumptions!$F$142),MONTH(AU$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AV36" s="10">
-        <f>IF(AND(YEAR(AV$3)=YEAR(Assumptions!$F$146),MONTH(AV$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AV$3)=YEAR(Assumptions!$F$142),MONTH(AV$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AW36" s="10">
-        <f>IF(AND(YEAR(AW$3)=YEAR(Assumptions!$F$146),MONTH(AW$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AW$3)=YEAR(Assumptions!$F$142),MONTH(AW$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AX36" s="10">
-        <f>IF(AND(YEAR(AX$3)=YEAR(Assumptions!$F$146),MONTH(AX$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AX$3)=YEAR(Assumptions!$F$142),MONTH(AX$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AY36" s="10">
-        <f>IF(AND(YEAR(AY$3)=YEAR(Assumptions!$F$146),MONTH(AY$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AY$3)=YEAR(Assumptions!$F$142),MONTH(AY$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="AZ36" s="10">
-        <f>IF(AND(YEAR(AZ$3)=YEAR(Assumptions!$F$146),MONTH(AZ$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(AZ$3)=YEAR(Assumptions!$F$142),MONTH(AZ$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="BA36" s="10">
-        <f>IF(AND(YEAR(BA$3)=YEAR(Assumptions!$F$146),MONTH(BA$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(BA$3)=YEAR(Assumptions!$F$142),MONTH(BA$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="BB36" s="10">
-        <f>IF(AND(YEAR(BB$3)=YEAR(Assumptions!$F$146),MONTH(BB$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(BB$3)=YEAR(Assumptions!$F$142),MONTH(BB$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="BC36" s="10">
-        <f>IF(AND(YEAR(BC$3)=YEAR(Assumptions!$F$146),MONTH(BC$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(BC$3)=YEAR(Assumptions!$F$142),MONTH(BC$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="BD36" s="10">
-        <f>IF(AND(YEAR(BD$3)=YEAR(Assumptions!$F$146),MONTH(BD$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(BD$3)=YEAR(Assumptions!$F$142),MONTH(BD$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="BE36" s="10">
-        <f>IF(AND(YEAR(BE$3)=YEAR(Assumptions!$F$146),MONTH(BE$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(BE$3)=YEAR(Assumptions!$F$142),MONTH(BE$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="BF36" s="10">
-        <f>IF(AND(YEAR(BF$3)=YEAR(Assumptions!$F$146),MONTH(BF$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(BF$3)=YEAR(Assumptions!$F$142),MONTH(BF$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="BG36" s="10">
-        <f>IF(AND(YEAR(BG$3)=YEAR(Assumptions!$F$146),MONTH(BG$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(BG$3)=YEAR(Assumptions!$F$142),MONTH(BG$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="BH36" s="10">
-        <f>IF(AND(YEAR(BH$3)=YEAR(Assumptions!$F$146),MONTH(BH$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(BH$3)=YEAR(Assumptions!$F$142),MONTH(BH$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="BI36" s="10">
-        <f>IF(AND(YEAR(BI$3)=YEAR(Assumptions!$F$146),MONTH(BI$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(BI$3)=YEAR(Assumptions!$F$142),MONTH(BI$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="BJ36" s="10">
-        <f>IF(AND(YEAR(BJ$3)=YEAR(Assumptions!$F$146),MONTH(BJ$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(BJ$3)=YEAR(Assumptions!$F$142),MONTH(BJ$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="BK36" s="10">
-        <f>IF(AND(YEAR(BK$3)=YEAR(Assumptions!$F$146),MONTH(BK$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(BK$3)=YEAR(Assumptions!$F$142),MONTH(BK$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="BL36" s="10">
-        <f>IF(AND(YEAR(BL$3)=YEAR(Assumptions!$F$146),MONTH(BL$3)=MONTH(Assumptions!$F$146)),Assumptions!$F$145,0)</f>
+        <f>IF(AND(YEAR(BL$3)=YEAR(Assumptions!$F$142),MONTH(BL$3)=MONTH(Assumptions!$F$142)),Assumptions!$F$141,0)</f>
         <v/>
       </c>
       <c r="BN36" s="53">
@@ -18782,243 +18696,243 @@
         </is>
       </c>
       <c r="E59" s="61">
-        <f>SUM($E$35:E35)+SUM($E$36:E36)-(IF((YEAR(E$3)*12+MONTH(E$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(E$3)*12+MONTH(E$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(E$3)*12+MONTH(E$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:E35)+SUM($E$36:E36)-(IF((YEAR(E$3)*12+MONTH(E$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(E$3)*12+MONTH(E$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(E$3)*12+MONTH(E$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="F59" s="61">
-        <f>SUM($E$35:F35)+SUM($E$36:F36)-(IF((YEAR(F$3)*12+MONTH(F$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(F$3)*12+MONTH(F$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(F$3)*12+MONTH(F$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:F35)+SUM($E$36:F36)-(IF((YEAR(F$3)*12+MONTH(F$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(F$3)*12+MONTH(F$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(F$3)*12+MONTH(F$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="G59" s="61">
-        <f>SUM($E$35:G35)+SUM($E$36:G36)-(IF((YEAR(G$3)*12+MONTH(G$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(G$3)*12+MONTH(G$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(G$3)*12+MONTH(G$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:G35)+SUM($E$36:G36)-(IF((YEAR(G$3)*12+MONTH(G$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(G$3)*12+MONTH(G$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(G$3)*12+MONTH(G$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="H59" s="61">
-        <f>SUM($E$35:H35)+SUM($E$36:H36)-(IF((YEAR(H$3)*12+MONTH(H$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(H$3)*12+MONTH(H$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(H$3)*12+MONTH(H$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:H35)+SUM($E$36:H36)-(IF((YEAR(H$3)*12+MONTH(H$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(H$3)*12+MONTH(H$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(H$3)*12+MONTH(H$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="I59" s="61">
-        <f>SUM($E$35:I35)+SUM($E$36:I36)-(IF((YEAR(I$3)*12+MONTH(I$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(I$3)*12+MONTH(I$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(I$3)*12+MONTH(I$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:I35)+SUM($E$36:I36)-(IF((YEAR(I$3)*12+MONTH(I$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(I$3)*12+MONTH(I$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(I$3)*12+MONTH(I$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="J59" s="61">
-        <f>SUM($E$35:J35)+SUM($E$36:J36)-(IF((YEAR(J$3)*12+MONTH(J$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(J$3)*12+MONTH(J$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(J$3)*12+MONTH(J$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:J35)+SUM($E$36:J36)-(IF((YEAR(J$3)*12+MONTH(J$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(J$3)*12+MONTH(J$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(J$3)*12+MONTH(J$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="K59" s="61">
-        <f>SUM($E$35:K35)+SUM($E$36:K36)-(IF((YEAR(K$3)*12+MONTH(K$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(K$3)*12+MONTH(K$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(K$3)*12+MONTH(K$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:K35)+SUM($E$36:K36)-(IF((YEAR(K$3)*12+MONTH(K$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(K$3)*12+MONTH(K$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(K$3)*12+MONTH(K$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="L59" s="61">
-        <f>SUM($E$35:L35)+SUM($E$36:L36)-(IF((YEAR(L$3)*12+MONTH(L$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(L$3)*12+MONTH(L$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(L$3)*12+MONTH(L$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:L35)+SUM($E$36:L36)-(IF((YEAR(L$3)*12+MONTH(L$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(L$3)*12+MONTH(L$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(L$3)*12+MONTH(L$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="M59" s="61">
-        <f>SUM($E$35:M35)+SUM($E$36:M36)-(IF((YEAR(M$3)*12+MONTH(M$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(M$3)*12+MONTH(M$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(M$3)*12+MONTH(M$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:M35)+SUM($E$36:M36)-(IF((YEAR(M$3)*12+MONTH(M$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(M$3)*12+MONTH(M$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(M$3)*12+MONTH(M$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="N59" s="61">
-        <f>SUM($E$35:N35)+SUM($E$36:N36)-(IF((YEAR(N$3)*12+MONTH(N$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(N$3)*12+MONTH(N$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(N$3)*12+MONTH(N$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:N35)+SUM($E$36:N36)-(IF((YEAR(N$3)*12+MONTH(N$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(N$3)*12+MONTH(N$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(N$3)*12+MONTH(N$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="O59" s="61">
-        <f>SUM($E$35:O35)+SUM($E$36:O36)-(IF((YEAR(O$3)*12+MONTH(O$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(O$3)*12+MONTH(O$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(O$3)*12+MONTH(O$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:O35)+SUM($E$36:O36)-(IF((YEAR(O$3)*12+MONTH(O$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(O$3)*12+MONTH(O$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(O$3)*12+MONTH(O$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="P59" s="61">
-        <f>SUM($E$35:P35)+SUM($E$36:P36)-(IF((YEAR(P$3)*12+MONTH(P$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(P$3)*12+MONTH(P$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(P$3)*12+MONTH(P$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:P35)+SUM($E$36:P36)-(IF((YEAR(P$3)*12+MONTH(P$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(P$3)*12+MONTH(P$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(P$3)*12+MONTH(P$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="Q59" s="61">
-        <f>SUM($E$35:Q35)+SUM($E$36:Q36)-(IF((YEAR(Q$3)*12+MONTH(Q$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(Q$3)*12+MONTH(Q$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(Q$3)*12+MONTH(Q$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:Q35)+SUM($E$36:Q36)-(IF((YEAR(Q$3)*12+MONTH(Q$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(Q$3)*12+MONTH(Q$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(Q$3)*12+MONTH(Q$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="R59" s="61">
-        <f>SUM($E$35:R35)+SUM($E$36:R36)-(IF((YEAR(R$3)*12+MONTH(R$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(R$3)*12+MONTH(R$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(R$3)*12+MONTH(R$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:R35)+SUM($E$36:R36)-(IF((YEAR(R$3)*12+MONTH(R$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(R$3)*12+MONTH(R$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(R$3)*12+MONTH(R$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="S59" s="61">
-        <f>SUM($E$35:S35)+SUM($E$36:S36)-(IF((YEAR(S$3)*12+MONTH(S$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(S$3)*12+MONTH(S$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(S$3)*12+MONTH(S$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:S35)+SUM($E$36:S36)-(IF((YEAR(S$3)*12+MONTH(S$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(S$3)*12+MONTH(S$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(S$3)*12+MONTH(S$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="T59" s="61">
-        <f>SUM($E$35:T35)+SUM($E$36:T36)-(IF((YEAR(T$3)*12+MONTH(T$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(T$3)*12+MONTH(T$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(T$3)*12+MONTH(T$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:T35)+SUM($E$36:T36)-(IF((YEAR(T$3)*12+MONTH(T$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(T$3)*12+MONTH(T$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(T$3)*12+MONTH(T$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="U59" s="61">
-        <f>SUM($E$35:U35)+SUM($E$36:U36)-(IF((YEAR(U$3)*12+MONTH(U$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(U$3)*12+MONTH(U$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(U$3)*12+MONTH(U$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:U35)+SUM($E$36:U36)-(IF((YEAR(U$3)*12+MONTH(U$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(U$3)*12+MONTH(U$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(U$3)*12+MONTH(U$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="V59" s="61">
-        <f>SUM($E$35:V35)+SUM($E$36:V36)-(IF((YEAR(V$3)*12+MONTH(V$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(V$3)*12+MONTH(V$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(V$3)*12+MONTH(V$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:V35)+SUM($E$36:V36)-(IF((YEAR(V$3)*12+MONTH(V$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(V$3)*12+MONTH(V$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(V$3)*12+MONTH(V$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="W59" s="61">
-        <f>SUM($E$35:W35)+SUM($E$36:W36)-(IF((YEAR(W$3)*12+MONTH(W$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(W$3)*12+MONTH(W$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(W$3)*12+MONTH(W$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:W35)+SUM($E$36:W36)-(IF((YEAR(W$3)*12+MONTH(W$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(W$3)*12+MONTH(W$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(W$3)*12+MONTH(W$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="X59" s="61">
-        <f>SUM($E$35:X35)+SUM($E$36:X36)-(IF((YEAR(X$3)*12+MONTH(X$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(X$3)*12+MONTH(X$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(X$3)*12+MONTH(X$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:X35)+SUM($E$36:X36)-(IF((YEAR(X$3)*12+MONTH(X$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(X$3)*12+MONTH(X$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(X$3)*12+MONTH(X$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="Y59" s="61">
-        <f>SUM($E$35:Y35)+SUM($E$36:Y36)-(IF((YEAR(Y$3)*12+MONTH(Y$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(Y$3)*12+MONTH(Y$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(Y$3)*12+MONTH(Y$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:Y35)+SUM($E$36:Y36)-(IF((YEAR(Y$3)*12+MONTH(Y$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(Y$3)*12+MONTH(Y$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(Y$3)*12+MONTH(Y$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="Z59" s="61">
-        <f>SUM($E$35:Z35)+SUM($E$36:Z36)-(IF((YEAR(Z$3)*12+MONTH(Z$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(Z$3)*12+MONTH(Z$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(Z$3)*12+MONTH(Z$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:Z35)+SUM($E$36:Z36)-(IF((YEAR(Z$3)*12+MONTH(Z$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(Z$3)*12+MONTH(Z$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(Z$3)*12+MONTH(Z$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AA59" s="61">
-        <f>SUM($E$35:AA35)+SUM($E$36:AA36)-(IF((YEAR(AA$3)*12+MONTH(AA$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AA$3)*12+MONTH(AA$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AA$3)*12+MONTH(AA$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AA35)+SUM($E$36:AA36)-(IF((YEAR(AA$3)*12+MONTH(AA$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AA$3)*12+MONTH(AA$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AA$3)*12+MONTH(AA$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AB59" s="61">
-        <f>SUM($E$35:AB35)+SUM($E$36:AB36)-(IF((YEAR(AB$3)*12+MONTH(AB$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AB$3)*12+MONTH(AB$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AB$3)*12+MONTH(AB$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AB35)+SUM($E$36:AB36)-(IF((YEAR(AB$3)*12+MONTH(AB$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AB$3)*12+MONTH(AB$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AB$3)*12+MONTH(AB$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AC59" s="61">
-        <f>SUM($E$35:AC35)+SUM($E$36:AC36)-(IF((YEAR(AC$3)*12+MONTH(AC$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AC$3)*12+MONTH(AC$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AC$3)*12+MONTH(AC$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AC35)+SUM($E$36:AC36)-(IF((YEAR(AC$3)*12+MONTH(AC$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AC$3)*12+MONTH(AC$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AC$3)*12+MONTH(AC$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AD59" s="61">
-        <f>SUM($E$35:AD35)+SUM($E$36:AD36)-(IF((YEAR(AD$3)*12+MONTH(AD$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AD$3)*12+MONTH(AD$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AD$3)*12+MONTH(AD$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AD35)+SUM($E$36:AD36)-(IF((YEAR(AD$3)*12+MONTH(AD$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AD$3)*12+MONTH(AD$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AD$3)*12+MONTH(AD$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AE59" s="61">
-        <f>SUM($E$35:AE35)+SUM($E$36:AE36)-(IF((YEAR(AE$3)*12+MONTH(AE$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AE$3)*12+MONTH(AE$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AE$3)*12+MONTH(AE$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AE35)+SUM($E$36:AE36)-(IF((YEAR(AE$3)*12+MONTH(AE$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AE$3)*12+MONTH(AE$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AE$3)*12+MONTH(AE$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AF59" s="61">
-        <f>SUM($E$35:AF35)+SUM($E$36:AF36)-(IF((YEAR(AF$3)*12+MONTH(AF$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AF$3)*12+MONTH(AF$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AF$3)*12+MONTH(AF$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AF35)+SUM($E$36:AF36)-(IF((YEAR(AF$3)*12+MONTH(AF$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AF$3)*12+MONTH(AF$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AF$3)*12+MONTH(AF$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AG59" s="61">
-        <f>SUM($E$35:AG35)+SUM($E$36:AG36)-(IF((YEAR(AG$3)*12+MONTH(AG$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AG$3)*12+MONTH(AG$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AG$3)*12+MONTH(AG$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AG35)+SUM($E$36:AG36)-(IF((YEAR(AG$3)*12+MONTH(AG$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AG$3)*12+MONTH(AG$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AG$3)*12+MONTH(AG$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AH59" s="61">
-        <f>SUM($E$35:AH35)+SUM($E$36:AH36)-(IF((YEAR(AH$3)*12+MONTH(AH$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AH$3)*12+MONTH(AH$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AH$3)*12+MONTH(AH$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AH35)+SUM($E$36:AH36)-(IF((YEAR(AH$3)*12+MONTH(AH$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AH$3)*12+MONTH(AH$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AH$3)*12+MONTH(AH$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AI59" s="61">
-        <f>SUM($E$35:AI35)+SUM($E$36:AI36)-(IF((YEAR(AI$3)*12+MONTH(AI$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AI$3)*12+MONTH(AI$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AI$3)*12+MONTH(AI$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AI35)+SUM($E$36:AI36)-(IF((YEAR(AI$3)*12+MONTH(AI$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AI$3)*12+MONTH(AI$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AI$3)*12+MONTH(AI$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AJ59" s="61">
-        <f>SUM($E$35:AJ35)+SUM($E$36:AJ36)-(IF((YEAR(AJ$3)*12+MONTH(AJ$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AJ$3)*12+MONTH(AJ$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AJ$3)*12+MONTH(AJ$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AJ35)+SUM($E$36:AJ36)-(IF((YEAR(AJ$3)*12+MONTH(AJ$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AJ$3)*12+MONTH(AJ$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AJ$3)*12+MONTH(AJ$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AK59" s="61">
-        <f>SUM($E$35:AK35)+SUM($E$36:AK36)-(IF((YEAR(AK$3)*12+MONTH(AK$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AK$3)*12+MONTH(AK$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AK$3)*12+MONTH(AK$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AK35)+SUM($E$36:AK36)-(IF((YEAR(AK$3)*12+MONTH(AK$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AK$3)*12+MONTH(AK$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AK$3)*12+MONTH(AK$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AL59" s="61">
-        <f>SUM($E$35:AL35)+SUM($E$36:AL36)-(IF((YEAR(AL$3)*12+MONTH(AL$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AL$3)*12+MONTH(AL$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AL$3)*12+MONTH(AL$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AL35)+SUM($E$36:AL36)-(IF((YEAR(AL$3)*12+MONTH(AL$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AL$3)*12+MONTH(AL$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AL$3)*12+MONTH(AL$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AM59" s="61">
-        <f>SUM($E$35:AM35)+SUM($E$36:AM36)-(IF((YEAR(AM$3)*12+MONTH(AM$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AM$3)*12+MONTH(AM$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AM$3)*12+MONTH(AM$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AM35)+SUM($E$36:AM36)-(IF((YEAR(AM$3)*12+MONTH(AM$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AM$3)*12+MONTH(AM$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AM$3)*12+MONTH(AM$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AN59" s="61">
-        <f>SUM($E$35:AN35)+SUM($E$36:AN36)-(IF((YEAR(AN$3)*12+MONTH(AN$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AN$3)*12+MONTH(AN$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AN$3)*12+MONTH(AN$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AN35)+SUM($E$36:AN36)-(IF((YEAR(AN$3)*12+MONTH(AN$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AN$3)*12+MONTH(AN$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AN$3)*12+MONTH(AN$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AO59" s="61">
-        <f>SUM($E$35:AO35)+SUM($E$36:AO36)-(IF((YEAR(AO$3)*12+MONTH(AO$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AO$3)*12+MONTH(AO$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AO$3)*12+MONTH(AO$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AO35)+SUM($E$36:AO36)-(IF((YEAR(AO$3)*12+MONTH(AO$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AO$3)*12+MONTH(AO$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AO$3)*12+MONTH(AO$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AP59" s="61">
-        <f>SUM($E$35:AP35)+SUM($E$36:AP36)-(IF((YEAR(AP$3)*12+MONTH(AP$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AP$3)*12+MONTH(AP$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AP$3)*12+MONTH(AP$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AP35)+SUM($E$36:AP36)-(IF((YEAR(AP$3)*12+MONTH(AP$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AP$3)*12+MONTH(AP$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AP$3)*12+MONTH(AP$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AQ59" s="61">
-        <f>SUM($E$35:AQ35)+SUM($E$36:AQ36)-(IF((YEAR(AQ$3)*12+MONTH(AQ$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AQ$3)*12+MONTH(AQ$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AQ$3)*12+MONTH(AQ$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AQ35)+SUM($E$36:AQ36)-(IF((YEAR(AQ$3)*12+MONTH(AQ$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AQ$3)*12+MONTH(AQ$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AQ$3)*12+MONTH(AQ$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AR59" s="61">
-        <f>SUM($E$35:AR35)+SUM($E$36:AR36)-(IF((YEAR(AR$3)*12+MONTH(AR$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AR$3)*12+MONTH(AR$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AR$3)*12+MONTH(AR$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AR35)+SUM($E$36:AR36)-(IF((YEAR(AR$3)*12+MONTH(AR$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AR$3)*12+MONTH(AR$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AR$3)*12+MONTH(AR$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AS59" s="61">
-        <f>SUM($E$35:AS35)+SUM($E$36:AS36)-(IF((YEAR(AS$3)*12+MONTH(AS$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AS$3)*12+MONTH(AS$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AS$3)*12+MONTH(AS$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AS35)+SUM($E$36:AS36)-(IF((YEAR(AS$3)*12+MONTH(AS$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AS$3)*12+MONTH(AS$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AS$3)*12+MONTH(AS$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AT59" s="61">
-        <f>SUM($E$35:AT35)+SUM($E$36:AT36)-(IF((YEAR(AT$3)*12+MONTH(AT$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AT$3)*12+MONTH(AT$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AT$3)*12+MONTH(AT$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AT35)+SUM($E$36:AT36)-(IF((YEAR(AT$3)*12+MONTH(AT$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AT$3)*12+MONTH(AT$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AT$3)*12+MONTH(AT$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AU59" s="61">
-        <f>SUM($E$35:AU35)+SUM($E$36:AU36)-(IF((YEAR(AU$3)*12+MONTH(AU$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AU$3)*12+MONTH(AU$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AU$3)*12+MONTH(AU$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AU35)+SUM($E$36:AU36)-(IF((YEAR(AU$3)*12+MONTH(AU$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AU$3)*12+MONTH(AU$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AU$3)*12+MONTH(AU$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AV59" s="61">
-        <f>SUM($E$35:AV35)+SUM($E$36:AV36)-(IF((YEAR(AV$3)*12+MONTH(AV$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AV$3)*12+MONTH(AV$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AV$3)*12+MONTH(AV$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AV35)+SUM($E$36:AV36)-(IF((YEAR(AV$3)*12+MONTH(AV$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AV$3)*12+MONTH(AV$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AV$3)*12+MONTH(AV$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AW59" s="61">
-        <f>SUM($E$35:AW35)+SUM($E$36:AW36)-(IF((YEAR(AW$3)*12+MONTH(AW$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AW$3)*12+MONTH(AW$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AW$3)*12+MONTH(AW$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AW35)+SUM($E$36:AW36)-(IF((YEAR(AW$3)*12+MONTH(AW$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AW$3)*12+MONTH(AW$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AW$3)*12+MONTH(AW$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AX59" s="61">
-        <f>SUM($E$35:AX35)+SUM($E$36:AX36)-(IF((YEAR(AX$3)*12+MONTH(AX$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AX$3)*12+MONTH(AX$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AX$3)*12+MONTH(AX$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AX35)+SUM($E$36:AX36)-(IF((YEAR(AX$3)*12+MONTH(AX$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AX$3)*12+MONTH(AX$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AX$3)*12+MONTH(AX$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AY59" s="61">
-        <f>SUM($E$35:AY35)+SUM($E$36:AY36)-(IF((YEAR(AY$3)*12+MONTH(AY$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AY$3)*12+MONTH(AY$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AY$3)*12+MONTH(AY$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AY35)+SUM($E$36:AY36)-(IF((YEAR(AY$3)*12+MONTH(AY$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AY$3)*12+MONTH(AY$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AY$3)*12+MONTH(AY$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="AZ59" s="61">
-        <f>SUM($E$35:AZ35)+SUM($E$36:AZ36)-(IF((YEAR(AZ$3)*12+MONTH(AZ$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(AZ$3)*12+MONTH(AZ$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(AZ$3)*12+MONTH(AZ$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:AZ35)+SUM($E$36:AZ36)-(IF((YEAR(AZ$3)*12+MONTH(AZ$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(AZ$3)*12+MONTH(AZ$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(AZ$3)*12+MONTH(AZ$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="BA59" s="61">
-        <f>SUM($E$35:BA35)+SUM($E$36:BA36)-(IF((YEAR(BA$3)*12+MONTH(BA$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BA$3)*12+MONTH(BA$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BA$3)*12+MONTH(BA$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:BA35)+SUM($E$36:BA36)-(IF((YEAR(BA$3)*12+MONTH(BA$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BA$3)*12+MONTH(BA$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BA$3)*12+MONTH(BA$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="BB59" s="61">
-        <f>SUM($E$35:BB35)+SUM($E$36:BB36)-(IF((YEAR(BB$3)*12+MONTH(BB$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BB$3)*12+MONTH(BB$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BB$3)*12+MONTH(BB$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:BB35)+SUM($E$36:BB36)-(IF((YEAR(BB$3)*12+MONTH(BB$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BB$3)*12+MONTH(BB$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BB$3)*12+MONTH(BB$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="BC59" s="61">
-        <f>SUM($E$35:BC35)+SUM($E$36:BC36)-(IF((YEAR(BC$3)*12+MONTH(BC$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BC$3)*12+MONTH(BC$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BC$3)*12+MONTH(BC$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:BC35)+SUM($E$36:BC36)-(IF((YEAR(BC$3)*12+MONTH(BC$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BC$3)*12+MONTH(BC$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BC$3)*12+MONTH(BC$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="BD59" s="61">
-        <f>SUM($E$35:BD35)+SUM($E$36:BD36)-(IF((YEAR(BD$3)*12+MONTH(BD$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BD$3)*12+MONTH(BD$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BD$3)*12+MONTH(BD$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:BD35)+SUM($E$36:BD36)-(IF((YEAR(BD$3)*12+MONTH(BD$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BD$3)*12+MONTH(BD$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BD$3)*12+MONTH(BD$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="BE59" s="61">
-        <f>SUM($E$35:BE35)+SUM($E$36:BE36)-(IF((YEAR(BE$3)*12+MONTH(BE$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BE$3)*12+MONTH(BE$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BE$3)*12+MONTH(BE$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:BE35)+SUM($E$36:BE36)-(IF((YEAR(BE$3)*12+MONTH(BE$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BE$3)*12+MONTH(BE$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BE$3)*12+MONTH(BE$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="BF59" s="61">
-        <f>SUM($E$35:BF35)+SUM($E$36:BF36)-(IF((YEAR(BF$3)*12+MONTH(BF$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BF$3)*12+MONTH(BF$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BF$3)*12+MONTH(BF$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:BF35)+SUM($E$36:BF36)-(IF((YEAR(BF$3)*12+MONTH(BF$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BF$3)*12+MONTH(BF$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BF$3)*12+MONTH(BF$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="BG59" s="61">
-        <f>SUM($E$35:BG35)+SUM($E$36:BG36)-(IF((YEAR(BG$3)*12+MONTH(BG$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BG$3)*12+MONTH(BG$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BG$3)*12+MONTH(BG$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:BG35)+SUM($E$36:BG36)-(IF((YEAR(BG$3)*12+MONTH(BG$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BG$3)*12+MONTH(BG$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BG$3)*12+MONTH(BG$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="BH59" s="61">
-        <f>SUM($E$35:BH35)+SUM($E$36:BH36)-(IF((YEAR(BH$3)*12+MONTH(BH$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BH$3)*12+MONTH(BH$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BH$3)*12+MONTH(BH$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:BH35)+SUM($E$36:BH36)-(IF((YEAR(BH$3)*12+MONTH(BH$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BH$3)*12+MONTH(BH$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BH$3)*12+MONTH(BH$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="BI59" s="61">
-        <f>SUM($E$35:BI35)+SUM($E$36:BI36)-(IF((YEAR(BI$3)*12+MONTH(BI$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BI$3)*12+MONTH(BI$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BI$3)*12+MONTH(BI$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:BI35)+SUM($E$36:BI36)-(IF((YEAR(BI$3)*12+MONTH(BI$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BI$3)*12+MONTH(BI$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BI$3)*12+MONTH(BI$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="BJ59" s="61">
-        <f>SUM($E$35:BJ35)+SUM($E$36:BJ36)-(IF((YEAR(BJ$3)*12+MONTH(BJ$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BJ$3)*12+MONTH(BJ$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BJ$3)*12+MONTH(BJ$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:BJ35)+SUM($E$36:BJ36)-(IF((YEAR(BJ$3)*12+MONTH(BJ$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BJ$3)*12+MONTH(BJ$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BJ$3)*12+MONTH(BJ$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="BK59" s="61">
-        <f>SUM($E$35:BK35)+SUM($E$36:BK36)-(IF((YEAR(BK$3)*12+MONTH(BK$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BK$3)*12+MONTH(BK$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BK$3)*12+MONTH(BK$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:BK35)+SUM($E$36:BK36)-(IF((YEAR(BK$3)*12+MONTH(BK$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BK$3)*12+MONTH(BK$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BK$3)*12+MONTH(BK$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="BL59" s="61">
-        <f>SUM($E$35:BL35)+SUM($E$36:BL36)-(IF((YEAR(BL$3)*12+MONTH(BL$3))&gt;=(YEAR(Assumptions!$F$141)*12+MONTH(Assumptions!$F$141)),Assumptions!$F$142,0)+IF((YEAR(BL$3)*12+MONTH(BL$3))&gt;=(YEAR(Assumptions!$F$143)*12+MONTH(Assumptions!$F$143)),Assumptions!$F$144,0)+IF((YEAR(BL$3)*12+MONTH(BL$3))&gt;=(YEAR(Assumptions!$F$146)*12+MONTH(Assumptions!$F$146)),Assumptions!$F$145,0))</f>
+        <f>SUM($E$35:BL35)+SUM($E$36:BL36)-(IF((YEAR(BL$3)*12+MONTH(BL$3))&gt;=(YEAR(Assumptions!$F$137)*12+MONTH(Assumptions!$F$137)),Assumptions!$F$138,0)+IF((YEAR(BL$3)*12+MONTH(BL$3))&gt;=(YEAR(Assumptions!$F$139)*12+MONTH(Assumptions!$F$139)),Assumptions!$F$140,0)+IF((YEAR(BL$3)*12+MONTH(BL$3))&gt;=(YEAR(Assumptions!$F$142)*12+MONTH(Assumptions!$F$142)),Assumptions!$F$141,0))</f>
         <v/>
       </c>
       <c r="BN59" s="62">
@@ -30410,7 +30324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:BT22"/>
+  <dimension ref="B1:BT21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -32228,283 +32142,6 @@
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Units built on our own lines</t>
-        </is>
-      </c>
-      <c r="C11" s="52" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="E11" s="9">
-        <f>MIN('Revenue Forecast'!E34,'Revenue Forecast'!E30)</f>
-        <v/>
-      </c>
-      <c r="F11" s="9">
-        <f>MIN('Revenue Forecast'!F34,'Revenue Forecast'!F30)</f>
-        <v/>
-      </c>
-      <c r="G11" s="9">
-        <f>MIN('Revenue Forecast'!G34,'Revenue Forecast'!G30)</f>
-        <v/>
-      </c>
-      <c r="H11" s="9">
-        <f>MIN('Revenue Forecast'!H34,'Revenue Forecast'!H30)</f>
-        <v/>
-      </c>
-      <c r="I11" s="9">
-        <f>MIN('Revenue Forecast'!I34,'Revenue Forecast'!I30)</f>
-        <v/>
-      </c>
-      <c r="J11" s="9">
-        <f>MIN('Revenue Forecast'!J34,'Revenue Forecast'!J30)</f>
-        <v/>
-      </c>
-      <c r="K11" s="9">
-        <f>MIN('Revenue Forecast'!K34,'Revenue Forecast'!K30)</f>
-        <v/>
-      </c>
-      <c r="L11" s="9">
-        <f>MIN('Revenue Forecast'!L34,'Revenue Forecast'!L30)</f>
-        <v/>
-      </c>
-      <c r="M11" s="9">
-        <f>MIN('Revenue Forecast'!M34,'Revenue Forecast'!M30)</f>
-        <v/>
-      </c>
-      <c r="N11" s="9">
-        <f>MIN('Revenue Forecast'!N34,'Revenue Forecast'!N30)</f>
-        <v/>
-      </c>
-      <c r="O11" s="9">
-        <f>MIN('Revenue Forecast'!O34,'Revenue Forecast'!O30)</f>
-        <v/>
-      </c>
-      <c r="P11" s="9">
-        <f>MIN('Revenue Forecast'!P34,'Revenue Forecast'!P30)</f>
-        <v/>
-      </c>
-      <c r="Q11" s="9">
-        <f>MIN('Revenue Forecast'!Q34,'Revenue Forecast'!Q30)</f>
-        <v/>
-      </c>
-      <c r="R11" s="9">
-        <f>MIN('Revenue Forecast'!R34,'Revenue Forecast'!R30)</f>
-        <v/>
-      </c>
-      <c r="S11" s="9">
-        <f>MIN('Revenue Forecast'!S34,'Revenue Forecast'!S30)</f>
-        <v/>
-      </c>
-      <c r="T11" s="9">
-        <f>MIN('Revenue Forecast'!T34,'Revenue Forecast'!T30)</f>
-        <v/>
-      </c>
-      <c r="U11" s="9">
-        <f>MIN('Revenue Forecast'!U34,'Revenue Forecast'!U30)</f>
-        <v/>
-      </c>
-      <c r="V11" s="9">
-        <f>MIN('Revenue Forecast'!V34,'Revenue Forecast'!V30)</f>
-        <v/>
-      </c>
-      <c r="W11" s="9">
-        <f>MIN('Revenue Forecast'!W34,'Revenue Forecast'!W30)</f>
-        <v/>
-      </c>
-      <c r="X11" s="9">
-        <f>MIN('Revenue Forecast'!X34,'Revenue Forecast'!X30)</f>
-        <v/>
-      </c>
-      <c r="Y11" s="9">
-        <f>MIN('Revenue Forecast'!Y34,'Revenue Forecast'!Y30)</f>
-        <v/>
-      </c>
-      <c r="Z11" s="9">
-        <f>MIN('Revenue Forecast'!Z34,'Revenue Forecast'!Z30)</f>
-        <v/>
-      </c>
-      <c r="AA11" s="9">
-        <f>MIN('Revenue Forecast'!AA34,'Revenue Forecast'!AA30)</f>
-        <v/>
-      </c>
-      <c r="AB11" s="9">
-        <f>MIN('Revenue Forecast'!AB34,'Revenue Forecast'!AB30)</f>
-        <v/>
-      </c>
-      <c r="AC11" s="9">
-        <f>MIN('Revenue Forecast'!AC34,'Revenue Forecast'!AC30)</f>
-        <v/>
-      </c>
-      <c r="AD11" s="9">
-        <f>MIN('Revenue Forecast'!AD34,'Revenue Forecast'!AD30)</f>
-        <v/>
-      </c>
-      <c r="AE11" s="9">
-        <f>MIN('Revenue Forecast'!AE34,'Revenue Forecast'!AE30)</f>
-        <v/>
-      </c>
-      <c r="AF11" s="9">
-        <f>MIN('Revenue Forecast'!AF34,'Revenue Forecast'!AF30)</f>
-        <v/>
-      </c>
-      <c r="AG11" s="9">
-        <f>MIN('Revenue Forecast'!AG34,'Revenue Forecast'!AG30)</f>
-        <v/>
-      </c>
-      <c r="AH11" s="9">
-        <f>MIN('Revenue Forecast'!AH34,'Revenue Forecast'!AH30)</f>
-        <v/>
-      </c>
-      <c r="AI11" s="9">
-        <f>MIN('Revenue Forecast'!AI34,'Revenue Forecast'!AI30)</f>
-        <v/>
-      </c>
-      <c r="AJ11" s="9">
-        <f>MIN('Revenue Forecast'!AJ34,'Revenue Forecast'!AJ30)</f>
-        <v/>
-      </c>
-      <c r="AK11" s="9">
-        <f>MIN('Revenue Forecast'!AK34,'Revenue Forecast'!AK30)</f>
-        <v/>
-      </c>
-      <c r="AL11" s="9">
-        <f>MIN('Revenue Forecast'!AL34,'Revenue Forecast'!AL30)</f>
-        <v/>
-      </c>
-      <c r="AM11" s="9">
-        <f>MIN('Revenue Forecast'!AM34,'Revenue Forecast'!AM30)</f>
-        <v/>
-      </c>
-      <c r="AN11" s="9">
-        <f>MIN('Revenue Forecast'!AN34,'Revenue Forecast'!AN30)</f>
-        <v/>
-      </c>
-      <c r="AO11" s="9">
-        <f>MIN('Revenue Forecast'!AO34,'Revenue Forecast'!AO30)</f>
-        <v/>
-      </c>
-      <c r="AP11" s="9">
-        <f>MIN('Revenue Forecast'!AP34,'Revenue Forecast'!AP30)</f>
-        <v/>
-      </c>
-      <c r="AQ11" s="9">
-        <f>MIN('Revenue Forecast'!AQ34,'Revenue Forecast'!AQ30)</f>
-        <v/>
-      </c>
-      <c r="AR11" s="9">
-        <f>MIN('Revenue Forecast'!AR34,'Revenue Forecast'!AR30)</f>
-        <v/>
-      </c>
-      <c r="AS11" s="9">
-        <f>MIN('Revenue Forecast'!AS34,'Revenue Forecast'!AS30)</f>
-        <v/>
-      </c>
-      <c r="AT11" s="9">
-        <f>MIN('Revenue Forecast'!AT34,'Revenue Forecast'!AT30)</f>
-        <v/>
-      </c>
-      <c r="AU11" s="9">
-        <f>MIN('Revenue Forecast'!AU34,'Revenue Forecast'!AU30)</f>
-        <v/>
-      </c>
-      <c r="AV11" s="9">
-        <f>MIN('Revenue Forecast'!AV34,'Revenue Forecast'!AV30)</f>
-        <v/>
-      </c>
-      <c r="AW11" s="9">
-        <f>MIN('Revenue Forecast'!AW34,'Revenue Forecast'!AW30)</f>
-        <v/>
-      </c>
-      <c r="AX11" s="9">
-        <f>MIN('Revenue Forecast'!AX34,'Revenue Forecast'!AX30)</f>
-        <v/>
-      </c>
-      <c r="AY11" s="9">
-        <f>MIN('Revenue Forecast'!AY34,'Revenue Forecast'!AY30)</f>
-        <v/>
-      </c>
-      <c r="AZ11" s="9">
-        <f>MIN('Revenue Forecast'!AZ34,'Revenue Forecast'!AZ30)</f>
-        <v/>
-      </c>
-      <c r="BA11" s="9">
-        <f>MIN('Revenue Forecast'!BA34,'Revenue Forecast'!BA30)</f>
-        <v/>
-      </c>
-      <c r="BB11" s="9">
-        <f>MIN('Revenue Forecast'!BB34,'Revenue Forecast'!BB30)</f>
-        <v/>
-      </c>
-      <c r="BC11" s="9">
-        <f>MIN('Revenue Forecast'!BC34,'Revenue Forecast'!BC30)</f>
-        <v/>
-      </c>
-      <c r="BD11" s="9">
-        <f>MIN('Revenue Forecast'!BD34,'Revenue Forecast'!BD30)</f>
-        <v/>
-      </c>
-      <c r="BE11" s="9">
-        <f>MIN('Revenue Forecast'!BE34,'Revenue Forecast'!BE30)</f>
-        <v/>
-      </c>
-      <c r="BF11" s="9">
-        <f>MIN('Revenue Forecast'!BF34,'Revenue Forecast'!BF30)</f>
-        <v/>
-      </c>
-      <c r="BG11" s="9">
-        <f>MIN('Revenue Forecast'!BG34,'Revenue Forecast'!BG30)</f>
-        <v/>
-      </c>
-      <c r="BH11" s="9">
-        <f>MIN('Revenue Forecast'!BH34,'Revenue Forecast'!BH30)</f>
-        <v/>
-      </c>
-      <c r="BI11" s="9">
-        <f>MIN('Revenue Forecast'!BI34,'Revenue Forecast'!BI30)</f>
-        <v/>
-      </c>
-      <c r="BJ11" s="9">
-        <f>MIN('Revenue Forecast'!BJ34,'Revenue Forecast'!BJ30)</f>
-        <v/>
-      </c>
-      <c r="BK11" s="9">
-        <f>MIN('Revenue Forecast'!BK34,'Revenue Forecast'!BK30)</f>
-        <v/>
-      </c>
-      <c r="BL11" s="9">
-        <f>MIN('Revenue Forecast'!BL34,'Revenue Forecast'!BL30)</f>
-        <v/>
-      </c>
-      <c r="BN11" s="63">
-        <f>SUM(E11:P11)</f>
-        <v/>
-      </c>
-      <c r="BO11" s="63">
-        <f>SUM(Q11:AB11)</f>
-        <v/>
-      </c>
-      <c r="BP11" s="63">
-        <f>SUM(AC11:AN11)</f>
-        <v/>
-      </c>
-      <c r="BQ11" s="63">
-        <f>SUM(AO11:AZ11)</f>
-        <v/>
-      </c>
-      <c r="BR11" s="63">
-        <f>SUM(BA11:BL11)</f>
-        <v/>
-      </c>
-      <c r="BT11" s="28" t="inlineStr">
-        <is>
-          <t>our lines are filled first, the assembly partner takes the rest</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
       <c r="B12" s="49" t="inlineStr">
         <is>
@@ -34234,829 +33871,552 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>In-house assembly saving</t>
-        </is>
-      </c>
-      <c r="C19" s="52" t="inlineStr">
+      <c r="B19" s="49" t="inlineStr">
+        <is>
+          <t>Total cost of goods sold</t>
+        </is>
+      </c>
+      <c r="C19" s="54" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E19" s="10">
-        <f>-E11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="F19" s="10">
-        <f>-F11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="G19" s="10">
-        <f>-G11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="H19" s="10">
-        <f>-H11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="I19" s="10">
-        <f>-I11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="J19" s="10">
-        <f>-J11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="K19" s="10">
-        <f>-K11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="L19" s="10">
-        <f>-L11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="M19" s="10">
-        <f>-M11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="N19" s="10">
-        <f>-N11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="O19" s="10">
-        <f>-O11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="P19" s="10">
-        <f>-P11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="Q19" s="10">
-        <f>-Q11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="R19" s="10">
-        <f>-R11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="S19" s="10">
-        <f>-S11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="T19" s="10">
-        <f>-T11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="U19" s="10">
-        <f>-U11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="V19" s="10">
-        <f>-V11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="W19" s="10">
-        <f>-W11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="X19" s="10">
-        <f>-X11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="Y19" s="10">
-        <f>-Y11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="Z19" s="10">
-        <f>-Z11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AA19" s="10">
-        <f>-AA11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AB19" s="10">
-        <f>-AB11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AC19" s="10">
-        <f>-AC11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AD19" s="10">
-        <f>-AD11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AE19" s="10">
-        <f>-AE11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AF19" s="10">
-        <f>-AF11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AG19" s="10">
-        <f>-AG11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AH19" s="10">
-        <f>-AH11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AI19" s="10">
-        <f>-AI11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AJ19" s="10">
-        <f>-AJ11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AK19" s="10">
-        <f>-AK11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AL19" s="10">
-        <f>-AL11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AM19" s="10">
-        <f>-AM11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AN19" s="10">
-        <f>-AN11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AO19" s="10">
-        <f>-AO11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AP19" s="10">
-        <f>-AP11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AQ19" s="10">
-        <f>-AQ11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AR19" s="10">
-        <f>-AR11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AS19" s="10">
-        <f>-AS11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AT19" s="10">
-        <f>-AT11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AU19" s="10">
-        <f>-AU11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AV19" s="10">
-        <f>-AV11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AW19" s="10">
-        <f>-AW11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AX19" s="10">
-        <f>-AX11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AY19" s="10">
-        <f>-AY11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="AZ19" s="10">
-        <f>-AZ11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="BA19" s="10">
-        <f>-BA11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="BB19" s="10">
-        <f>-BB11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="BC19" s="10">
-        <f>-BC11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="BD19" s="10">
-        <f>-BD11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="BE19" s="10">
-        <f>-BE11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="BF19" s="10">
-        <f>-BF11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="BG19" s="10">
-        <f>-BG11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="BH19" s="10">
-        <f>-BH11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="BI19" s="10">
-        <f>-BI11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="BJ19" s="10">
-        <f>-BJ11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="BK19" s="10">
-        <f>-BK11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="BL19" s="10">
-        <f>-BL11*Assumptions!$F$126</f>
-        <v/>
-      </c>
-      <c r="BN19" s="53">
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="55">
+        <f>SUM(E13:E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="55">
+        <f>SUM(F13:F18)</f>
+        <v/>
+      </c>
+      <c r="G19" s="55">
+        <f>SUM(G13:G18)</f>
+        <v/>
+      </c>
+      <c r="H19" s="55">
+        <f>SUM(H13:H18)</f>
+        <v/>
+      </c>
+      <c r="I19" s="55">
+        <f>SUM(I13:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="55">
+        <f>SUM(J13:J18)</f>
+        <v/>
+      </c>
+      <c r="K19" s="55">
+        <f>SUM(K13:K18)</f>
+        <v/>
+      </c>
+      <c r="L19" s="55">
+        <f>SUM(L13:L18)</f>
+        <v/>
+      </c>
+      <c r="M19" s="55">
+        <f>SUM(M13:M18)</f>
+        <v/>
+      </c>
+      <c r="N19" s="55">
+        <f>SUM(N13:N18)</f>
+        <v/>
+      </c>
+      <c r="O19" s="55">
+        <f>SUM(O13:O18)</f>
+        <v/>
+      </c>
+      <c r="P19" s="55">
+        <f>SUM(P13:P18)</f>
+        <v/>
+      </c>
+      <c r="Q19" s="55">
+        <f>SUM(Q13:Q18)</f>
+        <v/>
+      </c>
+      <c r="R19" s="55">
+        <f>SUM(R13:R18)</f>
+        <v/>
+      </c>
+      <c r="S19" s="55">
+        <f>SUM(S13:S18)</f>
+        <v/>
+      </c>
+      <c r="T19" s="55">
+        <f>SUM(T13:T18)</f>
+        <v/>
+      </c>
+      <c r="U19" s="55">
+        <f>SUM(U13:U18)</f>
+        <v/>
+      </c>
+      <c r="V19" s="55">
+        <f>SUM(V13:V18)</f>
+        <v/>
+      </c>
+      <c r="W19" s="55">
+        <f>SUM(W13:W18)</f>
+        <v/>
+      </c>
+      <c r="X19" s="55">
+        <f>SUM(X13:X18)</f>
+        <v/>
+      </c>
+      <c r="Y19" s="55">
+        <f>SUM(Y13:Y18)</f>
+        <v/>
+      </c>
+      <c r="Z19" s="55">
+        <f>SUM(Z13:Z18)</f>
+        <v/>
+      </c>
+      <c r="AA19" s="55">
+        <f>SUM(AA13:AA18)</f>
+        <v/>
+      </c>
+      <c r="AB19" s="55">
+        <f>SUM(AB13:AB18)</f>
+        <v/>
+      </c>
+      <c r="AC19" s="55">
+        <f>SUM(AC13:AC18)</f>
+        <v/>
+      </c>
+      <c r="AD19" s="55">
+        <f>SUM(AD13:AD18)</f>
+        <v/>
+      </c>
+      <c r="AE19" s="55">
+        <f>SUM(AE13:AE18)</f>
+        <v/>
+      </c>
+      <c r="AF19" s="55">
+        <f>SUM(AF13:AF18)</f>
+        <v/>
+      </c>
+      <c r="AG19" s="55">
+        <f>SUM(AG13:AG18)</f>
+        <v/>
+      </c>
+      <c r="AH19" s="55">
+        <f>SUM(AH13:AH18)</f>
+        <v/>
+      </c>
+      <c r="AI19" s="55">
+        <f>SUM(AI13:AI18)</f>
+        <v/>
+      </c>
+      <c r="AJ19" s="55">
+        <f>SUM(AJ13:AJ18)</f>
+        <v/>
+      </c>
+      <c r="AK19" s="55">
+        <f>SUM(AK13:AK18)</f>
+        <v/>
+      </c>
+      <c r="AL19" s="55">
+        <f>SUM(AL13:AL18)</f>
+        <v/>
+      </c>
+      <c r="AM19" s="55">
+        <f>SUM(AM13:AM18)</f>
+        <v/>
+      </c>
+      <c r="AN19" s="55">
+        <f>SUM(AN13:AN18)</f>
+        <v/>
+      </c>
+      <c r="AO19" s="55">
+        <f>SUM(AO13:AO18)</f>
+        <v/>
+      </c>
+      <c r="AP19" s="55">
+        <f>SUM(AP13:AP18)</f>
+        <v/>
+      </c>
+      <c r="AQ19" s="55">
+        <f>SUM(AQ13:AQ18)</f>
+        <v/>
+      </c>
+      <c r="AR19" s="55">
+        <f>SUM(AR13:AR18)</f>
+        <v/>
+      </c>
+      <c r="AS19" s="55">
+        <f>SUM(AS13:AS18)</f>
+        <v/>
+      </c>
+      <c r="AT19" s="55">
+        <f>SUM(AT13:AT18)</f>
+        <v/>
+      </c>
+      <c r="AU19" s="55">
+        <f>SUM(AU13:AU18)</f>
+        <v/>
+      </c>
+      <c r="AV19" s="55">
+        <f>SUM(AV13:AV18)</f>
+        <v/>
+      </c>
+      <c r="AW19" s="55">
+        <f>SUM(AW13:AW18)</f>
+        <v/>
+      </c>
+      <c r="AX19" s="55">
+        <f>SUM(AX13:AX18)</f>
+        <v/>
+      </c>
+      <c r="AY19" s="55">
+        <f>SUM(AY13:AY18)</f>
+        <v/>
+      </c>
+      <c r="AZ19" s="55">
+        <f>SUM(AZ13:AZ18)</f>
+        <v/>
+      </c>
+      <c r="BA19" s="55">
+        <f>SUM(BA13:BA18)</f>
+        <v/>
+      </c>
+      <c r="BB19" s="55">
+        <f>SUM(BB13:BB18)</f>
+        <v/>
+      </c>
+      <c r="BC19" s="55">
+        <f>SUM(BC13:BC18)</f>
+        <v/>
+      </c>
+      <c r="BD19" s="55">
+        <f>SUM(BD13:BD18)</f>
+        <v/>
+      </c>
+      <c r="BE19" s="55">
+        <f>SUM(BE13:BE18)</f>
+        <v/>
+      </c>
+      <c r="BF19" s="55">
+        <f>SUM(BF13:BF18)</f>
+        <v/>
+      </c>
+      <c r="BG19" s="55">
+        <f>SUM(BG13:BG18)</f>
+        <v/>
+      </c>
+      <c r="BH19" s="55">
+        <f>SUM(BH13:BH18)</f>
+        <v/>
+      </c>
+      <c r="BI19" s="55">
+        <f>SUM(BI13:BI18)</f>
+        <v/>
+      </c>
+      <c r="BJ19" s="55">
+        <f>SUM(BJ13:BJ18)</f>
+        <v/>
+      </c>
+      <c r="BK19" s="55">
+        <f>SUM(BK13:BK18)</f>
+        <v/>
+      </c>
+      <c r="BL19" s="55">
+        <f>SUM(BL13:BL18)</f>
+        <v/>
+      </c>
+      <c r="BM19" s="2" t="n"/>
+      <c r="BN19" s="55">
         <f>SUM(E19:P19)</f>
         <v/>
       </c>
-      <c r="BO19" s="53">
+      <c r="BO19" s="55">
         <f>SUM(Q19:AB19)</f>
         <v/>
       </c>
-      <c r="BP19" s="53">
+      <c r="BP19" s="55">
         <f>SUM(AC19:AN19)</f>
         <v/>
       </c>
-      <c r="BQ19" s="53">
+      <c r="BQ19" s="55">
         <f>SUM(AO19:AZ19)</f>
         <v/>
       </c>
-      <c r="BR19" s="53">
+      <c r="BR19" s="55">
         <f>SUM(BA19:BL19)</f>
         <v/>
       </c>
-      <c r="BT19" s="28" t="inlineStr">
-        <is>
-          <t>units built on our own lines do not pay the assembly partner; their operators and facility are in OPEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="49" t="inlineStr">
-        <is>
-          <t>Total cost of goods sold</t>
-        </is>
-      </c>
-      <c r="C20" s="54" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="55">
-        <f>SUM(E13:E19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="55">
-        <f>SUM(F13:F19)</f>
-        <v/>
-      </c>
-      <c r="G20" s="55">
-        <f>SUM(G13:G19)</f>
-        <v/>
-      </c>
-      <c r="H20" s="55">
-        <f>SUM(H13:H19)</f>
-        <v/>
-      </c>
-      <c r="I20" s="55">
-        <f>SUM(I13:I19)</f>
-        <v/>
-      </c>
-      <c r="J20" s="55">
-        <f>SUM(J13:J19)</f>
-        <v/>
-      </c>
-      <c r="K20" s="55">
-        <f>SUM(K13:K19)</f>
-        <v/>
-      </c>
-      <c r="L20" s="55">
-        <f>SUM(L13:L19)</f>
-        <v/>
-      </c>
-      <c r="M20" s="55">
-        <f>SUM(M13:M19)</f>
-        <v/>
-      </c>
-      <c r="N20" s="55">
-        <f>SUM(N13:N19)</f>
-        <v/>
-      </c>
-      <c r="O20" s="55">
-        <f>SUM(O13:O19)</f>
-        <v/>
-      </c>
-      <c r="P20" s="55">
-        <f>SUM(P13:P19)</f>
-        <v/>
-      </c>
-      <c r="Q20" s="55">
-        <f>SUM(Q13:Q19)</f>
-        <v/>
-      </c>
-      <c r="R20" s="55">
-        <f>SUM(R13:R19)</f>
-        <v/>
-      </c>
-      <c r="S20" s="55">
-        <f>SUM(S13:S19)</f>
-        <v/>
-      </c>
-      <c r="T20" s="55">
-        <f>SUM(T13:T19)</f>
-        <v/>
-      </c>
-      <c r="U20" s="55">
-        <f>SUM(U13:U19)</f>
-        <v/>
-      </c>
-      <c r="V20" s="55">
-        <f>SUM(V13:V19)</f>
-        <v/>
-      </c>
-      <c r="W20" s="55">
-        <f>SUM(W13:W19)</f>
-        <v/>
-      </c>
-      <c r="X20" s="55">
-        <f>SUM(X13:X19)</f>
-        <v/>
-      </c>
-      <c r="Y20" s="55">
-        <f>SUM(Y13:Y19)</f>
-        <v/>
-      </c>
-      <c r="Z20" s="55">
-        <f>SUM(Z13:Z19)</f>
-        <v/>
-      </c>
-      <c r="AA20" s="55">
-        <f>SUM(AA13:AA19)</f>
-        <v/>
-      </c>
-      <c r="AB20" s="55">
-        <f>SUM(AB13:AB19)</f>
-        <v/>
-      </c>
-      <c r="AC20" s="55">
-        <f>SUM(AC13:AC19)</f>
-        <v/>
-      </c>
-      <c r="AD20" s="55">
-        <f>SUM(AD13:AD19)</f>
-        <v/>
-      </c>
-      <c r="AE20" s="55">
-        <f>SUM(AE13:AE19)</f>
-        <v/>
-      </c>
-      <c r="AF20" s="55">
-        <f>SUM(AF13:AF19)</f>
-        <v/>
-      </c>
-      <c r="AG20" s="55">
-        <f>SUM(AG13:AG19)</f>
-        <v/>
-      </c>
-      <c r="AH20" s="55">
-        <f>SUM(AH13:AH19)</f>
-        <v/>
-      </c>
-      <c r="AI20" s="55">
-        <f>SUM(AI13:AI19)</f>
-        <v/>
-      </c>
-      <c r="AJ20" s="55">
-        <f>SUM(AJ13:AJ19)</f>
-        <v/>
-      </c>
-      <c r="AK20" s="55">
-        <f>SUM(AK13:AK19)</f>
-        <v/>
-      </c>
-      <c r="AL20" s="55">
-        <f>SUM(AL13:AL19)</f>
-        <v/>
-      </c>
-      <c r="AM20" s="55">
-        <f>SUM(AM13:AM19)</f>
-        <v/>
-      </c>
-      <c r="AN20" s="55">
-        <f>SUM(AN13:AN19)</f>
-        <v/>
-      </c>
-      <c r="AO20" s="55">
-        <f>SUM(AO13:AO19)</f>
-        <v/>
-      </c>
-      <c r="AP20" s="55">
-        <f>SUM(AP13:AP19)</f>
-        <v/>
-      </c>
-      <c r="AQ20" s="55">
-        <f>SUM(AQ13:AQ19)</f>
-        <v/>
-      </c>
-      <c r="AR20" s="55">
-        <f>SUM(AR13:AR19)</f>
-        <v/>
-      </c>
-      <c r="AS20" s="55">
-        <f>SUM(AS13:AS19)</f>
-        <v/>
-      </c>
-      <c r="AT20" s="55">
-        <f>SUM(AT13:AT19)</f>
-        <v/>
-      </c>
-      <c r="AU20" s="55">
-        <f>SUM(AU13:AU19)</f>
-        <v/>
-      </c>
-      <c r="AV20" s="55">
-        <f>SUM(AV13:AV19)</f>
-        <v/>
-      </c>
-      <c r="AW20" s="55">
-        <f>SUM(AW13:AW19)</f>
-        <v/>
-      </c>
-      <c r="AX20" s="55">
-        <f>SUM(AX13:AX19)</f>
-        <v/>
-      </c>
-      <c r="AY20" s="55">
-        <f>SUM(AY13:AY19)</f>
-        <v/>
-      </c>
-      <c r="AZ20" s="55">
-        <f>SUM(AZ13:AZ19)</f>
-        <v/>
-      </c>
-      <c r="BA20" s="55">
-        <f>SUM(BA13:BA19)</f>
-        <v/>
-      </c>
-      <c r="BB20" s="55">
-        <f>SUM(BB13:BB19)</f>
-        <v/>
-      </c>
-      <c r="BC20" s="55">
-        <f>SUM(BC13:BC19)</f>
-        <v/>
-      </c>
-      <c r="BD20" s="55">
-        <f>SUM(BD13:BD19)</f>
-        <v/>
-      </c>
-      <c r="BE20" s="55">
-        <f>SUM(BE13:BE19)</f>
-        <v/>
-      </c>
-      <c r="BF20" s="55">
-        <f>SUM(BF13:BF19)</f>
-        <v/>
-      </c>
-      <c r="BG20" s="55">
-        <f>SUM(BG13:BG19)</f>
-        <v/>
-      </c>
-      <c r="BH20" s="55">
-        <f>SUM(BH13:BH19)</f>
-        <v/>
-      </c>
-      <c r="BI20" s="55">
-        <f>SUM(BI13:BI19)</f>
-        <v/>
-      </c>
-      <c r="BJ20" s="55">
-        <f>SUM(BJ13:BJ19)</f>
-        <v/>
-      </c>
-      <c r="BK20" s="55">
-        <f>SUM(BK13:BK19)</f>
-        <v/>
-      </c>
-      <c r="BL20" s="55">
-        <f>SUM(BL13:BL19)</f>
-        <v/>
-      </c>
-      <c r="BM20" s="2" t="n"/>
-      <c r="BN20" s="55">
-        <f>SUM(E20:P20)</f>
-        <v/>
-      </c>
-      <c r="BO20" s="55">
-        <f>SUM(Q20:AB20)</f>
-        <v/>
-      </c>
-      <c r="BP20" s="55">
-        <f>SUM(AC20:AN20)</f>
-        <v/>
-      </c>
-      <c r="BQ20" s="55">
-        <f>SUM(AO20:AZ20)</f>
-        <v/>
-      </c>
-      <c r="BR20" s="55">
-        <f>SUM(BA20:BL20)</f>
-        <v/>
-      </c>
-      <c r="BS20" s="2" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="56" t="inlineStr">
+      <c r="BS19" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="56" t="inlineStr">
         <is>
           <t>Gross profit per unit</t>
         </is>
       </c>
-      <c r="C22" s="52" t="inlineStr">
+      <c r="C21" s="52" t="inlineStr">
         <is>
           <t>EUR/unit</t>
         </is>
       </c>
-      <c r="E22" s="72">
-        <f>IFERROR(('Revenue Forecast'!E50-'Revenue Forecast'!E49-E20)/'Revenue Forecast'!E34,0)</f>
-        <v/>
-      </c>
-      <c r="F22" s="72">
-        <f>IFERROR(('Revenue Forecast'!F50-'Revenue Forecast'!F49-F20)/'Revenue Forecast'!F34,0)</f>
-        <v/>
-      </c>
-      <c r="G22" s="72">
-        <f>IFERROR(('Revenue Forecast'!G50-'Revenue Forecast'!G49-G20)/'Revenue Forecast'!G34,0)</f>
-        <v/>
-      </c>
-      <c r="H22" s="72">
-        <f>IFERROR(('Revenue Forecast'!H50-'Revenue Forecast'!H49-H20)/'Revenue Forecast'!H34,0)</f>
-        <v/>
-      </c>
-      <c r="I22" s="72">
-        <f>IFERROR(('Revenue Forecast'!I50-'Revenue Forecast'!I49-I20)/'Revenue Forecast'!I34,0)</f>
-        <v/>
-      </c>
-      <c r="J22" s="72">
-        <f>IFERROR(('Revenue Forecast'!J50-'Revenue Forecast'!J49-J20)/'Revenue Forecast'!J34,0)</f>
-        <v/>
-      </c>
-      <c r="K22" s="72">
-        <f>IFERROR(('Revenue Forecast'!K50-'Revenue Forecast'!K49-K20)/'Revenue Forecast'!K34,0)</f>
-        <v/>
-      </c>
-      <c r="L22" s="72">
-        <f>IFERROR(('Revenue Forecast'!L50-'Revenue Forecast'!L49-L20)/'Revenue Forecast'!L34,0)</f>
-        <v/>
-      </c>
-      <c r="M22" s="72">
-        <f>IFERROR(('Revenue Forecast'!M50-'Revenue Forecast'!M49-M20)/'Revenue Forecast'!M34,0)</f>
-        <v/>
-      </c>
-      <c r="N22" s="72">
-        <f>IFERROR(('Revenue Forecast'!N50-'Revenue Forecast'!N49-N20)/'Revenue Forecast'!N34,0)</f>
-        <v/>
-      </c>
-      <c r="O22" s="72">
-        <f>IFERROR(('Revenue Forecast'!O50-'Revenue Forecast'!O49-O20)/'Revenue Forecast'!O34,0)</f>
-        <v/>
-      </c>
-      <c r="P22" s="72">
-        <f>IFERROR(('Revenue Forecast'!P50-'Revenue Forecast'!P49-P20)/'Revenue Forecast'!P34,0)</f>
-        <v/>
-      </c>
-      <c r="Q22" s="72">
-        <f>IFERROR(('Revenue Forecast'!Q50-'Revenue Forecast'!Q49-Q20)/'Revenue Forecast'!Q34,0)</f>
-        <v/>
-      </c>
-      <c r="R22" s="72">
-        <f>IFERROR(('Revenue Forecast'!R50-'Revenue Forecast'!R49-R20)/'Revenue Forecast'!R34,0)</f>
-        <v/>
-      </c>
-      <c r="S22" s="72">
-        <f>IFERROR(('Revenue Forecast'!S50-'Revenue Forecast'!S49-S20)/'Revenue Forecast'!S34,0)</f>
-        <v/>
-      </c>
-      <c r="T22" s="72">
-        <f>IFERROR(('Revenue Forecast'!T50-'Revenue Forecast'!T49-T20)/'Revenue Forecast'!T34,0)</f>
-        <v/>
-      </c>
-      <c r="U22" s="72">
-        <f>IFERROR(('Revenue Forecast'!U50-'Revenue Forecast'!U49-U20)/'Revenue Forecast'!U34,0)</f>
-        <v/>
-      </c>
-      <c r="V22" s="72">
-        <f>IFERROR(('Revenue Forecast'!V50-'Revenue Forecast'!V49-V20)/'Revenue Forecast'!V34,0)</f>
-        <v/>
-      </c>
-      <c r="W22" s="72">
-        <f>IFERROR(('Revenue Forecast'!W50-'Revenue Forecast'!W49-W20)/'Revenue Forecast'!W34,0)</f>
-        <v/>
-      </c>
-      <c r="X22" s="72">
-        <f>IFERROR(('Revenue Forecast'!X50-'Revenue Forecast'!X49-X20)/'Revenue Forecast'!X34,0)</f>
-        <v/>
-      </c>
-      <c r="Y22" s="72">
-        <f>IFERROR(('Revenue Forecast'!Y50-'Revenue Forecast'!Y49-Y20)/'Revenue Forecast'!Y34,0)</f>
-        <v/>
-      </c>
-      <c r="Z22" s="72">
-        <f>IFERROR(('Revenue Forecast'!Z50-'Revenue Forecast'!Z49-Z20)/'Revenue Forecast'!Z34,0)</f>
-        <v/>
-      </c>
-      <c r="AA22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AA50-'Revenue Forecast'!AA49-AA20)/'Revenue Forecast'!AA34,0)</f>
-        <v/>
-      </c>
-      <c r="AB22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AB50-'Revenue Forecast'!AB49-AB20)/'Revenue Forecast'!AB34,0)</f>
-        <v/>
-      </c>
-      <c r="AC22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AC50-'Revenue Forecast'!AC49-AC20)/'Revenue Forecast'!AC34,0)</f>
-        <v/>
-      </c>
-      <c r="AD22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AD50-'Revenue Forecast'!AD49-AD20)/'Revenue Forecast'!AD34,0)</f>
-        <v/>
-      </c>
-      <c r="AE22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AE50-'Revenue Forecast'!AE49-AE20)/'Revenue Forecast'!AE34,0)</f>
-        <v/>
-      </c>
-      <c r="AF22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AF50-'Revenue Forecast'!AF49-AF20)/'Revenue Forecast'!AF34,0)</f>
-        <v/>
-      </c>
-      <c r="AG22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AG50-'Revenue Forecast'!AG49-AG20)/'Revenue Forecast'!AG34,0)</f>
-        <v/>
-      </c>
-      <c r="AH22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AH50-'Revenue Forecast'!AH49-AH20)/'Revenue Forecast'!AH34,0)</f>
-        <v/>
-      </c>
-      <c r="AI22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AI50-'Revenue Forecast'!AI49-AI20)/'Revenue Forecast'!AI34,0)</f>
-        <v/>
-      </c>
-      <c r="AJ22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AJ50-'Revenue Forecast'!AJ49-AJ20)/'Revenue Forecast'!AJ34,0)</f>
-        <v/>
-      </c>
-      <c r="AK22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AK50-'Revenue Forecast'!AK49-AK20)/'Revenue Forecast'!AK34,0)</f>
-        <v/>
-      </c>
-      <c r="AL22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AL50-'Revenue Forecast'!AL49-AL20)/'Revenue Forecast'!AL34,0)</f>
-        <v/>
-      </c>
-      <c r="AM22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AM50-'Revenue Forecast'!AM49-AM20)/'Revenue Forecast'!AM34,0)</f>
-        <v/>
-      </c>
-      <c r="AN22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AN50-'Revenue Forecast'!AN49-AN20)/'Revenue Forecast'!AN34,0)</f>
-        <v/>
-      </c>
-      <c r="AO22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AO50-'Revenue Forecast'!AO49-AO20)/'Revenue Forecast'!AO34,0)</f>
-        <v/>
-      </c>
-      <c r="AP22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AP50-'Revenue Forecast'!AP49-AP20)/'Revenue Forecast'!AP34,0)</f>
-        <v/>
-      </c>
-      <c r="AQ22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AQ50-'Revenue Forecast'!AQ49-AQ20)/'Revenue Forecast'!AQ34,0)</f>
-        <v/>
-      </c>
-      <c r="AR22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AR50-'Revenue Forecast'!AR49-AR20)/'Revenue Forecast'!AR34,0)</f>
-        <v/>
-      </c>
-      <c r="AS22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AS50-'Revenue Forecast'!AS49-AS20)/'Revenue Forecast'!AS34,0)</f>
-        <v/>
-      </c>
-      <c r="AT22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AT50-'Revenue Forecast'!AT49-AT20)/'Revenue Forecast'!AT34,0)</f>
-        <v/>
-      </c>
-      <c r="AU22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AU50-'Revenue Forecast'!AU49-AU20)/'Revenue Forecast'!AU34,0)</f>
-        <v/>
-      </c>
-      <c r="AV22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AV50-'Revenue Forecast'!AV49-AV20)/'Revenue Forecast'!AV34,0)</f>
-        <v/>
-      </c>
-      <c r="AW22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AW50-'Revenue Forecast'!AW49-AW20)/'Revenue Forecast'!AW34,0)</f>
-        <v/>
-      </c>
-      <c r="AX22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AX50-'Revenue Forecast'!AX49-AX20)/'Revenue Forecast'!AX34,0)</f>
-        <v/>
-      </c>
-      <c r="AY22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AY50-'Revenue Forecast'!AY49-AY20)/'Revenue Forecast'!AY34,0)</f>
-        <v/>
-      </c>
-      <c r="AZ22" s="72">
-        <f>IFERROR(('Revenue Forecast'!AZ50-'Revenue Forecast'!AZ49-AZ20)/'Revenue Forecast'!AZ34,0)</f>
-        <v/>
-      </c>
-      <c r="BA22" s="72">
-        <f>IFERROR(('Revenue Forecast'!BA50-'Revenue Forecast'!BA49-BA20)/'Revenue Forecast'!BA34,0)</f>
-        <v/>
-      </c>
-      <c r="BB22" s="72">
-        <f>IFERROR(('Revenue Forecast'!BB50-'Revenue Forecast'!BB49-BB20)/'Revenue Forecast'!BB34,0)</f>
-        <v/>
-      </c>
-      <c r="BC22" s="72">
-        <f>IFERROR(('Revenue Forecast'!BC50-'Revenue Forecast'!BC49-BC20)/'Revenue Forecast'!BC34,0)</f>
-        <v/>
-      </c>
-      <c r="BD22" s="72">
-        <f>IFERROR(('Revenue Forecast'!BD50-'Revenue Forecast'!BD49-BD20)/'Revenue Forecast'!BD34,0)</f>
-        <v/>
-      </c>
-      <c r="BE22" s="72">
-        <f>IFERROR(('Revenue Forecast'!BE50-'Revenue Forecast'!BE49-BE20)/'Revenue Forecast'!BE34,0)</f>
-        <v/>
-      </c>
-      <c r="BF22" s="72">
-        <f>IFERROR(('Revenue Forecast'!BF50-'Revenue Forecast'!BF49-BF20)/'Revenue Forecast'!BF34,0)</f>
-        <v/>
-      </c>
-      <c r="BG22" s="72">
-        <f>IFERROR(('Revenue Forecast'!BG50-'Revenue Forecast'!BG49-BG20)/'Revenue Forecast'!BG34,0)</f>
-        <v/>
-      </c>
-      <c r="BH22" s="72">
-        <f>IFERROR(('Revenue Forecast'!BH50-'Revenue Forecast'!BH49-BH20)/'Revenue Forecast'!BH34,0)</f>
-        <v/>
-      </c>
-      <c r="BI22" s="72">
-        <f>IFERROR(('Revenue Forecast'!BI50-'Revenue Forecast'!BI49-BI20)/'Revenue Forecast'!BI34,0)</f>
-        <v/>
-      </c>
-      <c r="BJ22" s="72">
-        <f>IFERROR(('Revenue Forecast'!BJ50-'Revenue Forecast'!BJ49-BJ20)/'Revenue Forecast'!BJ34,0)</f>
-        <v/>
-      </c>
-      <c r="BK22" s="72">
-        <f>IFERROR(('Revenue Forecast'!BK50-'Revenue Forecast'!BK49-BK20)/'Revenue Forecast'!BK34,0)</f>
-        <v/>
-      </c>
-      <c r="BL22" s="72">
-        <f>IFERROR(('Revenue Forecast'!BL50-'Revenue Forecast'!BL49-BL20)/'Revenue Forecast'!BL34,0)</f>
-        <v/>
-      </c>
-      <c r="BN22" s="73">
-        <f>IFERROR(('Revenue Forecast'!BN50-'Revenue Forecast'!BN49-BN20)/'Revenue Forecast'!BN34,0)</f>
-        <v/>
-      </c>
-      <c r="BO22" s="73">
-        <f>IFERROR(('Revenue Forecast'!BO50-'Revenue Forecast'!BO49-BO20)/'Revenue Forecast'!BO34,0)</f>
-        <v/>
-      </c>
-      <c r="BP22" s="73">
-        <f>IFERROR(('Revenue Forecast'!BP50-'Revenue Forecast'!BP49-BP20)/'Revenue Forecast'!BP34,0)</f>
-        <v/>
-      </c>
-      <c r="BQ22" s="73">
-        <f>IFERROR(('Revenue Forecast'!BQ50-'Revenue Forecast'!BQ49-BQ20)/'Revenue Forecast'!BQ34,0)</f>
-        <v/>
-      </c>
-      <c r="BR22" s="73">
-        <f>IFERROR(('Revenue Forecast'!BR50-'Revenue Forecast'!BR49-BR20)/'Revenue Forecast'!BR34,0)</f>
-        <v/>
-      </c>
-      <c r="BT22" s="28" t="inlineStr">
+      <c r="E21" s="72">
+        <f>IFERROR(('Revenue Forecast'!E50-'Revenue Forecast'!E49-E19)/'Revenue Forecast'!E34,0)</f>
+        <v/>
+      </c>
+      <c r="F21" s="72">
+        <f>IFERROR(('Revenue Forecast'!F50-'Revenue Forecast'!F49-F19)/'Revenue Forecast'!F34,0)</f>
+        <v/>
+      </c>
+      <c r="G21" s="72">
+        <f>IFERROR(('Revenue Forecast'!G50-'Revenue Forecast'!G49-G19)/'Revenue Forecast'!G34,0)</f>
+        <v/>
+      </c>
+      <c r="H21" s="72">
+        <f>IFERROR(('Revenue Forecast'!H50-'Revenue Forecast'!H49-H19)/'Revenue Forecast'!H34,0)</f>
+        <v/>
+      </c>
+      <c r="I21" s="72">
+        <f>IFERROR(('Revenue Forecast'!I50-'Revenue Forecast'!I49-I19)/'Revenue Forecast'!I34,0)</f>
+        <v/>
+      </c>
+      <c r="J21" s="72">
+        <f>IFERROR(('Revenue Forecast'!J50-'Revenue Forecast'!J49-J19)/'Revenue Forecast'!J34,0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="72">
+        <f>IFERROR(('Revenue Forecast'!K50-'Revenue Forecast'!K49-K19)/'Revenue Forecast'!K34,0)</f>
+        <v/>
+      </c>
+      <c r="L21" s="72">
+        <f>IFERROR(('Revenue Forecast'!L50-'Revenue Forecast'!L49-L19)/'Revenue Forecast'!L34,0)</f>
+        <v/>
+      </c>
+      <c r="M21" s="72">
+        <f>IFERROR(('Revenue Forecast'!M50-'Revenue Forecast'!M49-M19)/'Revenue Forecast'!M34,0)</f>
+        <v/>
+      </c>
+      <c r="N21" s="72">
+        <f>IFERROR(('Revenue Forecast'!N50-'Revenue Forecast'!N49-N19)/'Revenue Forecast'!N34,0)</f>
+        <v/>
+      </c>
+      <c r="O21" s="72">
+        <f>IFERROR(('Revenue Forecast'!O50-'Revenue Forecast'!O49-O19)/'Revenue Forecast'!O34,0)</f>
+        <v/>
+      </c>
+      <c r="P21" s="72">
+        <f>IFERROR(('Revenue Forecast'!P50-'Revenue Forecast'!P49-P19)/'Revenue Forecast'!P34,0)</f>
+        <v/>
+      </c>
+      <c r="Q21" s="72">
+        <f>IFERROR(('Revenue Forecast'!Q50-'Revenue Forecast'!Q49-Q19)/'Revenue Forecast'!Q34,0)</f>
+        <v/>
+      </c>
+      <c r="R21" s="72">
+        <f>IFERROR(('Revenue Forecast'!R50-'Revenue Forecast'!R49-R19)/'Revenue Forecast'!R34,0)</f>
+        <v/>
+      </c>
+      <c r="S21" s="72">
+        <f>IFERROR(('Revenue Forecast'!S50-'Revenue Forecast'!S49-S19)/'Revenue Forecast'!S34,0)</f>
+        <v/>
+      </c>
+      <c r="T21" s="72">
+        <f>IFERROR(('Revenue Forecast'!T50-'Revenue Forecast'!T49-T19)/'Revenue Forecast'!T34,0)</f>
+        <v/>
+      </c>
+      <c r="U21" s="72">
+        <f>IFERROR(('Revenue Forecast'!U50-'Revenue Forecast'!U49-U19)/'Revenue Forecast'!U34,0)</f>
+        <v/>
+      </c>
+      <c r="V21" s="72">
+        <f>IFERROR(('Revenue Forecast'!V50-'Revenue Forecast'!V49-V19)/'Revenue Forecast'!V34,0)</f>
+        <v/>
+      </c>
+      <c r="W21" s="72">
+        <f>IFERROR(('Revenue Forecast'!W50-'Revenue Forecast'!W49-W19)/'Revenue Forecast'!W34,0)</f>
+        <v/>
+      </c>
+      <c r="X21" s="72">
+        <f>IFERROR(('Revenue Forecast'!X50-'Revenue Forecast'!X49-X19)/'Revenue Forecast'!X34,0)</f>
+        <v/>
+      </c>
+      <c r="Y21" s="72">
+        <f>IFERROR(('Revenue Forecast'!Y50-'Revenue Forecast'!Y49-Y19)/'Revenue Forecast'!Y34,0)</f>
+        <v/>
+      </c>
+      <c r="Z21" s="72">
+        <f>IFERROR(('Revenue Forecast'!Z50-'Revenue Forecast'!Z49-Z19)/'Revenue Forecast'!Z34,0)</f>
+        <v/>
+      </c>
+      <c r="AA21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AA50-'Revenue Forecast'!AA49-AA19)/'Revenue Forecast'!AA34,0)</f>
+        <v/>
+      </c>
+      <c r="AB21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AB50-'Revenue Forecast'!AB49-AB19)/'Revenue Forecast'!AB34,0)</f>
+        <v/>
+      </c>
+      <c r="AC21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AC50-'Revenue Forecast'!AC49-AC19)/'Revenue Forecast'!AC34,0)</f>
+        <v/>
+      </c>
+      <c r="AD21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AD50-'Revenue Forecast'!AD49-AD19)/'Revenue Forecast'!AD34,0)</f>
+        <v/>
+      </c>
+      <c r="AE21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AE50-'Revenue Forecast'!AE49-AE19)/'Revenue Forecast'!AE34,0)</f>
+        <v/>
+      </c>
+      <c r="AF21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AF50-'Revenue Forecast'!AF49-AF19)/'Revenue Forecast'!AF34,0)</f>
+        <v/>
+      </c>
+      <c r="AG21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AG50-'Revenue Forecast'!AG49-AG19)/'Revenue Forecast'!AG34,0)</f>
+        <v/>
+      </c>
+      <c r="AH21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AH50-'Revenue Forecast'!AH49-AH19)/'Revenue Forecast'!AH34,0)</f>
+        <v/>
+      </c>
+      <c r="AI21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AI50-'Revenue Forecast'!AI49-AI19)/'Revenue Forecast'!AI34,0)</f>
+        <v/>
+      </c>
+      <c r="AJ21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AJ50-'Revenue Forecast'!AJ49-AJ19)/'Revenue Forecast'!AJ34,0)</f>
+        <v/>
+      </c>
+      <c r="AK21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AK50-'Revenue Forecast'!AK49-AK19)/'Revenue Forecast'!AK34,0)</f>
+        <v/>
+      </c>
+      <c r="AL21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AL50-'Revenue Forecast'!AL49-AL19)/'Revenue Forecast'!AL34,0)</f>
+        <v/>
+      </c>
+      <c r="AM21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AM50-'Revenue Forecast'!AM49-AM19)/'Revenue Forecast'!AM34,0)</f>
+        <v/>
+      </c>
+      <c r="AN21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AN50-'Revenue Forecast'!AN49-AN19)/'Revenue Forecast'!AN34,0)</f>
+        <v/>
+      </c>
+      <c r="AO21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AO50-'Revenue Forecast'!AO49-AO19)/'Revenue Forecast'!AO34,0)</f>
+        <v/>
+      </c>
+      <c r="AP21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AP50-'Revenue Forecast'!AP49-AP19)/'Revenue Forecast'!AP34,0)</f>
+        <v/>
+      </c>
+      <c r="AQ21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AQ50-'Revenue Forecast'!AQ49-AQ19)/'Revenue Forecast'!AQ34,0)</f>
+        <v/>
+      </c>
+      <c r="AR21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AR50-'Revenue Forecast'!AR49-AR19)/'Revenue Forecast'!AR34,0)</f>
+        <v/>
+      </c>
+      <c r="AS21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AS50-'Revenue Forecast'!AS49-AS19)/'Revenue Forecast'!AS34,0)</f>
+        <v/>
+      </c>
+      <c r="AT21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AT50-'Revenue Forecast'!AT49-AT19)/'Revenue Forecast'!AT34,0)</f>
+        <v/>
+      </c>
+      <c r="AU21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AU50-'Revenue Forecast'!AU49-AU19)/'Revenue Forecast'!AU34,0)</f>
+        <v/>
+      </c>
+      <c r="AV21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AV50-'Revenue Forecast'!AV49-AV19)/'Revenue Forecast'!AV34,0)</f>
+        <v/>
+      </c>
+      <c r="AW21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AW50-'Revenue Forecast'!AW49-AW19)/'Revenue Forecast'!AW34,0)</f>
+        <v/>
+      </c>
+      <c r="AX21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AX50-'Revenue Forecast'!AX49-AX19)/'Revenue Forecast'!AX34,0)</f>
+        <v/>
+      </c>
+      <c r="AY21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AY50-'Revenue Forecast'!AY49-AY19)/'Revenue Forecast'!AY34,0)</f>
+        <v/>
+      </c>
+      <c r="AZ21" s="72">
+        <f>IFERROR(('Revenue Forecast'!AZ50-'Revenue Forecast'!AZ49-AZ19)/'Revenue Forecast'!AZ34,0)</f>
+        <v/>
+      </c>
+      <c r="BA21" s="72">
+        <f>IFERROR(('Revenue Forecast'!BA50-'Revenue Forecast'!BA49-BA19)/'Revenue Forecast'!BA34,0)</f>
+        <v/>
+      </c>
+      <c r="BB21" s="72">
+        <f>IFERROR(('Revenue Forecast'!BB50-'Revenue Forecast'!BB49-BB19)/'Revenue Forecast'!BB34,0)</f>
+        <v/>
+      </c>
+      <c r="BC21" s="72">
+        <f>IFERROR(('Revenue Forecast'!BC50-'Revenue Forecast'!BC49-BC19)/'Revenue Forecast'!BC34,0)</f>
+        <v/>
+      </c>
+      <c r="BD21" s="72">
+        <f>IFERROR(('Revenue Forecast'!BD50-'Revenue Forecast'!BD49-BD19)/'Revenue Forecast'!BD34,0)</f>
+        <v/>
+      </c>
+      <c r="BE21" s="72">
+        <f>IFERROR(('Revenue Forecast'!BE50-'Revenue Forecast'!BE49-BE19)/'Revenue Forecast'!BE34,0)</f>
+        <v/>
+      </c>
+      <c r="BF21" s="72">
+        <f>IFERROR(('Revenue Forecast'!BF50-'Revenue Forecast'!BF49-BF19)/'Revenue Forecast'!BF34,0)</f>
+        <v/>
+      </c>
+      <c r="BG21" s="72">
+        <f>IFERROR(('Revenue Forecast'!BG50-'Revenue Forecast'!BG49-BG19)/'Revenue Forecast'!BG34,0)</f>
+        <v/>
+      </c>
+      <c r="BH21" s="72">
+        <f>IFERROR(('Revenue Forecast'!BH50-'Revenue Forecast'!BH49-BH19)/'Revenue Forecast'!BH34,0)</f>
+        <v/>
+      </c>
+      <c r="BI21" s="72">
+        <f>IFERROR(('Revenue Forecast'!BI50-'Revenue Forecast'!BI49-BI19)/'Revenue Forecast'!BI34,0)</f>
+        <v/>
+      </c>
+      <c r="BJ21" s="72">
+        <f>IFERROR(('Revenue Forecast'!BJ50-'Revenue Forecast'!BJ49-BJ19)/'Revenue Forecast'!BJ34,0)</f>
+        <v/>
+      </c>
+      <c r="BK21" s="72">
+        <f>IFERROR(('Revenue Forecast'!BK50-'Revenue Forecast'!BK49-BK19)/'Revenue Forecast'!BK34,0)</f>
+        <v/>
+      </c>
+      <c r="BL21" s="72">
+        <f>IFERROR(('Revenue Forecast'!BL50-'Revenue Forecast'!BL49-BL19)/'Revenue Forecast'!BL34,0)</f>
+        <v/>
+      </c>
+      <c r="BN21" s="73">
+        <f>IFERROR(('Revenue Forecast'!BN50-'Revenue Forecast'!BN49-BN19)/'Revenue Forecast'!BN34,0)</f>
+        <v/>
+      </c>
+      <c r="BO21" s="73">
+        <f>IFERROR(('Revenue Forecast'!BO50-'Revenue Forecast'!BO49-BO19)/'Revenue Forecast'!BO34,0)</f>
+        <v/>
+      </c>
+      <c r="BP21" s="73">
+        <f>IFERROR(('Revenue Forecast'!BP50-'Revenue Forecast'!BP49-BP19)/'Revenue Forecast'!BP34,0)</f>
+        <v/>
+      </c>
+      <c r="BQ21" s="73">
+        <f>IFERROR(('Revenue Forecast'!BQ50-'Revenue Forecast'!BQ49-BQ19)/'Revenue Forecast'!BQ34,0)</f>
+        <v/>
+      </c>
+      <c r="BR21" s="73">
+        <f>IFERROR(('Revenue Forecast'!BR50-'Revenue Forecast'!BR49-BR19)/'Revenue Forecast'!BR34,0)</f>
+        <v/>
+      </c>
+      <c r="BT21" s="28" t="inlineStr">
         <is>
           <t>trading revenue less cost of sales, per unit; the subsidy is left out</t>
         </is>
@@ -36969,243 +36329,243 @@
         </is>
       </c>
       <c r="E13" s="10">
-        <f>'Revenue Forecast'!E19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(E$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!E19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(E$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="F13" s="10">
-        <f>'Revenue Forecast'!F19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(F$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!F19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(F$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="G13" s="10">
-        <f>'Revenue Forecast'!G19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(G$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!G19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(G$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="H13" s="10">
-        <f>'Revenue Forecast'!H19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(H$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!H19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(H$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="I13" s="10">
-        <f>'Revenue Forecast'!I19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(I$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!I19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(I$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="J13" s="10">
-        <f>'Revenue Forecast'!J19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(J$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!J19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(J$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="K13" s="10">
-        <f>'Revenue Forecast'!K19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(K$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!K19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(K$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="L13" s="10">
-        <f>'Revenue Forecast'!L19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(L$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!L19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(L$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="M13" s="10">
-        <f>'Revenue Forecast'!M19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(M$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!M19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(M$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="N13" s="10">
-        <f>'Revenue Forecast'!N19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(N$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!N19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(N$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="O13" s="10">
-        <f>'Revenue Forecast'!O19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(O$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!O19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(O$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="P13" s="10">
-        <f>'Revenue Forecast'!P19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(P$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!P19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(P$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Q13" s="10">
-        <f>'Revenue Forecast'!Q19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(Q$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!Q19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(Q$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="R13" s="10">
-        <f>'Revenue Forecast'!R19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(R$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!R19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(R$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="S13" s="10">
-        <f>'Revenue Forecast'!S19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(S$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!S19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(S$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="T13" s="10">
-        <f>'Revenue Forecast'!T19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(T$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!T19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(T$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="U13" s="10">
-        <f>'Revenue Forecast'!U19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(U$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!U19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(U$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="V13" s="10">
-        <f>'Revenue Forecast'!V19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(V$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!V19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(V$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="W13" s="10">
-        <f>'Revenue Forecast'!W19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(W$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!W19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(W$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="X13" s="10">
-        <f>'Revenue Forecast'!X19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(X$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!X19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(X$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Y13" s="10">
-        <f>'Revenue Forecast'!Y19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(Y$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!Y19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(Y$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Z13" s="10">
-        <f>'Revenue Forecast'!Z19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(Z$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!Z19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(Z$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AA13" s="10">
-        <f>'Revenue Forecast'!AA19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AA$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AA19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AB13" s="10">
-        <f>'Revenue Forecast'!AB19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AB$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AB19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AC13" s="10">
-        <f>'Revenue Forecast'!AC19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AC$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AC19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AD13" s="10">
-        <f>'Revenue Forecast'!AD19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AD$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AD19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AE13" s="10">
-        <f>'Revenue Forecast'!AE19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AE$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AE19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AF13" s="10">
-        <f>'Revenue Forecast'!AF19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AF$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AF19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AG13" s="10">
-        <f>'Revenue Forecast'!AG19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AG$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AG19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AH13" s="10">
-        <f>'Revenue Forecast'!AH19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AH$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AH19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AI13" s="10">
-        <f>'Revenue Forecast'!AI19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AI$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AI19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AJ13" s="10">
-        <f>'Revenue Forecast'!AJ19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AJ19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AK13" s="10">
-        <f>'Revenue Forecast'!AK19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AK$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AK19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AL13" s="10">
-        <f>'Revenue Forecast'!AL19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AL$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AL19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AM13" s="10">
-        <f>'Revenue Forecast'!AM19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AM$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AM19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AM$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AN13" s="10">
-        <f>'Revenue Forecast'!AN19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AN$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AN19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AN$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AO13" s="10">
-        <f>'Revenue Forecast'!AO19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AO$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AO19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AO$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AP13" s="10">
-        <f>'Revenue Forecast'!AP19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AP$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AP19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AP$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AQ13" s="10">
-        <f>'Revenue Forecast'!AQ19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AQ19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AR13" s="10">
-        <f>'Revenue Forecast'!AR19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AR$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AR19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AR$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AS13" s="10">
-        <f>'Revenue Forecast'!AS19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AS$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AS19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AS$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AT13" s="10">
-        <f>'Revenue Forecast'!AT19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AT$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AT19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AT$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AU13" s="10">
-        <f>'Revenue Forecast'!AU19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AU$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AU19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AU$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AV13" s="10">
-        <f>'Revenue Forecast'!AV19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AV$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AV19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AV$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AW13" s="10">
-        <f>'Revenue Forecast'!AW19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AW$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AW19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AW$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AX13" s="10">
-        <f>'Revenue Forecast'!AX19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AX$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AX19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AX$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AY13" s="10">
-        <f>'Revenue Forecast'!AY19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AY$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AY19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AY$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AZ13" s="10">
-        <f>'Revenue Forecast'!AZ19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!AZ19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BA13" s="10">
-        <f>'Revenue Forecast'!BA19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BA$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BA19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BB13" s="10">
-        <f>'Revenue Forecast'!BB19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BB$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BB19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BC13" s="10">
-        <f>'Revenue Forecast'!BC19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BC$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BC19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BD13" s="10">
-        <f>'Revenue Forecast'!BD19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BD$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BD19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BE13" s="10">
-        <f>'Revenue Forecast'!BE19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BE$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BE19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BF13" s="10">
-        <f>'Revenue Forecast'!BF19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BF$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BF19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BG13" s="10">
-        <f>'Revenue Forecast'!BG19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BG$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BG19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BH13" s="10">
-        <f>'Revenue Forecast'!BH19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BH$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BH19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BI13" s="10">
-        <f>'Revenue Forecast'!BI19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BI$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BI19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BJ13" s="10">
-        <f>'Revenue Forecast'!BJ19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BJ19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BK13" s="10">
-        <f>'Revenue Forecast'!BK19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BK$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BK19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BL13" s="10">
-        <f>'Revenue Forecast'!BL19*Assumptions!$F$133*(1+Assumptions!$F$138)^(YEAR(BL$3)-Assumptions!$F$9)</f>
+        <f>'Revenue Forecast'!BL19*Assumptions!$F$129*(1+Assumptions!$F$134)^(YEAR(BL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BN13" s="53">
@@ -37589,243 +36949,243 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(E$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(E$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="F17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(F$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(F$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="G17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(G$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(G$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="H17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(H$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(H$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="I17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(I$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(I$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="J17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(J$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(J$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="K17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(K$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(K$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="L17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(L$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(L$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="M17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(M$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(M$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="N17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(N$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(N$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="O17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(O$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(O$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="P17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(P$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(P$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Q17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(Q$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(Q$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="R17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(R$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(R$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="S17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(S$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(S$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="T17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(T$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(T$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="U17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(U$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(U$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="V17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(V$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(V$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="W17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(W$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(W$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="X17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(X$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(X$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Y17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(Y$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(Y$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Z17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(Z$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(Z$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AA17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AA$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AB17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AB$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AC17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AC$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AD17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AD$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AE17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AE$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AF17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AF$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AG17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AG$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AH17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AH$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AI17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AI$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AJ17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AK17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AK$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AL17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AL$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AM17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AM$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AM$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AN17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AN$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AN$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AO17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AO$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AO$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AP17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AP$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AP$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AQ17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AR17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AR$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AR$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AS17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AS$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AS$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AT17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AT$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AT$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AU17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AU$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AU$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AV17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AV$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AV$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AW17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AW$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AW$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AX17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AX$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AX$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AY17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AY$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AY$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AZ17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BA17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BA$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BB17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BB$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BC17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BC$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BD17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BD$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BE17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BE$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BF17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BF$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BG17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BG$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BH17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BH$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BI17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BI$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BJ17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BK17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BK$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BL17" s="10">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$138)^(YEAR(BL$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$134)^(YEAR(BL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BN17" s="53">
@@ -37861,243 +37221,243 @@
         </is>
       </c>
       <c r="E18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(E$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(E$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="F18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(F$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(F$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="G18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(G$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(G$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="H18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(H$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(H$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="I18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(I$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(I$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="J18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(J$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(J$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="K18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(K$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(K$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="L18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(L$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(L$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="M18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(M$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(M$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="N18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(N$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(N$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="O18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(O$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(O$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="P18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(P$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(P$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Q18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(Q$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(Q$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="R18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(R$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(R$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="S18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(S$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(S$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="T18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(T$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(T$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="U18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(U$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(U$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="V18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(V$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(V$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="W18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(W$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(W$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="X18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(X$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(X$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Y18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(Y$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(Y$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Z18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(Z$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(Z$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AA18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AA$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AB18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AB$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AC18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AC$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AD18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AD$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AE18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AE$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AF18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AF$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AG18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AG$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AH18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AH$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AI18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AI$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AJ18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AK18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AK$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AL18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AL$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AM18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AM$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AM$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AN18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AN$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AN$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AO18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AO$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AO$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AP18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AP$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AP$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AQ18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AR18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AR$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AR$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AS18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AS$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AS$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AT18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AT$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AT$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AU18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AU$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AU$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AV18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AV$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AV$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AW18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AW$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AW$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AX18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AX$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AX$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AY18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AY$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AY$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AZ18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BA18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BA$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BB18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BB$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BC18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BC$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BD18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BD$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BE18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BE$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BF18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BF$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BG18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BG$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BH18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BH$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BI18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BI$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BJ18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BK18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BK$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BL18" s="10">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$138)^(YEAR(BL$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$134)^(YEAR(BL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BN18" s="53">
@@ -38481,243 +37841,243 @@
         </is>
       </c>
       <c r="E22" s="10">
-        <f>Personnel!E20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(E$3)-Assumptions!$F$9)</f>
+        <f>Personnel!E20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(E$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="F22" s="10">
-        <f>Personnel!F20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(F$3)-Assumptions!$F$9)</f>
+        <f>Personnel!F20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(F$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="G22" s="10">
-        <f>Personnel!G20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(G$3)-Assumptions!$F$9)</f>
+        <f>Personnel!G20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(G$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="H22" s="10">
-        <f>Personnel!H20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(H$3)-Assumptions!$F$9)</f>
+        <f>Personnel!H20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(H$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="I22" s="10">
-        <f>Personnel!I20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(I$3)-Assumptions!$F$9)</f>
+        <f>Personnel!I20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(I$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="J22" s="10">
-        <f>Personnel!J20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(J$3)-Assumptions!$F$9)</f>
+        <f>Personnel!J20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(J$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="K22" s="10">
-        <f>Personnel!K20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(K$3)-Assumptions!$F$9)</f>
+        <f>Personnel!K20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(K$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="L22" s="10">
-        <f>Personnel!L20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(L$3)-Assumptions!$F$9)</f>
+        <f>Personnel!L20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(L$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="M22" s="10">
-        <f>Personnel!M20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(M$3)-Assumptions!$F$9)</f>
+        <f>Personnel!M20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(M$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="N22" s="10">
-        <f>Personnel!N20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(N$3)-Assumptions!$F$9)</f>
+        <f>Personnel!N20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(N$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="O22" s="10">
-        <f>Personnel!O20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(O$3)-Assumptions!$F$9)</f>
+        <f>Personnel!O20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(O$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="P22" s="10">
-        <f>Personnel!P20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(P$3)-Assumptions!$F$9)</f>
+        <f>Personnel!P20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(P$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Q22" s="10">
-        <f>Personnel!Q20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(Q$3)-Assumptions!$F$9)</f>
+        <f>Personnel!Q20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(Q$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="R22" s="10">
-        <f>Personnel!R20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(R$3)-Assumptions!$F$9)</f>
+        <f>Personnel!R20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(R$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="S22" s="10">
-        <f>Personnel!S20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(S$3)-Assumptions!$F$9)</f>
+        <f>Personnel!S20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(S$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="T22" s="10">
-        <f>Personnel!T20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(T$3)-Assumptions!$F$9)</f>
+        <f>Personnel!T20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(T$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="U22" s="10">
-        <f>Personnel!U20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(U$3)-Assumptions!$F$9)</f>
+        <f>Personnel!U20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(U$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="V22" s="10">
-        <f>Personnel!V20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(V$3)-Assumptions!$F$9)</f>
+        <f>Personnel!V20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(V$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="W22" s="10">
-        <f>Personnel!W20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(W$3)-Assumptions!$F$9)</f>
+        <f>Personnel!W20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(W$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="X22" s="10">
-        <f>Personnel!X20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(X$3)-Assumptions!$F$9)</f>
+        <f>Personnel!X20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(X$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Y22" s="10">
-        <f>Personnel!Y20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(Y$3)-Assumptions!$F$9)</f>
+        <f>Personnel!Y20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(Y$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Z22" s="10">
-        <f>Personnel!Z20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(Z$3)-Assumptions!$F$9)</f>
+        <f>Personnel!Z20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(Z$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AA22" s="10">
-        <f>Personnel!AA20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AA$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AA20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AB22" s="10">
-        <f>Personnel!AB20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AB$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AB20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AC22" s="10">
-        <f>Personnel!AC20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AC$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AC20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AD22" s="10">
-        <f>Personnel!AD20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AD$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AD20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AE22" s="10">
-        <f>Personnel!AE20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AE$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AE20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AF22" s="10">
-        <f>Personnel!AF20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AF$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AF20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AG22" s="10">
-        <f>Personnel!AG20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AG$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AG20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AH22" s="10">
-        <f>Personnel!AH20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AH$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AH20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AI22" s="10">
-        <f>Personnel!AI20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AI$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AI20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AJ22" s="10">
-        <f>Personnel!AJ20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AJ20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AK22" s="10">
-        <f>Personnel!AK20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AK$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AK20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AL22" s="10">
-        <f>Personnel!AL20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AL$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AL20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AM22" s="10">
-        <f>Personnel!AM20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AM$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AM20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AM$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AN22" s="10">
-        <f>Personnel!AN20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AN$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AN20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AN$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AO22" s="10">
-        <f>Personnel!AO20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AO$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AO20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AO$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AP22" s="10">
-        <f>Personnel!AP20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AP$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AP20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AP$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AQ22" s="10">
-        <f>Personnel!AQ20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AQ20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AR22" s="10">
-        <f>Personnel!AR20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AR$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AR20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AR$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AS22" s="10">
-        <f>Personnel!AS20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AS$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AS20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AS$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AT22" s="10">
-        <f>Personnel!AT20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AT$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AT20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AT$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AU22" s="10">
-        <f>Personnel!AU20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AU$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AU20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AU$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AV22" s="10">
-        <f>Personnel!AV20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AV$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AV20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AV$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AW22" s="10">
-        <f>Personnel!AW20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AW$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AW20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AW$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AX22" s="10">
-        <f>Personnel!AX20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AX$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AX20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AX$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AY22" s="10">
-        <f>Personnel!AY20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AY$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AY20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AY$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AZ22" s="10">
-        <f>Personnel!AZ20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
+        <f>Personnel!AZ20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BA22" s="10">
-        <f>Personnel!BA20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BA$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BA20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BB22" s="10">
-        <f>Personnel!BB20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BB$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BB20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BC22" s="10">
-        <f>Personnel!BC20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BC$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BC20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BD22" s="10">
-        <f>Personnel!BD20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BD$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BD20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BE22" s="10">
-        <f>Personnel!BE20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BE$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BE20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BF22" s="10">
-        <f>Personnel!BF20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BF$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BF20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BG22" s="10">
-        <f>Personnel!BG20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BG$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BG20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BH22" s="10">
-        <f>Personnel!BH20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BH$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BH20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BI22" s="10">
-        <f>Personnel!BI20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BI$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BI20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BJ22" s="10">
-        <f>Personnel!BJ20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BJ20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BK22" s="10">
-        <f>Personnel!BK20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BK$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BK20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BL22" s="10">
-        <f>Personnel!BL20*(Assumptions!$F$129+Assumptions!$F$130+Assumptions!$F$131)*(1+Assumptions!$F$138)^(YEAR(BL$3)-Assumptions!$F$9)</f>
+        <f>Personnel!BL20*(Assumptions!$F$125+Assumptions!$F$126+Assumptions!$F$127)*(1+Assumptions!$F$134)^(YEAR(BL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BN22" s="53">
@@ -38762,239 +38122,239 @@
         <v/>
       </c>
       <c r="F23" s="10">
-        <f>MAX(0,Personnel!F20-Personnel!E20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(F$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!F20-Personnel!E20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(F$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="G23" s="10">
-        <f>MAX(0,Personnel!G20-Personnel!F20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(G$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!G20-Personnel!F20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(G$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="H23" s="10">
-        <f>MAX(0,Personnel!H20-Personnel!G20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(H$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!H20-Personnel!G20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(H$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="I23" s="10">
-        <f>MAX(0,Personnel!I20-Personnel!H20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(I$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!I20-Personnel!H20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(I$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="J23" s="10">
-        <f>MAX(0,Personnel!J20-Personnel!I20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(J$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!J20-Personnel!I20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(J$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="K23" s="10">
-        <f>MAX(0,Personnel!K20-Personnel!J20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(K$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!K20-Personnel!J20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(K$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="L23" s="10">
-        <f>MAX(0,Personnel!L20-Personnel!K20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(L$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!L20-Personnel!K20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(L$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="M23" s="10">
-        <f>MAX(0,Personnel!M20-Personnel!L20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(M$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!M20-Personnel!L20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(M$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="N23" s="10">
-        <f>MAX(0,Personnel!N20-Personnel!M20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(N$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!N20-Personnel!M20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(N$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="O23" s="10">
-        <f>MAX(0,Personnel!O20-Personnel!N20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(O$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!O20-Personnel!N20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(O$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="P23" s="10">
-        <f>MAX(0,Personnel!P20-Personnel!O20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(P$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!P20-Personnel!O20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(P$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Q23" s="10">
-        <f>MAX(0,Personnel!Q20-Personnel!P20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(Q$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!Q20-Personnel!P20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(Q$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="R23" s="10">
-        <f>MAX(0,Personnel!R20-Personnel!Q20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(R$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!R20-Personnel!Q20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(R$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="S23" s="10">
-        <f>MAX(0,Personnel!S20-Personnel!R20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(S$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!S20-Personnel!R20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(S$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="T23" s="10">
-        <f>MAX(0,Personnel!T20-Personnel!S20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(T$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!T20-Personnel!S20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(T$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="U23" s="10">
-        <f>MAX(0,Personnel!U20-Personnel!T20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(U$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!U20-Personnel!T20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(U$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="V23" s="10">
-        <f>MAX(0,Personnel!V20-Personnel!U20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(V$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!V20-Personnel!U20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(V$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="W23" s="10">
-        <f>MAX(0,Personnel!W20-Personnel!V20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(W$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!W20-Personnel!V20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(W$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="X23" s="10">
-        <f>MAX(0,Personnel!X20-Personnel!W20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(X$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!X20-Personnel!W20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(X$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Y23" s="10">
-        <f>MAX(0,Personnel!Y20-Personnel!X20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(Y$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!Y20-Personnel!X20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(Y$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Z23" s="10">
-        <f>MAX(0,Personnel!Z20-Personnel!Y20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(Z$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!Z20-Personnel!Y20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(Z$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AA23" s="10">
-        <f>MAX(0,Personnel!AA20-Personnel!Z20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AA$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AA20-Personnel!Z20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AB23" s="10">
-        <f>MAX(0,Personnel!AB20-Personnel!AA20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AB$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AB20-Personnel!AA20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AC23" s="10">
-        <f>MAX(0,Personnel!AC20-Personnel!AB20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AC$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AC20-Personnel!AB20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AD23" s="10">
-        <f>MAX(0,Personnel!AD20-Personnel!AC20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AD$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AD20-Personnel!AC20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AE23" s="10">
-        <f>MAX(0,Personnel!AE20-Personnel!AD20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AE$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AE20-Personnel!AD20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AF23" s="10">
-        <f>MAX(0,Personnel!AF20-Personnel!AE20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AF$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AF20-Personnel!AE20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AG23" s="10">
-        <f>MAX(0,Personnel!AG20-Personnel!AF20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AG$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AG20-Personnel!AF20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AH23" s="10">
-        <f>MAX(0,Personnel!AH20-Personnel!AG20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AH$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AH20-Personnel!AG20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AI23" s="10">
-        <f>MAX(0,Personnel!AI20-Personnel!AH20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AI$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AI20-Personnel!AH20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AJ23" s="10">
-        <f>MAX(0,Personnel!AJ20-Personnel!AI20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AJ20-Personnel!AI20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AK23" s="10">
-        <f>MAX(0,Personnel!AK20-Personnel!AJ20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AK$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AK20-Personnel!AJ20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AL23" s="10">
-        <f>MAX(0,Personnel!AL20-Personnel!AK20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AL$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AL20-Personnel!AK20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AM23" s="10">
-        <f>MAX(0,Personnel!AM20-Personnel!AL20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AM$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AM20-Personnel!AL20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AM$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AN23" s="10">
-        <f>MAX(0,Personnel!AN20-Personnel!AM20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AN$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AN20-Personnel!AM20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AN$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AO23" s="10">
-        <f>MAX(0,Personnel!AO20-Personnel!AN20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AO$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AO20-Personnel!AN20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AO$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AP23" s="10">
-        <f>MAX(0,Personnel!AP20-Personnel!AO20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AP$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AP20-Personnel!AO20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AP$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AQ23" s="10">
-        <f>MAX(0,Personnel!AQ20-Personnel!AP20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AQ20-Personnel!AP20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AR23" s="10">
-        <f>MAX(0,Personnel!AR20-Personnel!AQ20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AR$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AR20-Personnel!AQ20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AR$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AS23" s="10">
-        <f>MAX(0,Personnel!AS20-Personnel!AR20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AS$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AS20-Personnel!AR20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AS$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AT23" s="10">
-        <f>MAX(0,Personnel!AT20-Personnel!AS20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AT$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AT20-Personnel!AS20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AT$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AU23" s="10">
-        <f>MAX(0,Personnel!AU20-Personnel!AT20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AU$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AU20-Personnel!AT20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AU$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AV23" s="10">
-        <f>MAX(0,Personnel!AV20-Personnel!AU20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AV$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AV20-Personnel!AU20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AV$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AW23" s="10">
-        <f>MAX(0,Personnel!AW20-Personnel!AV20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AW$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AW20-Personnel!AV20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AW$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AX23" s="10">
-        <f>MAX(0,Personnel!AX20-Personnel!AW20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AX$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AX20-Personnel!AW20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AX$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AY23" s="10">
-        <f>MAX(0,Personnel!AY20-Personnel!AX20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AY$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AY20-Personnel!AX20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AY$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AZ23" s="10">
-        <f>MAX(0,Personnel!AZ20-Personnel!AY20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!AZ20-Personnel!AY20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BA23" s="10">
-        <f>MAX(0,Personnel!BA20-Personnel!AZ20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BA$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BA20-Personnel!AZ20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BB23" s="10">
-        <f>MAX(0,Personnel!BB20-Personnel!BA20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BB$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BB20-Personnel!BA20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BC23" s="10">
-        <f>MAX(0,Personnel!BC20-Personnel!BB20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BC$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BC20-Personnel!BB20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BD23" s="10">
-        <f>MAX(0,Personnel!BD20-Personnel!BC20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BD$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BD20-Personnel!BC20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BE23" s="10">
-        <f>MAX(0,Personnel!BE20-Personnel!BD20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BE$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BE20-Personnel!BD20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BF23" s="10">
-        <f>MAX(0,Personnel!BF20-Personnel!BE20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BF$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BF20-Personnel!BE20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BG23" s="10">
-        <f>MAX(0,Personnel!BG20-Personnel!BF20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BG$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BG20-Personnel!BF20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BH23" s="10">
-        <f>MAX(0,Personnel!BH20-Personnel!BG20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BH$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BH20-Personnel!BG20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BI23" s="10">
-        <f>MAX(0,Personnel!BI20-Personnel!BH20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BI$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BI20-Personnel!BH20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BJ23" s="10">
-        <f>MAX(0,Personnel!BJ20-Personnel!BI20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BJ20-Personnel!BI20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BK23" s="10">
-        <f>MAX(0,Personnel!BK20-Personnel!BJ20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BK$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BK20-Personnel!BJ20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BL23" s="10">
-        <f>MAX(0,Personnel!BL20-Personnel!BK20)*Assumptions!$F$132*(1+Assumptions!$F$138)^(YEAR(BL$3)-Assumptions!$F$9)</f>
+        <f>MAX(0,Personnel!BL20-Personnel!BK20)*Assumptions!$F$128*(1+Assumptions!$F$134)^(YEAR(BL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BN23" s="53">
@@ -39307,243 +38667,243 @@
         </is>
       </c>
       <c r="E25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(E$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(E$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="F25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(F$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(F$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="G25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(G$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(G$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="H25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(H$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(H$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="I25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(I$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(I$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="J25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(J$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(J$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="K25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(K$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(K$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="L25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(L$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(L$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="M25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(M$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(M$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="N25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(N$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(N$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="O25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(O$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(O$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="P25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(P$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(P$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Q25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(Q$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(Q$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="R25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(R$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(R$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="S25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(S$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(S$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="T25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(T$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(T$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="U25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(U$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(U$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="V25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(V$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(V$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="W25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(W$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(W$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="X25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(X$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(X$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Y25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(Y$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(Y$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Z25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(Z$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(Z$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AA25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AA$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AB25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AB$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AC25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AC$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AD25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AD$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AE25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AE$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AF25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AF$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AG25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AG$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AH25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AH$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AI25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AI$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AJ25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AK25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AK$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AL25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AL$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AM25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AM$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AM$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AN25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AN$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AN$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AO25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AO$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AO$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AP25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AP$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AP$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AQ25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AR25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AR$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AR$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AS25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AS$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AS$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AT25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AT$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AT$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AU25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AU$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AU$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AV25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AV$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AV$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AW25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AW$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AW$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AX25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AX$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AX$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AY25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AY$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AY$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AZ25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BA25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BA$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BB25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BB$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BC25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BC$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BD25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BD$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BE25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BE$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BF25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BF$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BG25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BG$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BH25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BH$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BI25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BI$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BJ25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BK25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BK$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BL25" s="10">
-        <f>Assumptions!$F$134*(1+Assumptions!$F$138)^(YEAR(BL$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$130*(1+Assumptions!$F$134)^(YEAR(BL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BN25" s="53">
@@ -39579,243 +38939,243 @@
         </is>
       </c>
       <c r="E26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(E$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(E$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="F26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(F$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(F$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="G26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(G$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(G$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="H26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(H$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(H$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="I26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(I$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(I$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="J26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(J$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(J$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="K26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(K$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(K$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="L26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(L$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(L$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="M26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(M$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(M$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="N26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(N$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(N$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="O26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(O$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(O$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="P26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(P$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(P$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Q26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(Q$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(Q$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="R26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(R$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(R$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="S26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(S$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(S$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="T26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(T$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(T$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="U26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(U$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(U$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="V26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(V$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(V$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="W26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(W$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(W$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="X26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(X$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(X$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Y26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(Y$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(Y$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="Z26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(Z$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(Z$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AA26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AA$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AB26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AB$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AC26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AC$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AD26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AD$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AE26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AE$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AF26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AF$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AG26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AG$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AH26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AH$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AI26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AI$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AJ26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AK26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AK$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AL26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AL$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AM26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AM$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AM$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AN26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AN$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AN$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AO26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AO$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AO$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AP26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AP$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AP$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AQ26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AQ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AR26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AR$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AR$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AS26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AS$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AS$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AT26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AT$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AT$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AU26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AU$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AU$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AV26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AV$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AV$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AW26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AW$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AW$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AX26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AX$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AX$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AY26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AY$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AY$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="AZ26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(AZ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BA26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BA$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BA$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BB26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BB$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BB$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BC26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BC$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BC$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BD26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BD$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BD$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BE26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BE$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BE$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BF26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BF$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BF$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BG26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BG$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BG$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BH26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BH$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BH$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BI26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BI$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BI$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BJ26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BJ$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BK26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BK$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BK$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BL26" s="10">
-        <f>Assumptions!$F$135*(1+Assumptions!$F$138)^(YEAR(BL$3)-Assumptions!$F$9)</f>
+        <f>Assumptions!$F$131*(1+Assumptions!$F$134)^(YEAR(BL$3)-Assumptions!$F$9)</f>
         <v/>
       </c>
       <c r="BN26" s="53">

--- a/models/Tarnoc_v2_2026-09-07.xlsx
+++ b/models/Tarnoc_v2_2026-09-07.xlsx
@@ -4929,7 +4929,7 @@
         <v>0</v>
       </c>
       <c r="E60" s="47" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F60" s="47" t="n">
         <v>0.25</v>
@@ -5033,7 +5033,7 @@
         <v>0</v>
       </c>
       <c r="E64" s="49" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F64" s="49" t="n">
         <v>1.5</v>
@@ -5855,10 +5855,10 @@
         <v>0</v>
       </c>
       <c r="E99" s="41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F99" s="41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G99" s="41" t="n">
         <v>3</v>
@@ -6165,10 +6165,10 @@
         </is>
       </c>
       <c r="D112" s="41" t="n">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="E112" s="41" t="n">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="F112" s="42">
         <f>IF(Assumptions!$E$5=2,E112,D112)</f>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="J112" s="30" t="inlineStr">
         <is>
-          <t>sizes the field service team: units on a service contract divided by this number = engineers to hire. Each unit gets one visit a year, an engineer does three to four a day</t>
+          <t>sizes the field service team: units on a service contract divided by this number = engineers to hire. Each unit gets one visit a year plus breakdown cover; market range 600 to 900</t>
         </is>
       </c>
     </row>

--- a/models/Tarnoc_v2_2026-09-07.xlsx
+++ b/models/Tarnoc_v2_2026-09-07.xlsx
@@ -1205,21 +1205,21 @@
     <row r="38">
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Base, EUR3m: 310 / 1,200 / 3,900 / 7,200 units in 2027 to 2030, EUR123m revenue in 2030. Gross margin 10%, 25%, 37%, 37%. EBITDA -2.1m, +1.0m, +17m, +34m. 85 people.</t>
+          <t>Base, EUR3m: 350 / 1,350 / 4,100 / 7,400 units in 2027 to 2030, EUR127m revenue in 2030. Gross margin 10%, 25%, 37%, 37%. EBITDA -2.5m, +0.8m, +18m, +34m. 95 people.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Cash low EUR0.9m in December 2027, about four months of cost; 69% of the raise used.</t>
+          <t xml:space="preserve">     Cash low EUR0.6m in December 2027, about two months of cost; 81% of the raise used.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Aggressive, EUR10m: 2,800 / 6,900 / 11,700 / 18,800 units, EUR321m revenue in 2030. Gross margin 28%, 38%, 37%, 37%. EBITDA +4.8m, +23m, +45m, +80m. 289 people.</t>
+          <t>Aggressive, EUR10m: 2,800 / 6,900 / 11,700 / 18,800 units, EUR321m revenue in 2030. Gross margin 28%, 38%, 37%, 37%. EBITDA +4.8m, +23m, +45m, +79m. 301 people.</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
     <row r="47">
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Soft spot 1. Base turns on about 100 units: 2028 plus 2029 volume is 5,100 against a 5,000 tier. At 4,900, 2028 costs EUR2,900 more per unit and EBITDA goes back to about -2.7m.</t>
+          <t>Soft spot 1. Base turns on about 500 units: 2028 plus 2029 volume is 5,500 against a 5,000 tier. Below 5,000, 2028 costs EUR2,900 more per unit and EBITDA goes back to about -3m.</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
     <row r="90">
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Base: the 5,000-unit cliff in 2028. A one-quarter delay in the 2029 ramp is enough to miss it, and with it the year's margin step.</t>
+          <t>Base: the 5,000-unit cliff in 2028 (2028 plus 2029 volume is 5,500 against the 5,000 tier) and two months of cash cover in December 2027. A one-quarter delay in the 2029 ramp costs the margin step.</t>
         </is>
       </c>
     </row>

--- a/models/Tarnoc_v2_2026-09-07.xlsx
+++ b/models/Tarnoc_v2_2026-09-07.xlsx
@@ -5371,7 +5371,7 @@
     <row r="78">
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>BUILD CAPACITY AND CAPEX  (assembly partner first, in-house takes over)</t>
+          <t>BUILD CAPACITY AND CAPEX  (assembly partner in both cases; in-house lines and capex in the aggressive case only)</t>
         </is>
       </c>
       <c r="C78" s="2" t="n"/>
@@ -5508,6 +5508,11 @@
         <f>IF(Assumptions!$E$5=2,E83,D83)</f>
         <v/>
       </c>
+      <c r="J83" s="30" t="inlineStr">
+        <is>
+          <t>aggressive only: the base case has no in-house line, so rows 83 to 89 do nothing in base</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="B84" s="6" t="inlineStr">
@@ -5532,7 +5537,7 @@
       </c>
       <c r="J84" s="30" t="inlineStr">
         <is>
-          <t>EUR250 per unit of annual capacity; peers run EUR250 to 600</t>
+          <t>aggressive only. EUR250 per unit of annual capacity; peers run EUR250 to 600</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5564,7 @@
       </c>
       <c r="J85" s="30" t="inlineStr">
         <is>
-          <t>automated test, balancing and handling, which is why a line runs on 25 operators rather than 35</t>
+          <t>aggressive only. Automated test, balancing and handling, which is why a line runs on 25 operators rather than 35</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5645,7 @@
       </c>
       <c r="J88" s="30" t="inlineStr">
         <is>
-          <t>the building and the machines, not the people</t>
+          <t>aggressive only: the building and the machines, not the people</t>
         </is>
       </c>
     </row>
@@ -5664,6 +5669,11 @@
       <c r="F89" s="42">
         <f>IF(Assumptions!$E$5=2,E89,D89)</f>
         <v/>
+      </c>
+      <c r="J89" s="30" t="inlineStr">
+        <is>
+          <t>aggressive only: the base case has no fixed assets</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -6111,7 +6121,7 @@
     <row r="110">
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Marketing spend per marketer</t>
+          <t>Yearly marketing budget one marketer can run</t>
         </is>
       </c>
       <c r="C110" s="28" t="inlineStr">
@@ -6120,14 +6130,19 @@
         </is>
       </c>
       <c r="D110" s="33" t="n">
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
       <c r="E110" s="33" t="n">
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
       <c r="F110" s="34">
         <f>IF(Assumptions!$E$5=2,E110,D110)</f>
         <v/>
+      </c>
+      <c r="J110" s="30" t="inlineStr">
+        <is>
+          <t>sizes the marketing team only: the floor above plus one more person for every EUR1.5m of yearly spend. Not a spend. Benchmarks: one marketer per EUR1-1.5m of media</t>
+        </is>
       </c>
     </row>
     <row r="111">

--- a/models/Tarnoc_v2_2026-09-07.xlsx
+++ b/models/Tarnoc_v2_2026-09-07.xlsx
@@ -1548,12 +1548,12 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>2 + 1 per EUR3m spend</t>
+          <t>2 + 1 per EUR1.5m of yearly spend</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>supported</t>
         </is>
       </c>
       <c r="E63" s="17" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>For 289 staff, 14-22; HR alone needs 4-6</t>
+          <t>Fine for 95 staff; for 300 staff 14-22, and HR alone needs 4-6</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="J83" s="30" t="inlineStr">
         <is>
-          <t>aggressive only: the base case has no in-house line, so rows 83 to 89 do nothing in base</t>
+          <t>aggressive only: the base case has no in-house line, so the rows below do nothing in base</t>
         </is>
       </c>
     </row>

--- a/models/Tarnoc_v2_2026-09-07.xlsx
+++ b/models/Tarnoc_v2_2026-09-07.xlsx
@@ -1205,21 +1205,21 @@
     <row r="38">
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Base, EUR3m: 350 / 1,350 / 4,100 / 7,400 units in 2027 to 2030, EUR127m revenue in 2030. Gross margin 10%, 25%, 37%, 37%. EBITDA -2.5m, +0.8m, +18m, +34m. 95 people.</t>
+          <t>Base, EUR3m: 354 / 1,344 / 4,122 / 7,407 units in 2027 to 2030, EUR126m revenue in 2030. Gross margin 10%, 25%, 37%, 37%. EBITDA -2.5m, +0.9m, +17m, +34m. 95 people.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Cash low EUR0.6m in December 2027, about two months of cost; 81% of the raise used.</t>
+          <t xml:space="preserve">     Cash low EUR0.6m in December 2027, about two months of cost; 80% of the raise used.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Aggressive, EUR10m: 2,800 / 6,900 / 11,700 / 18,800 units, EUR321m revenue in 2030. Gross margin 28%, 38%, 37%, 37%. EBITDA +4.8m, +23m, +45m, +79m. 301 people.</t>
+          <t>Aggressive, EUR10m: 2,812 / 6,864 / 11,730 / 18,780 units, EUR321m revenue in 2030. Gross margin 28%, 38%, 37%, 37%. EBITDA +4.8m, +23m, +45m, +79m. 302 people.</t>
         </is>
       </c>
     </row>
@@ -23655,12 +23655,12 @@
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Reps hired</t>
+          <t>Rep hiring rate</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>FTE</t>
+          <t>FTE/month</t>
         </is>
       </c>
       <c r="E16" s="66">
@@ -23925,7 +23925,7 @@
       </c>
       <c r="BT16" s="30" t="inlineStr">
         <is>
-          <t>no sales reps before the first month we can sell</t>
+          <t>the planned rate, which can be less than one a month</t>
         </is>
       </c>
     </row>
@@ -23941,243 +23941,243 @@
         </is>
       </c>
       <c r="E17" s="13">
-        <f>Assumptions!$F$72+E16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:E16),0)</f>
         <v/>
       </c>
       <c r="F17" s="13">
-        <f>E17+F16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:F16),0)</f>
         <v/>
       </c>
       <c r="G17" s="13">
-        <f>F17+G16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:G16),0)</f>
         <v/>
       </c>
       <c r="H17" s="13">
-        <f>G17+H16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:H16),0)</f>
         <v/>
       </c>
       <c r="I17" s="13">
-        <f>H17+I16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:I16),0)</f>
         <v/>
       </c>
       <c r="J17" s="13">
-        <f>I17+J16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:J16),0)</f>
         <v/>
       </c>
       <c r="K17" s="13">
-        <f>J17+K16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:K16),0)</f>
         <v/>
       </c>
       <c r="L17" s="13">
-        <f>K17+L16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:L16),0)</f>
         <v/>
       </c>
       <c r="M17" s="13">
-        <f>L17+M16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:M16),0)</f>
         <v/>
       </c>
       <c r="N17" s="13">
-        <f>M17+N16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:N16),0)</f>
         <v/>
       </c>
       <c r="O17" s="13">
-        <f>N17+O16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:O16),0)</f>
         <v/>
       </c>
       <c r="P17" s="13">
-        <f>O17+P16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:P16),0)</f>
         <v/>
       </c>
       <c r="Q17" s="13">
-        <f>P17+Q16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:Q16),0)</f>
         <v/>
       </c>
       <c r="R17" s="13">
-        <f>Q17+R16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:R16),0)</f>
         <v/>
       </c>
       <c r="S17" s="13">
-        <f>R17+S16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:S16),0)</f>
         <v/>
       </c>
       <c r="T17" s="13">
-        <f>S17+T16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:T16),0)</f>
         <v/>
       </c>
       <c r="U17" s="13">
-        <f>T17+U16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:U16),0)</f>
         <v/>
       </c>
       <c r="V17" s="13">
-        <f>U17+V16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:V16),0)</f>
         <v/>
       </c>
       <c r="W17" s="13">
-        <f>V17+W16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:W16),0)</f>
         <v/>
       </c>
       <c r="X17" s="13">
-        <f>W17+X16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:X16),0)</f>
         <v/>
       </c>
       <c r="Y17" s="13">
-        <f>X17+Y16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:Y16),0)</f>
         <v/>
       </c>
       <c r="Z17" s="13">
-        <f>Y17+Z16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:Z16),0)</f>
         <v/>
       </c>
       <c r="AA17" s="13">
-        <f>Z17+AA16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AA16),0)</f>
         <v/>
       </c>
       <c r="AB17" s="13">
-        <f>AA17+AB16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AB16),0)</f>
         <v/>
       </c>
       <c r="AC17" s="13">
-        <f>AB17+AC16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AC16),0)</f>
         <v/>
       </c>
       <c r="AD17" s="13">
-        <f>AC17+AD16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AD16),0)</f>
         <v/>
       </c>
       <c r="AE17" s="13">
-        <f>AD17+AE16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AE16),0)</f>
         <v/>
       </c>
       <c r="AF17" s="13">
-        <f>AE17+AF16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AF16),0)</f>
         <v/>
       </c>
       <c r="AG17" s="13">
-        <f>AF17+AG16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AG16),0)</f>
         <v/>
       </c>
       <c r="AH17" s="13">
-        <f>AG17+AH16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AH16),0)</f>
         <v/>
       </c>
       <c r="AI17" s="13">
-        <f>AH17+AI16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AI16),0)</f>
         <v/>
       </c>
       <c r="AJ17" s="13">
-        <f>AI17+AJ16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AJ16),0)</f>
         <v/>
       </c>
       <c r="AK17" s="13">
-        <f>AJ17+AK16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AK16),0)</f>
         <v/>
       </c>
       <c r="AL17" s="13">
-        <f>AK17+AL16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AL16),0)</f>
         <v/>
       </c>
       <c r="AM17" s="13">
-        <f>AL17+AM16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AM16),0)</f>
         <v/>
       </c>
       <c r="AN17" s="13">
-        <f>AM17+AN16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AN16),0)</f>
         <v/>
       </c>
       <c r="AO17" s="13">
-        <f>AN17+AO16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AO16),0)</f>
         <v/>
       </c>
       <c r="AP17" s="13">
-        <f>AO17+AP16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AP16),0)</f>
         <v/>
       </c>
       <c r="AQ17" s="13">
-        <f>AP17+AQ16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AQ16),0)</f>
         <v/>
       </c>
       <c r="AR17" s="13">
-        <f>AQ17+AR16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AR16),0)</f>
         <v/>
       </c>
       <c r="AS17" s="13">
-        <f>AR17+AS16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AS16),0)</f>
         <v/>
       </c>
       <c r="AT17" s="13">
-        <f>AS17+AT16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AT16),0)</f>
         <v/>
       </c>
       <c r="AU17" s="13">
-        <f>AT17+AU16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AU16),0)</f>
         <v/>
       </c>
       <c r="AV17" s="13">
-        <f>AU17+AV16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AV16),0)</f>
         <v/>
       </c>
       <c r="AW17" s="13">
-        <f>AV17+AW16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AW16),0)</f>
         <v/>
       </c>
       <c r="AX17" s="13">
-        <f>AW17+AX16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AX16),0)</f>
         <v/>
       </c>
       <c r="AY17" s="13">
-        <f>AX17+AY16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AY16),0)</f>
         <v/>
       </c>
       <c r="AZ17" s="13">
-        <f>AY17+AZ16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:AZ16),0)</f>
         <v/>
       </c>
       <c r="BA17" s="13">
-        <f>AZ17+BA16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:BA16),0)</f>
         <v/>
       </c>
       <c r="BB17" s="13">
-        <f>BA17+BB16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:BB16),0)</f>
         <v/>
       </c>
       <c r="BC17" s="13">
-        <f>BB17+BC16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:BC16),0)</f>
         <v/>
       </c>
       <c r="BD17" s="13">
-        <f>BC17+BD16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:BD16),0)</f>
         <v/>
       </c>
       <c r="BE17" s="13">
-        <f>BD17+BE16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:BE16),0)</f>
         <v/>
       </c>
       <c r="BF17" s="13">
-        <f>BE17+BF16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:BF16),0)</f>
         <v/>
       </c>
       <c r="BG17" s="13">
-        <f>BF17+BG16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:BG16),0)</f>
         <v/>
       </c>
       <c r="BH17" s="13">
-        <f>BG17+BH16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:BH16),0)</f>
         <v/>
       </c>
       <c r="BI17" s="13">
-        <f>BH17+BI16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:BI16),0)</f>
         <v/>
       </c>
       <c r="BJ17" s="13">
-        <f>BI17+BJ16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:BJ16),0)</f>
         <v/>
       </c>
       <c r="BK17" s="13">
-        <f>BJ17+BK16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:BK16),0)</f>
         <v/>
       </c>
       <c r="BL17" s="13">
-        <f>BK17+BL16</f>
+        <f>ROUNDDOWN(Assumptions!$F$72+SUM($E16:BL16),0)</f>
         <v/>
       </c>
       <c r="BN17" s="68">
@@ -24200,6 +24200,11 @@
         <f>BL17</f>
         <v/>
       </c>
+      <c r="BT17" s="30" t="inlineStr">
+        <is>
+          <t>whole people only, so half a rep a month means one every second month</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
@@ -24481,277 +24486,277 @@
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Installer partners signed</t>
+          <t>Partner signing rate</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>partners</t>
-        </is>
-      </c>
-      <c r="E19" s="13">
+          <t>partners/month</t>
+        </is>
+      </c>
+      <c r="E19" s="66">
         <f>IF(E$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(E$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="66">
         <f>IF(F$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(F$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="66">
         <f>IF(G$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(G$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="66">
         <f>IF(H$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(H$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="66">
         <f>IF(I$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(I$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="J19" s="13">
+      <c r="J19" s="66">
         <f>IF(J$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(J$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="K19" s="13">
+      <c r="K19" s="66">
         <f>IF(K$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(K$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="L19" s="13">
+      <c r="L19" s="66">
         <f>IF(L$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(L$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="M19" s="13">
+      <c r="M19" s="66">
         <f>IF(M$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(M$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="N19" s="13">
+      <c r="N19" s="66">
         <f>IF(N$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(N$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="O19" s="13">
+      <c r="O19" s="66">
         <f>IF(O$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(O$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="P19" s="13">
+      <c r="P19" s="66">
         <f>IF(P$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(P$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="Q19" s="13">
+      <c r="Q19" s="66">
         <f>IF(Q$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(Q$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="R19" s="13">
+      <c r="R19" s="66">
         <f>IF(R$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(R$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="S19" s="13">
+      <c r="S19" s="66">
         <f>IF(S$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(S$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="T19" s="13">
+      <c r="T19" s="66">
         <f>IF(T$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(T$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="U19" s="13">
+      <c r="U19" s="66">
         <f>IF(U$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(U$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="V19" s="13">
+      <c r="V19" s="66">
         <f>IF(V$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(V$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="W19" s="13">
+      <c r="W19" s="66">
         <f>IF(W$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(W$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="X19" s="13">
+      <c r="X19" s="66">
         <f>IF(X$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(X$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="Y19" s="13">
+      <c r="Y19" s="66">
         <f>IF(Y$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(Y$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="Z19" s="13">
+      <c r="Z19" s="66">
         <f>IF(Z$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(Z$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AA19" s="13">
+      <c r="AA19" s="66">
         <f>IF(AA$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AA$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AB19" s="13">
+      <c r="AB19" s="66">
         <f>IF(AB$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AB$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AC19" s="13">
+      <c r="AC19" s="66">
         <f>IF(AC$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AC$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AD19" s="13">
+      <c r="AD19" s="66">
         <f>IF(AD$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AD$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AE19" s="13">
+      <c r="AE19" s="66">
         <f>IF(AE$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AE$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AF19" s="13">
+      <c r="AF19" s="66">
         <f>IF(AF$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AF$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AG19" s="13">
+      <c r="AG19" s="66">
         <f>IF(AG$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AG$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AH19" s="13">
+      <c r="AH19" s="66">
         <f>IF(AH$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AH$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AI19" s="13">
+      <c r="AI19" s="66">
         <f>IF(AI$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AI$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AJ19" s="13">
+      <c r="AJ19" s="66">
         <f>IF(AJ$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AJ$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AK19" s="13">
+      <c r="AK19" s="66">
         <f>IF(AK$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AK$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AL19" s="13">
+      <c r="AL19" s="66">
         <f>IF(AL$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AL$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AM19" s="13">
+      <c r="AM19" s="66">
         <f>IF(AM$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AM$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AN19" s="13">
+      <c r="AN19" s="66">
         <f>IF(AN$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AN$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AO19" s="13">
+      <c r="AO19" s="66">
         <f>IF(AO$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AO$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AP19" s="13">
+      <c r="AP19" s="66">
         <f>IF(AP$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AP$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AQ19" s="13">
+      <c r="AQ19" s="66">
         <f>IF(AQ$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AQ$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AR19" s="13">
+      <c r="AR19" s="66">
         <f>IF(AR$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AR$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AS19" s="13">
+      <c r="AS19" s="66">
         <f>IF(AS$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AS$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AT19" s="13">
+      <c r="AT19" s="66">
         <f>IF(AT$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AT$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AU19" s="13">
+      <c r="AU19" s="66">
         <f>IF(AU$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AU$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AV19" s="13">
+      <c r="AV19" s="66">
         <f>IF(AV$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AV$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AW19" s="13">
+      <c r="AW19" s="66">
         <f>IF(AW$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AW$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AX19" s="13">
+      <c r="AX19" s="66">
         <f>IF(AX$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AX$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AY19" s="13">
+      <c r="AY19" s="66">
         <f>IF(AY$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AY$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="AZ19" s="13">
+      <c r="AZ19" s="66">
         <f>IF(AZ$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(AZ$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="BA19" s="13">
+      <c r="BA19" s="66">
         <f>IF(BA$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(BA$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="BB19" s="13">
+      <c r="BB19" s="66">
         <f>IF(BB$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(BB$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="BC19" s="13">
+      <c r="BC19" s="66">
         <f>IF(BC$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(BC$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="BD19" s="13">
+      <c r="BD19" s="66">
         <f>IF(BD$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(BD$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="BE19" s="13">
+      <c r="BE19" s="66">
         <f>IF(BE$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(BE$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="BF19" s="13">
+      <c r="BF19" s="66">
         <f>IF(BF$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(BF$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="BG19" s="13">
+      <c r="BG19" s="66">
         <f>IF(BG$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(BG$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="BH19" s="13">
+      <c r="BH19" s="66">
         <f>IF(BH$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(BH$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="BI19" s="13">
+      <c r="BI19" s="66">
         <f>IF(BI$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(BI$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="BJ19" s="13">
+      <c r="BJ19" s="66">
         <f>IF(BJ$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(BJ$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="BK19" s="13">
+      <c r="BK19" s="66">
         <f>IF(BK$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(BK$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="BL19" s="13">
+      <c r="BL19" s="66">
         <f>IF(BL$3&lt;Assumptions!$F$13,0,HLOOKUP(YEAR(BL$3),Assumptions!$D$63:$H$66,4,FALSE))</f>
         <v/>
       </c>
-      <c r="BN19" s="68">
+      <c r="BN19" s="67">
         <f>SUM(E19:P19)</f>
         <v/>
       </c>
-      <c r="BO19" s="68">
+      <c r="BO19" s="67">
         <f>SUM(Q19:AB19)</f>
         <v/>
       </c>
-      <c r="BP19" s="68">
+      <c r="BP19" s="67">
         <f>SUM(AC19:AN19)</f>
         <v/>
       </c>
-      <c r="BQ19" s="68">
+      <c r="BQ19" s="67">
         <f>SUM(AO19:AZ19)</f>
         <v/>
       </c>
-      <c r="BR19" s="68">
+      <c r="BR19" s="67">
         <f>SUM(BA19:BL19)</f>
         <v/>
       </c>
       <c r="BT19" s="30" t="inlineStr">
         <is>
-          <t>no partner intros before the first month we can sell</t>
+          <t>the planned rate, which can be less than one a month</t>
         </is>
       </c>
     </row>
@@ -24767,243 +24772,243 @@
         </is>
       </c>
       <c r="E20" s="13">
-        <f>Assumptions!$F$74+E19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:E19),0)</f>
         <v/>
       </c>
       <c r="F20" s="13">
-        <f>E20+F19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:F19),0)</f>
         <v/>
       </c>
       <c r="G20" s="13">
-        <f>F20+G19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:G19),0)</f>
         <v/>
       </c>
       <c r="H20" s="13">
-        <f>G20+H19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:H19),0)</f>
         <v/>
       </c>
       <c r="I20" s="13">
-        <f>H20+I19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:I19),0)</f>
         <v/>
       </c>
       <c r="J20" s="13">
-        <f>I20+J19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:J19),0)</f>
         <v/>
       </c>
       <c r="K20" s="13">
-        <f>J20+K19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:K19),0)</f>
         <v/>
       </c>
       <c r="L20" s="13">
-        <f>K20+L19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:L19),0)</f>
         <v/>
       </c>
       <c r="M20" s="13">
-        <f>L20+M19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:M19),0)</f>
         <v/>
       </c>
       <c r="N20" s="13">
-        <f>M20+N19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:N19),0)</f>
         <v/>
       </c>
       <c r="O20" s="13">
-        <f>N20+O19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:O19),0)</f>
         <v/>
       </c>
       <c r="P20" s="13">
-        <f>O20+P19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:P19),0)</f>
         <v/>
       </c>
       <c r="Q20" s="13">
-        <f>P20+Q19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:Q19),0)</f>
         <v/>
       </c>
       <c r="R20" s="13">
-        <f>Q20+R19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:R19),0)</f>
         <v/>
       </c>
       <c r="S20" s="13">
-        <f>R20+S19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:S19),0)</f>
         <v/>
       </c>
       <c r="T20" s="13">
-        <f>S20+T19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:T19),0)</f>
         <v/>
       </c>
       <c r="U20" s="13">
-        <f>T20+U19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:U19),0)</f>
         <v/>
       </c>
       <c r="V20" s="13">
-        <f>U20+V19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:V19),0)</f>
         <v/>
       </c>
       <c r="W20" s="13">
-        <f>V20+W19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:W19),0)</f>
         <v/>
       </c>
       <c r="X20" s="13">
-        <f>W20+X19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:X19),0)</f>
         <v/>
       </c>
       <c r="Y20" s="13">
-        <f>X20+Y19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:Y19),0)</f>
         <v/>
       </c>
       <c r="Z20" s="13">
-        <f>Y20+Z19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:Z19),0)</f>
         <v/>
       </c>
       <c r="AA20" s="13">
-        <f>Z20+AA19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AA19),0)</f>
         <v/>
       </c>
       <c r="AB20" s="13">
-        <f>AA20+AB19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AB19),0)</f>
         <v/>
       </c>
       <c r="AC20" s="13">
-        <f>AB20+AC19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AC19),0)</f>
         <v/>
       </c>
       <c r="AD20" s="13">
-        <f>AC20+AD19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AD19),0)</f>
         <v/>
       </c>
       <c r="AE20" s="13">
-        <f>AD20+AE19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AE19),0)</f>
         <v/>
       </c>
       <c r="AF20" s="13">
-        <f>AE20+AF19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AF19),0)</f>
         <v/>
       </c>
       <c r="AG20" s="13">
-        <f>AF20+AG19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AG19),0)</f>
         <v/>
       </c>
       <c r="AH20" s="13">
-        <f>AG20+AH19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AH19),0)</f>
         <v/>
       </c>
       <c r="AI20" s="13">
-        <f>AH20+AI19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AI19),0)</f>
         <v/>
       </c>
       <c r="AJ20" s="13">
-        <f>AI20+AJ19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AJ19),0)</f>
         <v/>
       </c>
       <c r="AK20" s="13">
-        <f>AJ20+AK19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AK19),0)</f>
         <v/>
       </c>
       <c r="AL20" s="13">
-        <f>AK20+AL19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AL19),0)</f>
         <v/>
       </c>
       <c r="AM20" s="13">
-        <f>AL20+AM19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AM19),0)</f>
         <v/>
       </c>
       <c r="AN20" s="13">
-        <f>AM20+AN19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AN19),0)</f>
         <v/>
       </c>
       <c r="AO20" s="13">
-        <f>AN20+AO19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AO19),0)</f>
         <v/>
       </c>
       <c r="AP20" s="13">
-        <f>AO20+AP19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AP19),0)</f>
         <v/>
       </c>
       <c r="AQ20" s="13">
-        <f>AP20+AQ19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AQ19),0)</f>
         <v/>
       </c>
       <c r="AR20" s="13">
-        <f>AQ20+AR19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AR19),0)</f>
         <v/>
       </c>
       <c r="AS20" s="13">
-        <f>AR20+AS19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AS19),0)</f>
         <v/>
       </c>
       <c r="AT20" s="13">
-        <f>AS20+AT19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AT19),0)</f>
         <v/>
       </c>
       <c r="AU20" s="13">
-        <f>AT20+AU19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AU19),0)</f>
         <v/>
       </c>
       <c r="AV20" s="13">
-        <f>AU20+AV19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AV19),0)</f>
         <v/>
       </c>
       <c r="AW20" s="13">
-        <f>AV20+AW19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AW19),0)</f>
         <v/>
       </c>
       <c r="AX20" s="13">
-        <f>AW20+AX19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AX19),0)</f>
         <v/>
       </c>
       <c r="AY20" s="13">
-        <f>AX20+AY19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AY19),0)</f>
         <v/>
       </c>
       <c r="AZ20" s="13">
-        <f>AY20+AZ19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:AZ19),0)</f>
         <v/>
       </c>
       <c r="BA20" s="13">
-        <f>AZ20+BA19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:BA19),0)</f>
         <v/>
       </c>
       <c r="BB20" s="13">
-        <f>BA20+BB19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:BB19),0)</f>
         <v/>
       </c>
       <c r="BC20" s="13">
-        <f>BB20+BC19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:BC19),0)</f>
         <v/>
       </c>
       <c r="BD20" s="13">
-        <f>BC20+BD19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:BD19),0)</f>
         <v/>
       </c>
       <c r="BE20" s="13">
-        <f>BD20+BE19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:BE19),0)</f>
         <v/>
       </c>
       <c r="BF20" s="13">
-        <f>BE20+BF19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:BF19),0)</f>
         <v/>
       </c>
       <c r="BG20" s="13">
-        <f>BF20+BG19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:BG19),0)</f>
         <v/>
       </c>
       <c r="BH20" s="13">
-        <f>BG20+BH19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:BH19),0)</f>
         <v/>
       </c>
       <c r="BI20" s="13">
-        <f>BH20+BI19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:BI19),0)</f>
         <v/>
       </c>
       <c r="BJ20" s="13">
-        <f>BI20+BJ19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:BJ19),0)</f>
         <v/>
       </c>
       <c r="BK20" s="13">
-        <f>BJ20+BK19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:BK19),0)</f>
         <v/>
       </c>
       <c r="BL20" s="13">
-        <f>BK20+BL19</f>
+        <f>ROUNDDOWN(Assumptions!$F$74+SUM($E19:BL19),0)</f>
         <v/>
       </c>
       <c r="BN20" s="68">
@@ -25025,6 +25030,11 @@
       <c r="BR20" s="68">
         <f>BL20</f>
         <v/>
+      </c>
+      <c r="BT20" s="30" t="inlineStr">
+        <is>
+          <t>whole partners only, signed as the running total passes each whole number</t>
+        </is>
       </c>
     </row>
     <row r="21">

--- a/models/Tarnoc_v2_2026-09-07.xlsx
+++ b/models/Tarnoc_v2_2026-09-07.xlsx
@@ -28020,243 +28020,243 @@
         </is>
       </c>
       <c r="E39" s="9">
-        <f>E34*Assumptions!$F$27</f>
+        <f>ROUND(E34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="F39" s="9">
-        <f>F34*Assumptions!$F$27</f>
+        <f>ROUND(F34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="G39" s="9">
-        <f>G34*Assumptions!$F$27</f>
+        <f>ROUND(G34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="H39" s="9">
-        <f>H34*Assumptions!$F$27</f>
+        <f>ROUND(H34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="I39" s="9">
-        <f>I34*Assumptions!$F$27</f>
+        <f>ROUND(I34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="J39" s="9">
-        <f>J34*Assumptions!$F$27</f>
+        <f>ROUND(J34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="K39" s="9">
-        <f>K34*Assumptions!$F$27</f>
+        <f>ROUND(K34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="L39" s="9">
-        <f>L34*Assumptions!$F$27</f>
+        <f>ROUND(L34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="M39" s="9">
-        <f>M34*Assumptions!$F$27</f>
+        <f>ROUND(M34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="N39" s="9">
-        <f>N34*Assumptions!$F$27</f>
+        <f>ROUND(N34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="O39" s="9">
-        <f>O34*Assumptions!$F$27</f>
+        <f>ROUND(O34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="P39" s="9">
-        <f>P34*Assumptions!$F$27</f>
+        <f>ROUND(P34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="Q39" s="9">
-        <f>Q34*Assumptions!$F$27</f>
+        <f>ROUND(Q34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="R39" s="9">
-        <f>R34*Assumptions!$F$27</f>
+        <f>ROUND(R34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="S39" s="9">
-        <f>S34*Assumptions!$F$27</f>
+        <f>ROUND(S34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="T39" s="9">
-        <f>T34*Assumptions!$F$27</f>
+        <f>ROUND(T34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="U39" s="9">
-        <f>U34*Assumptions!$F$27</f>
+        <f>ROUND(U34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="V39" s="9">
-        <f>V34*Assumptions!$F$27</f>
+        <f>ROUND(V34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="W39" s="9">
-        <f>W34*Assumptions!$F$27</f>
+        <f>ROUND(W34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="X39" s="9">
-        <f>X34*Assumptions!$F$27</f>
+        <f>ROUND(X34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="Y39" s="9">
-        <f>Y34*Assumptions!$F$27</f>
+        <f>ROUND(Y34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="Z39" s="9">
-        <f>Z34*Assumptions!$F$27</f>
+        <f>ROUND(Z34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AA39" s="9">
-        <f>AA34*Assumptions!$F$27</f>
+        <f>ROUND(AA34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AB39" s="9">
-        <f>AB34*Assumptions!$F$27</f>
+        <f>ROUND(AB34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AC39" s="9">
-        <f>AC34*Assumptions!$F$27</f>
+        <f>ROUND(AC34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AD39" s="9">
-        <f>AD34*Assumptions!$F$27</f>
+        <f>ROUND(AD34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AE39" s="9">
-        <f>AE34*Assumptions!$F$27</f>
+        <f>ROUND(AE34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AF39" s="9">
-        <f>AF34*Assumptions!$F$27</f>
+        <f>ROUND(AF34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AG39" s="9">
-        <f>AG34*Assumptions!$F$27</f>
+        <f>ROUND(AG34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AH39" s="9">
-        <f>AH34*Assumptions!$F$27</f>
+        <f>ROUND(AH34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AI39" s="9">
-        <f>AI34*Assumptions!$F$27</f>
+        <f>ROUND(AI34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AJ39" s="9">
-        <f>AJ34*Assumptions!$F$27</f>
+        <f>ROUND(AJ34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AK39" s="9">
-        <f>AK34*Assumptions!$F$27</f>
+        <f>ROUND(AK34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AL39" s="9">
-        <f>AL34*Assumptions!$F$27</f>
+        <f>ROUND(AL34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AM39" s="9">
-        <f>AM34*Assumptions!$F$27</f>
+        <f>ROUND(AM34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AN39" s="9">
-        <f>AN34*Assumptions!$F$27</f>
+        <f>ROUND(AN34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AO39" s="9">
-        <f>AO34*Assumptions!$F$27</f>
+        <f>ROUND(AO34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AP39" s="9">
-        <f>AP34*Assumptions!$F$27</f>
+        <f>ROUND(AP34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AQ39" s="9">
-        <f>AQ34*Assumptions!$F$27</f>
+        <f>ROUND(AQ34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AR39" s="9">
-        <f>AR34*Assumptions!$F$27</f>
+        <f>ROUND(AR34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AS39" s="9">
-        <f>AS34*Assumptions!$F$27</f>
+        <f>ROUND(AS34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AT39" s="9">
-        <f>AT34*Assumptions!$F$27</f>
+        <f>ROUND(AT34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AU39" s="9">
-        <f>AU34*Assumptions!$F$27</f>
+        <f>ROUND(AU34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AV39" s="9">
-        <f>AV34*Assumptions!$F$27</f>
+        <f>ROUND(AV34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AW39" s="9">
-        <f>AW34*Assumptions!$F$27</f>
+        <f>ROUND(AW34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AX39" s="9">
-        <f>AX34*Assumptions!$F$27</f>
+        <f>ROUND(AX34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AY39" s="9">
-        <f>AY34*Assumptions!$F$27</f>
+        <f>ROUND(AY34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="AZ39" s="9">
-        <f>AZ34*Assumptions!$F$27</f>
+        <f>ROUND(AZ34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="BA39" s="9">
-        <f>BA34*Assumptions!$F$27</f>
+        <f>ROUND(BA34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="BB39" s="9">
-        <f>BB34*Assumptions!$F$27</f>
+        <f>ROUND(BB34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="BC39" s="9">
-        <f>BC34*Assumptions!$F$27</f>
+        <f>ROUND(BC34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="BD39" s="9">
-        <f>BD34*Assumptions!$F$27</f>
+        <f>ROUND(BD34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="BE39" s="9">
-        <f>BE34*Assumptions!$F$27</f>
+        <f>ROUND(BE34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="BF39" s="9">
-        <f>BF34*Assumptions!$F$27</f>
+        <f>ROUND(BF34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="BG39" s="9">
-        <f>BG34*Assumptions!$F$27</f>
+        <f>ROUND(BG34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="BH39" s="9">
-        <f>BH34*Assumptions!$F$27</f>
+        <f>ROUND(BH34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="BI39" s="9">
-        <f>BI34*Assumptions!$F$27</f>
+        <f>ROUND(BI34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="BJ39" s="9">
-        <f>BJ34*Assumptions!$F$27</f>
+        <f>ROUND(BJ34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="BK39" s="9">
-        <f>BK34*Assumptions!$F$27</f>
+        <f>ROUND(BK34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="BL39" s="9">
-        <f>BL34*Assumptions!$F$27</f>
+        <f>ROUND(BL34*Assumptions!$F$27,0)</f>
         <v/>
       </c>
       <c r="BN39" s="63">
@@ -28279,6 +28279,11 @@
         <f>SUM(BA39:BL39)</f>
         <v/>
       </c>
+      <c r="BT39" s="30" t="inlineStr">
+        <is>
+          <t>whole units, and the Combi+ row takes the remainder so the two add to units sold</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="B40" s="6" t="inlineStr">
@@ -28292,243 +28297,243 @@
         </is>
       </c>
       <c r="E40" s="9">
-        <f>E34*Assumptions!$F$28</f>
+        <f>E34-E39</f>
         <v/>
       </c>
       <c r="F40" s="9">
-        <f>F34*Assumptions!$F$28</f>
+        <f>F34-F39</f>
         <v/>
       </c>
       <c r="G40" s="9">
-        <f>G34*Assumptions!$F$28</f>
+        <f>G34-G39</f>
         <v/>
       </c>
       <c r="H40" s="9">
-        <f>H34*Assumptions!$F$28</f>
+        <f>H34-H39</f>
         <v/>
       </c>
       <c r="I40" s="9">
-        <f>I34*Assumptions!$F$28</f>
+        <f>I34-I39</f>
         <v/>
       </c>
       <c r="J40" s="9">
-        <f>J34*Assumptions!$F$28</f>
+        <f>J34-J39</f>
         <v/>
       </c>
       <c r="K40" s="9">
-        <f>K34*Assumptions!$F$28</f>
+        <f>K34-K39</f>
         <v/>
       </c>
       <c r="L40" s="9">
-        <f>L34*Assumptions!$F$28</f>
+        <f>L34-L39</f>
         <v/>
       </c>
       <c r="M40" s="9">
-        <f>M34*Assumptions!$F$28</f>
+        <f>M34-M39</f>
         <v/>
       </c>
       <c r="N40" s="9">
-        <f>N34*Assumptions!$F$28</f>
+        <f>N34-N39</f>
         <v/>
       </c>
       <c r="O40" s="9">
-        <f>O34*Assumptions!$F$28</f>
+        <f>O34-O39</f>
         <v/>
       </c>
       <c r="P40" s="9">
-        <f>P34*Assumptions!$F$28</f>
+        <f>P34-P39</f>
         <v/>
       </c>
       <c r="Q40" s="9">
-        <f>Q34*Assumptions!$F$28</f>
+        <f>Q34-Q39</f>
         <v/>
       </c>
       <c r="R40" s="9">
-        <f>R34*Assumptions!$F$28</f>
+        <f>R34-R39</f>
         <v/>
       </c>
       <c r="S40" s="9">
-        <f>S34*Assumptions!$F$28</f>
+        <f>S34-S39</f>
         <v/>
       </c>
       <c r="T40" s="9">
-        <f>T34*Assumptions!$F$28</f>
+        <f>T34-T39</f>
         <v/>
       </c>
       <c r="U40" s="9">
-        <f>U34*Assumptions!$F$28</f>
+        <f>U34-U39</f>
         <v/>
       </c>
       <c r="V40" s="9">
-        <f>V34*Assumptions!$F$28</f>
+        <f>V34-V39</f>
         <v/>
       </c>
       <c r="W40" s="9">
-        <f>W34*Assumptions!$F$28</f>
+        <f>W34-W39</f>
         <v/>
       </c>
       <c r="X40" s="9">
-        <f>X34*Assumptions!$F$28</f>
+        <f>X34-X39</f>
         <v/>
       </c>
       <c r="Y40" s="9">
-        <f>Y34*Assumptions!$F$28</f>
+        <f>Y34-Y39</f>
         <v/>
       </c>
       <c r="Z40" s="9">
-        <f>Z34*Assumptions!$F$28</f>
+        <f>Z34-Z39</f>
         <v/>
       </c>
       <c r="AA40" s="9">
-        <f>AA34*Assumptions!$F$28</f>
+        <f>AA34-AA39</f>
         <v/>
       </c>
       <c r="AB40" s="9">
-        <f>AB34*Assumptions!$F$28</f>
+        <f>AB34-AB39</f>
         <v/>
       </c>
       <c r="AC40" s="9">
-        <f>AC34*Assumptions!$F$28</f>
+        <f>AC34-AC39</f>
         <v/>
       </c>
       <c r="AD40" s="9">
-        <f>AD34*Assumptions!$F$28</f>
+        <f>AD34-AD39</f>
         <v/>
       </c>
       <c r="AE40" s="9">
-        <f>AE34*Assumptions!$F$28</f>
+        <f>AE34-AE39</f>
         <v/>
       </c>
       <c r="AF40" s="9">
-        <f>AF34*Assumptions!$F$28</f>
+        <f>AF34-AF39</f>
         <v/>
       </c>
       <c r="AG40" s="9">
-        <f>AG34*Assumptions!$F$28</f>
+        <f>AG34-AG39</f>
         <v/>
       </c>
       <c r="AH40" s="9">
-        <f>AH34*Assumptions!$F$28</f>
+        <f>AH34-AH39</f>
         <v/>
       </c>
       <c r="AI40" s="9">
-        <f>AI34*Assumptions!$F$28</f>
+        <f>AI34-AI39</f>
         <v/>
       </c>
       <c r="AJ40" s="9">
-        <f>AJ34*Assumptions!$F$28</f>
+        <f>AJ34-AJ39</f>
         <v/>
       </c>
       <c r="AK40" s="9">
-        <f>AK34*Assumptions!$F$28</f>
+        <f>AK34-AK39</f>
         <v/>
       </c>
       <c r="AL40" s="9">
-        <f>AL34*Assumptions!$F$28</f>
+        <f>AL34-AL39</f>
         <v/>
       </c>
       <c r="AM40" s="9">
-        <f>AM34*Assumptions!$F$28</f>
+        <f>AM34-AM39</f>
         <v/>
       </c>
       <c r="AN40" s="9">
-        <f>AN34*Assumptions!$F$28</f>
+        <f>AN34-AN39</f>
         <v/>
       </c>
       <c r="AO40" s="9">
-        <f>AO34*Assumptions!$F$28</f>
+        <f>AO34-AO39</f>
         <v/>
       </c>
       <c r="AP40" s="9">
-        <f>AP34*Assumptions!$F$28</f>
+        <f>AP34-AP39</f>
         <v/>
       </c>
       <c r="AQ40" s="9">
-        <f>AQ34*Assumptions!$F$28</f>
+        <f>AQ34-AQ39</f>
         <v/>
       </c>
       <c r="AR40" s="9">
-        <f>AR34*Assumptions!$F$28</f>
+        <f>AR34-AR39</f>
         <v/>
       </c>
       <c r="AS40" s="9">
-        <f>AS34*Assumptions!$F$28</f>
+        <f>AS34-AS39</f>
         <v/>
       </c>
       <c r="AT40" s="9">
-        <f>AT34*Assumptions!$F$28</f>
+        <f>AT34-AT39</f>
         <v/>
       </c>
       <c r="AU40" s="9">
-        <f>AU34*Assumptions!$F$28</f>
+        <f>AU34-AU39</f>
         <v/>
       </c>
       <c r="AV40" s="9">
-        <f>AV34*Assumptions!$F$28</f>
+        <f>AV34-AV39</f>
         <v/>
       </c>
       <c r="AW40" s="9">
-        <f>AW34*Assumptions!$F$28</f>
+        <f>AW34-AW39</f>
         <v/>
       </c>
       <c r="AX40" s="9">
-        <f>AX34*Assumptions!$F$28</f>
+        <f>AX34-AX39</f>
         <v/>
       </c>
       <c r="AY40" s="9">
-        <f>AY34*Assumptions!$F$28</f>
+        <f>AY34-AY39</f>
         <v/>
       </c>
       <c r="AZ40" s="9">
-        <f>AZ34*Assumptions!$F$28</f>
+        <f>AZ34-AZ39</f>
         <v/>
       </c>
       <c r="BA40" s="9">
-        <f>BA34*Assumptions!$F$28</f>
+        <f>BA34-BA39</f>
         <v/>
       </c>
       <c r="BB40" s="9">
-        <f>BB34*Assumptions!$F$28</f>
+        <f>BB34-BB39</f>
         <v/>
       </c>
       <c r="BC40" s="9">
-        <f>BC34*Assumptions!$F$28</f>
+        <f>BC34-BC39</f>
         <v/>
       </c>
       <c r="BD40" s="9">
-        <f>BD34*Assumptions!$F$28</f>
+        <f>BD34-BD39</f>
         <v/>
       </c>
       <c r="BE40" s="9">
-        <f>BE34*Assumptions!$F$28</f>
+        <f>BE34-BE39</f>
         <v/>
       </c>
       <c r="BF40" s="9">
-        <f>BF34*Assumptions!$F$28</f>
+        <f>BF34-BF39</f>
         <v/>
       </c>
       <c r="BG40" s="9">
-        <f>BG34*Assumptions!$F$28</f>
+        <f>BG34-BG39</f>
         <v/>
       </c>
       <c r="BH40" s="9">
-        <f>BH34*Assumptions!$F$28</f>
+        <f>BH34-BH39</f>
         <v/>
       </c>
       <c r="BI40" s="9">
-        <f>BI34*Assumptions!$F$28</f>
+        <f>BI34-BI39</f>
         <v/>
       </c>
       <c r="BJ40" s="9">
-        <f>BJ34*Assumptions!$F$28</f>
+        <f>BJ34-BJ39</f>
         <v/>
       </c>
       <c r="BK40" s="9">
-        <f>BK34*Assumptions!$F$28</f>
+        <f>BK34-BK39</f>
         <v/>
       </c>
       <c r="BL40" s="9">
-        <f>BL34*Assumptions!$F$28</f>
+        <f>BL34-BL39</f>
         <v/>
       </c>
       <c r="BN40" s="63">
